--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8730" windowHeight="6510"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="535">
   <si>
     <t>orgao</t>
   </si>
@@ -709,9 +709,6 @@
     <t>http://www.der.mg.gov.br</t>
   </si>
   <si>
-    <t>http://www.esp.mg.gov.br</t>
-  </si>
-  <si>
     <t>http://www.fha.mg.gov.br</t>
   </si>
   <si>
@@ -853,9 +850,6 @@
     <t>Avenida Afonso Pena, 1537, Centro, Belo Horizonte, 30130-004</t>
   </si>
   <si>
-    <t>3915 8050</t>
-  </si>
-  <si>
     <t>4º andar do Edifício Minas - Cidade Administrativa, Belo Horizonte</t>
   </si>
   <si>
@@ -977,9 +971,6 @@
   </si>
   <si>
     <t>http://www.secretariageral.mg.gov.br/</t>
-  </si>
-  <si>
-    <t>Romeu Zema Neto</t>
   </si>
   <si>
     <t>Coronel Carlos Frederico Otoni Garcia</t>
@@ -1058,171 +1049,15 @@
     <t>https://www.policiacivil.mg.gov.br/</t>
   </si>
   <si>
-    <t>(31)3218 0700</t>
-  </si>
-  <si>
-    <t>(31)3219 8000</t>
-  </si>
-  <si>
     <t>(31)2109-9350</t>
   </si>
   <si>
-    <t>(31)3915 8119</t>
-  </si>
-  <si>
-    <t>(31)3506 3711</t>
-  </si>
-  <si>
-    <t>(31)3915 7030</t>
-  </si>
-  <si>
-    <t>(31)3348 9600</t>
-  </si>
-  <si>
-    <t>(31)3217 6161</t>
-  </si>
-  <si>
-    <t>(31)3521 9501</t>
-  </si>
-  <si>
-    <t>(31)3239 9500</t>
-  </si>
-  <si>
-    <t>(31)3915 2912</t>
-  </si>
-  <si>
-    <t>(31)3915 9099</t>
-  </si>
-  <si>
     <t>(31)3915-5209</t>
   </si>
   <si>
-    <t>(31)3915 1507</t>
-  </si>
-  <si>
-    <t>(31)3915 1752</t>
-  </si>
-  <si>
-    <t>(31)3298 3400</t>
-  </si>
-  <si>
-    <t>(31)3915 8366</t>
-  </si>
-  <si>
-    <t>(31)3399 7100</t>
-  </si>
-  <si>
     <t>(31)3915-2617</t>
   </si>
   <si>
-    <t>(31)3915 8050</t>
-  </si>
-  <si>
-    <t>(31)3916 8813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(31)3915 6983 </t>
-  </si>
-  <si>
-    <t>(31)3915 4878</t>
-  </si>
-  <si>
-    <t>(31)3239 8400</t>
-  </si>
-  <si>
-    <t>(31)3916 0790</t>
-  </si>
-  <si>
-    <t>(31)3915 3075</t>
-  </si>
-  <si>
-    <t>(31)3916 8235</t>
-  </si>
-  <si>
-    <t>(31)3916 0471</t>
-  </si>
-  <si>
-    <t>(31)3263 7500</t>
-  </si>
-  <si>
-    <t>(31)3915 5233</t>
-  </si>
-  <si>
-    <t>(31)3915 2677</t>
-  </si>
-  <si>
-    <t>(31)3349 8000</t>
-  </si>
-  <si>
-    <t>(31)3489 5000</t>
-  </si>
-  <si>
-    <t>(31)3551 2014</t>
-  </si>
-  <si>
-    <t>(31)3236 7400</t>
-  </si>
-  <si>
-    <t>(31)3235 2800</t>
-  </si>
-  <si>
-    <t>(31)3915 8682</t>
-  </si>
-  <si>
-    <t>(31)3915 7392</t>
-  </si>
-  <si>
-    <t>0800 9701212</t>
-  </si>
-  <si>
-    <t>0800 2831980</t>
-  </si>
-  <si>
-    <t>(31)3916 8100</t>
-  </si>
-  <si>
-    <t>(31)3501 3000</t>
-  </si>
-  <si>
-    <t>(31)3448 9400</t>
-  </si>
-  <si>
-    <t>(31)3295 5360</t>
-  </si>
-  <si>
-    <t>(31)3768 7450</t>
-  </si>
-  <si>
-    <t>(31)3915 2022</t>
-  </si>
-  <si>
-    <t>(31)3915 1700</t>
-  </si>
-  <si>
-    <t>(38)3229 8101</t>
-  </si>
-  <si>
-    <t>(31)3916 7819</t>
-  </si>
-  <si>
-    <t>(31)3916 7650</t>
-  </si>
-  <si>
-    <t>(31)3339 1100</t>
-  </si>
-  <si>
-    <t>(31)3915 7525</t>
-  </si>
-  <si>
-    <t>(31)3915 2093</t>
-  </si>
-  <si>
-    <t>(31)3280 2100</t>
-  </si>
-  <si>
-    <t>(31)3915 5028</t>
-  </si>
-  <si>
     <t>Advocacia Geral do Estado</t>
   </si>
   <si>
@@ -1329,13 +1164,493 @@
   </si>
   <si>
     <t>Secretaria Geral do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>e-mail</t>
+  </si>
+  <si>
+    <t>horario_atendimento</t>
+  </si>
+  <si>
+    <t>08:00 às 17:00</t>
+  </si>
+  <si>
+    <t>comunicacao@advocaciageral.mg.gov.br</t>
+  </si>
+  <si>
+    <t>janderson.silva@agenciarmbh.mg.gov.br</t>
+  </si>
+  <si>
+    <t>comunicacao@agenciarmva.mg.gov.br</t>
+  </si>
+  <si>
+    <t>08:00 às 18:00</t>
+  </si>
+  <si>
+    <t>09:00 às 18:00</t>
+  </si>
+  <si>
+    <t>circularizacao@bdmg.mg.gov.br</t>
+  </si>
+  <si>
+    <t>copasadigital@copasa.com.br</t>
+  </si>
+  <si>
+    <t>08:00 às 16:30</t>
+  </si>
+  <si>
+    <t>atendimento@prodemge.gov.br</t>
+  </si>
+  <si>
+    <t>duvidas_sistema_aprweb@cemig.com.br</t>
+  </si>
+  <si>
+    <t>ascom@cge.mg.gov.br </t>
+  </si>
+  <si>
+    <t>dai.secretaria@bombeiros.mg.gov.br</t>
+  </si>
+  <si>
+    <t>imprensa@der.mg.gov.br </t>
+  </si>
+  <si>
+    <t>ascom@epamig.br</t>
+  </si>
+  <si>
+    <t>marcelo.torres@emater.mg.gov.br</t>
+  </si>
+  <si>
+    <t>atendimento@redeminas.mg.gov.br</t>
+  </si>
+  <si>
+    <t>08:00 às 19:00</t>
+  </si>
+  <si>
+    <t>08:00 às 20:00</t>
+  </si>
+  <si>
+    <t>https://esp.mg.gov.br/</t>
+  </si>
+  <si>
+    <t>comunicacao@esp.mg.gov.br</t>
+  </si>
+  <si>
+    <t>07:00 às 18:00</t>
+  </si>
+  <si>
+    <t>comunicacao@hemominas.mg.gov.br</t>
+  </si>
+  <si>
+    <t>mediacao@fcs.mg.gov.br</t>
+  </si>
+  <si>
+    <t>comunicacao@desenvolvimento.mg.gov.br</t>
+  </si>
+  <si>
+    <t>faop@faop.mg.gov.br</t>
+  </si>
+  <si>
+    <t>faleconosco@utramig.mg.gov.br</t>
+  </si>
+  <si>
+    <t>09:00 às 17:00</t>
+  </si>
+  <si>
+    <t>comunicacao@edu.fucam.mg.gov.br</t>
+  </si>
+  <si>
+    <t>feam@feam.br</t>
+  </si>
+  <si>
+    <t>ouvidoriasus@funed.mg.gov.br</t>
+  </si>
+  <si>
+    <t>faleconosco@fha.mg.gov.br</t>
+  </si>
+  <si>
+    <t>faleconosco@ipsm.mg.gov.br</t>
+  </si>
+  <si>
+    <t>07:00 às 22:40</t>
+  </si>
+  <si>
+    <t>ce.dir@fhemig.mg.gov.br</t>
+  </si>
+  <si>
+    <t>comunicacao@fjp.mg.gov.br</t>
+  </si>
+  <si>
+    <t>comunicacao@gabinetemilitar.mg.gov.br</t>
+  </si>
+  <si>
+    <t>contato@idene.com.br</t>
+  </si>
+  <si>
+    <t>ola@investminas.mg.gov.br</t>
+  </si>
+  <si>
+    <t>ouvidoria@arsae.mg.gov.br</t>
+  </si>
+  <si>
+    <t>DETRAN</t>
+  </si>
+  <si>
+    <t>Departamento Estadual de Trânsito de Minas Gerais</t>
+  </si>
+  <si>
+    <t>https://www.transito.mg.gov.br/</t>
+  </si>
+  <si>
+    <t>ima@ima.mg.gov.br</t>
+  </si>
+  <si>
+    <t>08:00 às 18:30</t>
+  </si>
+  <si>
+    <t>Agência Reguladora de Transportes de Minas Gerais</t>
+  </si>
+  <si>
+    <t>ARTEMIG</t>
+  </si>
+  <si>
+    <t>codemge@codemge.com.br</t>
+  </si>
+  <si>
+    <t>Companhia de Gás de Minas Gerais</t>
+  </si>
+  <si>
+    <t>GASMIG</t>
+  </si>
+  <si>
+    <t>http://www.gasmig.com.br/</t>
+  </si>
+  <si>
+    <t>relacionamento@mgs.srv.br</t>
+  </si>
+  <si>
+    <t>Trem Metropolitano de Belo Horizonte S.A.</t>
+  </si>
+  <si>
+    <t>METROMINAS</t>
+  </si>
+  <si>
+    <t>gabinete@iepha.mg.gov.br</t>
+  </si>
+  <si>
+    <t>07:00 às 17:00</t>
+  </si>
+  <si>
+    <t>08:30 às 18:00</t>
+  </si>
+  <si>
+    <t>09:00 às 22:00</t>
+  </si>
+  <si>
+    <t>jornalismo@ouvidoriageral.mg.gov.br</t>
+  </si>
+  <si>
+    <t>gabsecom@governo.mg.gov.br</t>
+  </si>
+  <si>
+    <t>Rone Evaldo Barbosa</t>
+  </si>
+  <si>
+    <t>3º andar do Edifício Gerais - Cidade Administrativa, Belo Horizonte</t>
+  </si>
+  <si>
+    <t>relacionamento@detran.mg.gov.br</t>
+  </si>
+  <si>
+    <t>(31)3069-6601</t>
+  </si>
+  <si>
+    <t>secretariageral@jucemg.mg.gov.br</t>
+  </si>
+  <si>
+    <t>(31)3916-7205</t>
+  </si>
+  <si>
+    <t>(31)3915-0564</t>
+  </si>
+  <si>
+    <t>ascom@planejamento.mg.gov.br</t>
+  </si>
+  <si>
+    <t>Mateus Simões de Almeida</t>
+  </si>
+  <si>
+    <t>secretariageral@governo.mg.gov.br</t>
+  </si>
+  <si>
+    <t>(31)3915-9071</t>
+  </si>
+  <si>
+    <t>(31)3915-0262</t>
+  </si>
+  <si>
+    <t>0800-9701212</t>
+  </si>
+  <si>
+    <t>0800-2831980</t>
+  </si>
+  <si>
+    <t>(38)3229-8101</t>
+  </si>
+  <si>
+    <t>(31)3916-8813</t>
+  </si>
+  <si>
+    <t>(31)3916-8235</t>
+  </si>
+  <si>
+    <t>(31)3916-8100</t>
+  </si>
+  <si>
+    <t>(31)3916-7819</t>
+  </si>
+  <si>
+    <t>(31)3916-7650</t>
+  </si>
+  <si>
+    <t>(31)3916-0790</t>
+  </si>
+  <si>
+    <t>(31)3916-0471</t>
+  </si>
+  <si>
+    <t>(31)3915-9099</t>
+  </si>
+  <si>
+    <t>(31)3915-8682</t>
+  </si>
+  <si>
+    <t>(31)3915-8366</t>
+  </si>
+  <si>
+    <t>(31)3915-8119</t>
+  </si>
+  <si>
+    <t>(31)3915-8050</t>
+  </si>
+  <si>
+    <t>(31)3915-7525</t>
+  </si>
+  <si>
+    <t>(31)3915-7392</t>
+  </si>
+  <si>
+    <t>(31)3915-7030</t>
+  </si>
+  <si>
+    <t>(31)3915-6983-</t>
+  </si>
+  <si>
+    <t>(31)3915-5233</t>
+  </si>
+  <si>
+    <t>(31)3915-5028</t>
+  </si>
+  <si>
+    <t>(31)3915-4878</t>
+  </si>
+  <si>
+    <t>(31)3915-3075</t>
+  </si>
+  <si>
+    <t>(31)3915-2912</t>
+  </si>
+  <si>
+    <t>(31)3915-2677</t>
+  </si>
+  <si>
+    <t>(31)3915-2093</t>
+  </si>
+  <si>
+    <t>(31)3915-2022</t>
+  </si>
+  <si>
+    <t>(31)3915-1752</t>
+  </si>
+  <si>
+    <t>(31)3915-1700</t>
+  </si>
+  <si>
+    <t>(31)3915-1507</t>
+  </si>
+  <si>
+    <t>(31)3768-7450</t>
+  </si>
+  <si>
+    <t>(31)3551-2014</t>
+  </si>
+  <si>
+    <t>(31)3521-9501</t>
+  </si>
+  <si>
+    <t>(31)3506-3711</t>
+  </si>
+  <si>
+    <t>(31)3501-3000</t>
+  </si>
+  <si>
+    <t>(31)3489-5000</t>
+  </si>
+  <si>
+    <t>(31)3448-9400</t>
+  </si>
+  <si>
+    <t>(31)3399-7100</t>
+  </si>
+  <si>
+    <t>(31)3349-8000</t>
+  </si>
+  <si>
+    <t>(31)3348-9600</t>
+  </si>
+  <si>
+    <t>(31)3339-1100</t>
+  </si>
+  <si>
+    <t>(31)3298-3400</t>
+  </si>
+  <si>
+    <t>(31)3295-5360</t>
+  </si>
+  <si>
+    <t>(31)3280-2100</t>
+  </si>
+  <si>
+    <t>(31)3263-7500</t>
+  </si>
+  <si>
+    <t>(31)3239-9500</t>
+  </si>
+  <si>
+    <t>(31)3239-8400</t>
+  </si>
+  <si>
+    <t>(31)3236-7400</t>
+  </si>
+  <si>
+    <t>(31)3235-2800</t>
+  </si>
+  <si>
+    <t>(31)3219-8000</t>
+  </si>
+  <si>
+    <t>(31)3218-0700</t>
+  </si>
+  <si>
+    <t>(31)3217-6161</t>
+  </si>
+  <si>
+    <t>Breno Longobucco</t>
+  </si>
+  <si>
+    <t>(31)3915-8282</t>
+  </si>
+  <si>
+    <t>regulacaodetransportes@artemig.mg.gov.br</t>
+  </si>
+  <si>
+    <t>https://artemig.mg.gov.br/</t>
+  </si>
+  <si>
+    <t>Av. Barbacena, 1200 - 7º andar - Santo Agostinho, Belo Horizonte - MG</t>
+  </si>
+  <si>
+    <t>atendimento@gasmig.com.br</t>
+  </si>
+  <si>
+    <t>Carlos Ivan Camargo de Colón</t>
+  </si>
+  <si>
+    <t>0800-0300005</t>
+  </si>
+  <si>
+    <t>gabseemg@educacao.mg.gov.br</t>
+  </si>
+  <si>
+    <t>contato@metrominas.mg</t>
+  </si>
+  <si>
+    <t>secretaria.administracao@unimontes.br</t>
+  </si>
+  <si>
+    <t>gabinetesec@social.mg.gov.br</t>
+  </si>
+  <si>
+    <t>acs@saude.mg.gov.br</t>
+  </si>
+  <si>
+    <t>gtic@uemg.br</t>
+  </si>
+  <si>
+    <t>segov@governo.mg.gov.br</t>
+  </si>
+  <si>
+    <t>1bpm@pmmg.mg.gov.br</t>
+  </si>
+  <si>
+    <t>joao.sampaio@jucemg.mg.gov.br </t>
+  </si>
+  <si>
+    <t>acsgabinete@fazenda.mg.gov.br</t>
+  </si>
+  <si>
+    <t>comunicacao@ipem.mg.gov.br</t>
+  </si>
+  <si>
+    <t>gabinete.ief@meioambiente.mg.gov.br</t>
+  </si>
+  <si>
+    <t>ascom@meioambiente.mg.gov.br</t>
+  </si>
+  <si>
+    <t>gabinete.igam@meioambiente.mg.gov.br</t>
+  </si>
+  <si>
+    <t>matheus.rufino@ipsemg.mg.gov.br</t>
+  </si>
+  <si>
+    <t>imprensa@secult.mg.gov.br</t>
+  </si>
+  <si>
+    <t>ascom@seguranca.mg.gov.br</t>
+  </si>
+  <si>
+    <t>mgi@mgipar.com.br</t>
+  </si>
+  <si>
+    <t>maria.leal@agricultura.mg.gov.br</t>
+  </si>
+  <si>
+    <t>imprensa@infraestrutura.mg.gov.br</t>
+  </si>
+  <si>
+    <t>cobranca@cohab.mg.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/LEI/25235/2025/</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/LEI/25663/2025/</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/LEI/11021/1993/</t>
+  </si>
+  <si>
+    <t>https://www.policiacivil.mg.gov.br/pagina/fale-conosco</t>
+  </si>
+  <si>
+    <t>www.loteriamineira.com.br/fale-conosco</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1350,6 +1665,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1373,12 +1694,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1714,21 +2036,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="77.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.25" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
     <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="31.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1751,18 +2075,24 @@
         <v>193</v>
       </c>
       <c r="H1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I1" t="s">
+        <v>376</v>
+      </c>
+      <c r="J1" t="s">
         <v>128</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>394</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>
@@ -1771,573 +2101,693 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>400</v>
+        <v>356</v>
       </c>
       <c r="F2" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>339</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>464</v>
+      </c>
+      <c r="H2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="F3" t="s">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="G3" t="s">
-        <v>360</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>465</v>
+      </c>
+      <c r="H3" t="s">
+        <v>533</v>
+      </c>
+      <c r="I3" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="57">
+      <c r="A4" t="s">
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="G4" t="s">
-        <v>341</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="28.5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>451</v>
+      </c>
+      <c r="H4" t="s">
+        <v>511</v>
+      </c>
+      <c r="I4" t="s">
+        <v>394</v>
+      </c>
+      <c r="J4" t="s">
+        <v>143</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>324</v>
+      </c>
+      <c r="F5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G5" t="s">
+        <v>487</v>
+      </c>
+      <c r="H5" t="s">
+        <v>392</v>
+      </c>
+      <c r="I5" t="s">
+        <v>377</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>231</v>
-      </c>
-      <c r="F5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>236</v>
+        <v>315</v>
+      </c>
+      <c r="F6" t="s">
+        <v>203</v>
       </c>
       <c r="G6" t="s">
-        <v>340</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>440</v>
+      </c>
+      <c r="H6" t="s">
+        <v>517</v>
+      </c>
+      <c r="I6" t="s">
+        <v>404</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>325</v>
       </c>
       <c r="F7" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="G7" t="s">
-        <v>379</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>490</v>
+      </c>
+      <c r="H7" t="s">
+        <v>393</v>
+      </c>
+      <c r="I7" t="s">
+        <v>381</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G8" t="s">
+        <v>337</v>
+      </c>
+      <c r="H8" t="s">
+        <v>414</v>
+      </c>
+      <c r="I8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" t="s">
+        <v>496</v>
+      </c>
+      <c r="H9" t="s">
+        <v>400</v>
+      </c>
+      <c r="I9" t="s">
+        <v>434</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" t="s">
+        <v>460</v>
+      </c>
+      <c r="H10" t="s">
+        <v>420</v>
+      </c>
+      <c r="I10" t="s">
+        <v>377</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" t="s">
+        <v>209</v>
+      </c>
+      <c r="G11" t="s">
+        <v>476</v>
+      </c>
+      <c r="H11" t="s">
+        <v>522</v>
+      </c>
+      <c r="I11" t="s">
+        <v>377</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>358</v>
+      </c>
+      <c r="F12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" t="s">
+        <v>493</v>
+      </c>
+      <c r="H12" t="s">
+        <v>403</v>
+      </c>
+      <c r="I12" t="s">
+        <v>395</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" t="s">
+        <v>485</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="I13" t="s">
+        <v>432</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" t="s">
+        <v>251</v>
+      </c>
+      <c r="G14" t="s">
+        <v>455</v>
+      </c>
+      <c r="H14" t="s">
+        <v>405</v>
+      </c>
+      <c r="I14" t="s">
+        <v>404</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.5">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" t="s">
+        <v>231</v>
+      </c>
+      <c r="G15" t="s">
+        <v>462</v>
+      </c>
+      <c r="H15" t="s">
+        <v>416</v>
+      </c>
+      <c r="I15" t="s">
+        <v>381</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="57">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>359</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" t="s">
+        <v>478</v>
+      </c>
+      <c r="H16" t="s">
+        <v>520</v>
+      </c>
+      <c r="I16" t="s">
+        <v>381</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="57">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G17" t="s">
+        <v>486</v>
+      </c>
+      <c r="H17" t="s">
+        <v>519</v>
+      </c>
+      <c r="I17" t="s">
+        <v>377</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
         <v>34</v>
       </c>
-      <c r="E8" t="s">
-        <v>326</v>
-      </c>
-      <c r="F8" t="s">
-        <v>252</v>
-      </c>
-      <c r="G8" t="s">
-        <v>344</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>287</v>
-      </c>
-      <c r="F9" t="s">
-        <v>250</v>
-      </c>
-      <c r="G9" t="s">
-        <v>345</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>334</v>
-      </c>
-      <c r="F10" t="s">
-        <v>249</v>
-      </c>
-      <c r="G10" t="s">
-        <v>389</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>324</v>
-      </c>
-      <c r="F11" t="s">
-        <v>247</v>
-      </c>
-      <c r="G11" t="s">
-        <v>343</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>395</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>322</v>
-      </c>
-      <c r="F12" t="s">
-        <v>279</v>
-      </c>
-      <c r="G12" t="s">
-        <v>391</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>411</v>
-      </c>
-      <c r="F13" t="s">
-        <v>229</v>
-      </c>
-      <c r="G13" t="s">
-        <v>390</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>407</v>
-      </c>
-      <c r="F14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G14" t="s">
-        <v>380</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>327</v>
-      </c>
-      <c r="F15" t="s">
-        <v>243</v>
-      </c>
-      <c r="G15" t="s">
-        <v>370</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>329</v>
-      </c>
-      <c r="F16" t="s">
-        <v>242</v>
-      </c>
-      <c r="G16" t="s">
-        <v>371</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" t="s">
-        <v>328</v>
-      </c>
-      <c r="F17" t="s">
-        <v>241</v>
-      </c>
-      <c r="G17" t="s">
-        <v>354</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
       <c r="E18" t="s">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="F18" t="s">
-        <v>278</v>
+        <v>210</v>
       </c>
       <c r="G18" t="s">
-        <v>382</v>
+        <v>452</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>534</v>
+      </c>
+      <c r="I18" t="s">
+        <v>421</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
         <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>412</v>
+        <v>258</v>
       </c>
       <c r="F19" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G19" t="s">
-        <v>383</v>
+        <v>481</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>408</v>
+      </c>
+      <c r="I19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="F20" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G20" t="s">
-        <v>373</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>111</v>
+        <v>450</v>
+      </c>
+      <c r="H20" t="s">
+        <v>407</v>
+      </c>
+      <c r="I20" t="s">
+        <v>377</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="28.5">
+      <c r="A21" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
         <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="F21" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="G21" t="s">
-        <v>392</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>497</v>
+      </c>
+      <c r="H21" t="s">
+        <v>431</v>
+      </c>
+      <c r="I21" t="s">
+        <v>381</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -2351,633 +2801,768 @@
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G22" t="s">
-        <v>372</v>
+        <v>480</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="I22" t="s">
+        <v>381</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="K22" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>413</v>
+        <v>348</v>
       </c>
       <c r="F23" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="G23" t="s">
-        <v>367</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>467</v>
+      </c>
+      <c r="H23" t="s">
+        <v>379</v>
+      </c>
+      <c r="I23" t="s">
+        <v>377</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
         <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="F24" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="G24" t="s">
-        <v>387</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>492</v>
+      </c>
+      <c r="H24" t="s">
+        <v>401</v>
+      </c>
+      <c r="I24" t="s">
+        <v>433</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>397</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
         <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>264</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>209</v>
+        <v>357</v>
+      </c>
+      <c r="F25" t="s">
+        <v>253</v>
       </c>
       <c r="G25" t="s">
-        <v>385</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>122</v>
+        <v>479</v>
+      </c>
+      <c r="H25" t="s">
+        <v>399</v>
+      </c>
+      <c r="I25" t="s">
+        <v>398</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="57">
+      <c r="A26" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>261</v>
-      </c>
-      <c r="F26" t="s">
-        <v>262</v>
+        <v>233</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="G26" t="s">
-        <v>378</v>
+        <v>336</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>380</v>
+      </c>
+      <c r="I26" t="s">
+        <v>377</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="F27" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="G27" t="s">
-        <v>347</v>
+        <v>484</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>391</v>
+      </c>
+      <c r="I27" t="s">
+        <v>377</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="57">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>257</v>
-      </c>
-      <c r="F28" t="s">
-        <v>258</v>
+        <v>312</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="G28" t="s">
-        <v>348</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="1" t="s">
-        <v>396</v>
+        <v>475</v>
+      </c>
+      <c r="H28" t="s">
+        <v>435</v>
+      </c>
+      <c r="I28" t="s">
+        <v>377</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>415</v>
+        <v>307</v>
       </c>
       <c r="F29" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="G29" t="s">
+        <v>442</v>
+      </c>
+      <c r="H29" t="s">
+        <v>441</v>
+      </c>
+      <c r="I29" t="s">
+        <v>381</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="57">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G30" t="s">
+        <v>443</v>
+      </c>
+      <c r="H30" t="s">
+        <v>444</v>
+      </c>
+      <c r="I30" t="s">
+        <v>381</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
         <v>374</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" t="s">
-        <v>316</v>
-      </c>
-      <c r="F30" t="s">
-        <v>256</v>
-      </c>
-      <c r="G30" t="s">
-        <v>381</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>82</v>
-      </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
         <v>31</v>
       </c>
       <c r="E31" t="s">
-        <v>275</v>
+        <v>445</v>
       </c>
       <c r="F31" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="G31" t="s">
-        <v>349</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>447</v>
+      </c>
+      <c r="H31" t="s">
+        <v>446</v>
+      </c>
+      <c r="I31" t="s">
+        <v>381</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
+        <v>305</v>
+      </c>
+      <c r="F32" t="s">
+        <v>306</v>
+      </c>
+      <c r="G32" t="s">
+        <v>448</v>
+      </c>
+      <c r="H32" t="s">
+        <v>436</v>
+      </c>
+      <c r="I32" t="s">
+        <v>381</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="57">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>369</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G33" t="s">
+        <v>473</v>
+      </c>
+      <c r="H33" t="s">
+        <v>524</v>
+      </c>
+      <c r="I33" t="s">
+        <v>404</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
+        <v>288</v>
+      </c>
+      <c r="F34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G34" t="s">
+        <v>471</v>
+      </c>
+      <c r="H34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I34" t="s">
+        <v>394</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
         <v>16</v>
       </c>
-      <c r="E32" t="s">
-        <v>220</v>
-      </c>
-      <c r="F32" t="s">
-        <v>221</v>
-      </c>
-      <c r="G32" t="s">
-        <v>351</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" t="s">
-        <v>331</v>
-      </c>
-      <c r="F33" t="s">
-        <v>221</v>
-      </c>
-      <c r="G33" t="s">
-        <v>388</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" t="s">
-        <v>217</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G34" t="s">
-        <v>356</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>28</v>
-      </c>
       <c r="C35" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E35" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>398</v>
+        <v>301</v>
+      </c>
+      <c r="F35" t="s">
+        <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>357</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>453</v>
+      </c>
+      <c r="H35" t="s">
+        <v>512</v>
+      </c>
+      <c r="I35" t="s">
+        <v>377</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
         <v>31</v>
       </c>
       <c r="E36" t="s">
-        <v>416</v>
+        <v>281</v>
       </c>
       <c r="F36" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="G36" t="s">
-        <v>358</v>
+        <v>457</v>
       </c>
       <c r="H36" t="s">
-        <v>184</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>513</v>
+      </c>
+      <c r="I36" t="s">
+        <v>381</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
       </c>
       <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>352</v>
+      </c>
+      <c r="F37" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" t="s">
+        <v>483</v>
+      </c>
+      <c r="H37" t="s">
+        <v>390</v>
+      </c>
+      <c r="I37" t="s">
+        <v>381</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="57">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
+        <v>332</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G38" t="s">
+        <v>469</v>
+      </c>
+      <c r="H38" t="s">
+        <v>401</v>
+      </c>
+      <c r="I38" t="s">
+        <v>381</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="57">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
+        <v>308</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G39" t="s">
+        <v>468</v>
+      </c>
+      <c r="H39" t="s">
+        <v>527</v>
+      </c>
+      <c r="I39" t="s">
+        <v>382</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>297</v>
+      </c>
+      <c r="F40" t="s">
+        <v>296</v>
+      </c>
+      <c r="G40" t="s">
+        <v>500</v>
+      </c>
+      <c r="H40" t="s">
+        <v>518</v>
+      </c>
+      <c r="I40" t="s">
+        <v>381</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s">
         <v>6</v>
       </c>
-      <c r="E37" t="s">
-        <v>414</v>
-      </c>
-      <c r="F37" s="1" t="s">
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>373</v>
+      </c>
+      <c r="F41" t="s">
+        <v>286</v>
+      </c>
+      <c r="G41" t="s">
+        <v>476</v>
+      </c>
+      <c r="H41" t="s">
+        <v>521</v>
+      </c>
+      <c r="I41" t="s">
+        <v>381</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="57">
+      <c r="A42" t="s">
+        <v>342</v>
+      </c>
+      <c r="B42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" t="s">
+        <v>263</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G37" t="s">
-        <v>352</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" t="s">
-        <v>212</v>
-      </c>
-      <c r="F38" t="s">
-        <v>213</v>
-      </c>
-      <c r="G38" t="s">
-        <v>375</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" t="s">
-        <v>208</v>
-      </c>
-      <c r="F39" t="s">
-        <v>209</v>
-      </c>
-      <c r="G39" t="s">
-        <v>353</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" t="s">
-        <v>318</v>
-      </c>
-      <c r="F40" t="s">
-        <v>203</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" t="s">
-        <v>201</v>
-      </c>
-      <c r="F41" t="s">
-        <v>210</v>
-      </c>
-      <c r="G41" t="s">
-        <v>359</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" t="s">
-        <v>333</v>
-      </c>
-      <c r="F42" t="s">
-        <v>238</v>
-      </c>
       <c r="G42" t="s">
-        <v>362</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>477</v>
+      </c>
+      <c r="H42" t="s">
+        <v>406</v>
+      </c>
+      <c r="I42" t="s">
+        <v>404</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>332</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>398</v>
+        <v>372</v>
+      </c>
+      <c r="F43" t="s">
+        <v>299</v>
       </c>
       <c r="G43" t="s">
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>509</v>
+      </c>
+      <c r="I43" t="s">
+        <v>381</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C44" t="s">
         <v>76</v>
@@ -2986,114 +3571,138 @@
         <v>31</v>
       </c>
       <c r="E44" t="s">
-        <v>315</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
+      </c>
+      <c r="F44" t="s">
+        <v>276</v>
       </c>
       <c r="G44" t="s">
-        <v>384</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>491</v>
+      </c>
+      <c r="H44" t="s">
+        <v>397</v>
+      </c>
+      <c r="I44" t="s">
+        <v>381</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>422</v>
+        <v>199</v>
       </c>
       <c r="F45" t="s">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="G45" t="s">
-        <v>376</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I45" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H45" t="s">
+        <v>514</v>
+      </c>
+      <c r="I45" t="s">
+        <v>382</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="57">
+      <c r="A46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" t="s">
+        <v>216</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G46" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" t="s">
-        <v>31</v>
-      </c>
-      <c r="E46" t="s">
-        <v>314</v>
-      </c>
-      <c r="F46" t="s">
-        <v>215</v>
-      </c>
-      <c r="G46" t="s">
-        <v>271</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="H46" t="s">
+        <v>523</v>
+      </c>
+      <c r="I46" t="s">
+        <v>404</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="E47" t="s">
-        <v>310</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>311</v>
+        <v>256</v>
+      </c>
+      <c r="F47" t="s">
+        <v>257</v>
       </c>
       <c r="G47" t="s">
-        <v>368</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>494</v>
+      </c>
+      <c r="H47" t="s">
+        <v>411</v>
+      </c>
+      <c r="I47" t="s">
+        <v>377</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="57">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
         <v>92</v>
@@ -3102,24 +3711,33 @@
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>309</v>
-      </c>
-      <c r="F48" t="s">
-        <v>308</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>314</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G48" t="s">
+        <v>459</v>
+      </c>
+      <c r="H48" t="s">
+        <v>515</v>
+      </c>
+      <c r="I48" t="s">
+        <v>381</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
         <v>92</v>
@@ -3128,532 +3746,780 @@
         <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="F49" t="s">
-        <v>308</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>290</v>
+      </c>
+      <c r="G49" t="s">
+        <v>461</v>
+      </c>
+      <c r="H49" t="s">
+        <v>528</v>
+      </c>
+      <c r="I49" t="s">
+        <v>381</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D50" t="s">
         <v>31</v>
       </c>
       <c r="E50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F50" t="s">
+        <v>274</v>
+      </c>
+      <c r="G50" t="s">
+        <v>472</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="I50" t="s">
+        <v>381</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
+        <v>34</v>
+      </c>
+      <c r="E51" t="s">
+        <v>330</v>
+      </c>
+      <c r="F51" t="s">
+        <v>237</v>
+      </c>
+      <c r="G51" t="s">
+        <v>495</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="I51" t="s">
+        <v>377</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E52" t="s">
+        <v>322</v>
+      </c>
+      <c r="F52" t="s">
+        <v>252</v>
+      </c>
+      <c r="G52" t="s">
+        <v>454</v>
+      </c>
+      <c r="H52" t="s">
         <v>424</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="G50" t="s">
-        <v>369</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="I52" t="s">
+        <v>404</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
         <v>34</v>
       </c>
-      <c r="C51" t="s">
-        <v>92</v>
-      </c>
-      <c r="D51" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51" t="s">
-        <v>335</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="E53" t="s">
+        <v>328</v>
+      </c>
+      <c r="F53" t="s">
         <v>221</v>
       </c>
-      <c r="G51" t="s">
-        <v>393</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="s">
-        <v>92</v>
-      </c>
-      <c r="D52" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" t="s">
-        <v>303</v>
-      </c>
-      <c r="F52" t="s">
-        <v>304</v>
-      </c>
-      <c r="G52" t="s">
-        <v>365</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" t="s">
-        <v>98</v>
-      </c>
-      <c r="B53" t="s">
-        <v>39</v>
-      </c>
-      <c r="C53" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" t="s">
-        <v>427</v>
-      </c>
-      <c r="F53" t="s">
-        <v>301</v>
-      </c>
       <c r="G53" t="s">
+        <v>456</v>
+      </c>
+      <c r="H53" t="s">
+        <v>415</v>
+      </c>
+      <c r="I53" t="s">
+        <v>381</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="57">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" t="s">
+        <v>329</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G54" t="s">
+        <v>470</v>
+      </c>
+      <c r="H54" t="s">
+        <v>526</v>
+      </c>
+      <c r="I54" t="s">
+        <v>381</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" t="s">
+        <v>323</v>
+      </c>
+      <c r="F55" t="s">
+        <v>251</v>
+      </c>
+      <c r="G55" t="s">
+        <v>466</v>
+      </c>
+      <c r="H55" t="s">
+        <v>529</v>
+      </c>
+      <c r="I55" t="s">
         <v>377</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54" t="s">
-        <v>100</v>
-      </c>
-      <c r="C54" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" t="s">
-        <v>299</v>
-      </c>
-      <c r="F54" t="s">
-        <v>298</v>
-      </c>
-      <c r="G54" t="s">
-        <v>346</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" t="s">
-        <v>101</v>
-      </c>
-      <c r="B55" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" t="s">
-        <v>92</v>
-      </c>
-      <c r="D55" t="s">
-        <v>31</v>
-      </c>
-      <c r="E55" t="s">
-        <v>317</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="G55" t="s">
-        <v>350</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="J55" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="F56" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="G56" t="s">
-        <v>355</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>489</v>
+      </c>
+      <c r="H56" t="s">
+        <v>386</v>
+      </c>
+      <c r="I56" t="s">
+        <v>377</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E57" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F57" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="G57" t="s">
-        <v>364</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>488</v>
+      </c>
+      <c r="H57" t="s">
+        <v>384</v>
+      </c>
+      <c r="I57" t="s">
+        <v>385</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>428</v>
+        <v>321</v>
       </c>
       <c r="F58" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="G58" t="s">
-        <v>353</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>482</v>
+      </c>
+      <c r="H58" t="s">
+        <v>387</v>
+      </c>
+      <c r="I58" t="s">
+        <v>377</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="42.75">
       <c r="A59" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E59" t="s">
         <v>320</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>235</v>
+      </c>
+      <c r="G59" t="s">
+        <v>498</v>
+      </c>
+      <c r="H59" t="s">
+        <v>383</v>
+      </c>
+      <c r="I59" t="s">
+        <v>382</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>108</v>
+        <v>339</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D60" t="s">
         <v>31</v>
       </c>
       <c r="E60" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
       <c r="F60" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="G60" t="s">
-        <v>363</v>
+        <v>499</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>378</v>
+      </c>
+      <c r="I60" t="s">
+        <v>377</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>429</v>
+        <v>340</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
         <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F61" t="s">
-        <v>308</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>277</v>
+      </c>
+      <c r="G61" t="s">
+        <v>474</v>
+      </c>
+      <c r="H61" t="s">
+        <v>388</v>
+      </c>
+      <c r="I61" t="s">
+        <v>381</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
       </c>
       <c r="D62" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>199</v>
+        <v>361</v>
       </c>
       <c r="F62" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>463</v>
+      </c>
+      <c r="H62" t="s">
+        <v>409</v>
+      </c>
+      <c r="I62" t="s">
+        <v>404</v>
+      </c>
+      <c r="J62" t="s">
+        <v>184</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D63" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" t="s">
+        <v>311</v>
+      </c>
+      <c r="F63" t="s">
+        <v>215</v>
+      </c>
+      <c r="G63" t="s">
+        <v>463</v>
+      </c>
+      <c r="H63" t="s">
+        <v>516</v>
+      </c>
+      <c r="I63" t="s">
+        <v>404</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>422</v>
+      </c>
+      <c r="B64" t="s">
+        <v>423</v>
+      </c>
+      <c r="C64" t="s">
         <v>5</v>
       </c>
-      <c r="D63" t="s">
-        <v>39</v>
-      </c>
-      <c r="E63" t="s">
-        <v>195</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G63" t="s">
-        <v>386</v>
-      </c>
-      <c r="H63" t="s">
-        <v>143</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>196</v>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>501</v>
+      </c>
+      <c r="F64" t="s">
+        <v>290</v>
+      </c>
+      <c r="G64" t="s">
+        <v>502</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="I64" t="s">
+        <v>381</v>
+      </c>
+      <c r="J64" t="s">
+        <v>530</v>
+      </c>
+      <c r="K64" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>418</v>
+      </c>
+      <c r="B65" t="s">
+        <v>417</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" t="s">
+        <v>437</v>
+      </c>
+      <c r="F65" t="s">
+        <v>438</v>
+      </c>
+      <c r="G65">
+        <v>155</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="I65" t="s">
+        <v>381</v>
+      </c>
+      <c r="J65" t="s">
+        <v>531</v>
+      </c>
+      <c r="K65" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>425</v>
+      </c>
+      <c r="B66" t="s">
+        <v>426</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66" t="s">
+        <v>507</v>
+      </c>
+      <c r="F66" t="s">
+        <v>505</v>
+      </c>
+      <c r="G66">
+        <v>117</v>
+      </c>
+      <c r="H66" t="s">
+        <v>506</v>
+      </c>
+      <c r="I66" t="s">
+        <v>381</v>
+      </c>
+      <c r="J66" t="s">
+        <v>532</v>
+      </c>
+      <c r="K66" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>429</v>
+      </c>
+      <c r="B67" t="s">
+        <v>430</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" t="s">
+        <v>291</v>
+      </c>
+      <c r="F67" t="s">
+        <v>290</v>
+      </c>
+      <c r="G67" t="s">
+        <v>508</v>
+      </c>
+      <c r="H67" t="s">
+        <v>510</v>
+      </c>
+      <c r="I67" t="s">
+        <v>377</v>
+      </c>
+      <c r="J67" t="s">
+        <v>163</v>
+      </c>
+      <c r="K67" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1">
-    <sortState ref="A2:I63">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A1:K1">
+    <sortState ref="A2:K67">
+      <sortCondition ref="J1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H61" r:id="rId1"/>
-    <hyperlink ref="H47" r:id="rId2"/>
-    <hyperlink ref="H51" r:id="rId3"/>
-    <hyperlink ref="H29" r:id="rId4"/>
-    <hyperlink ref="H20" r:id="rId5"/>
-    <hyperlink ref="H22" r:id="rId6"/>
-    <hyperlink ref="H50" r:id="rId7"/>
-    <hyperlink ref="H17" r:id="rId8"/>
-    <hyperlink ref="H49" r:id="rId9"/>
-    <hyperlink ref="H48" r:id="rId10"/>
-    <hyperlink ref="H38" r:id="rId11"/>
-    <hyperlink ref="H16" r:id="rId12"/>
-    <hyperlink ref="H15" r:id="rId13"/>
-    <hyperlink ref="H24" r:id="rId14"/>
-    <hyperlink ref="H27" r:id="rId15"/>
-    <hyperlink ref="H53" r:id="rId16"/>
-    <hyperlink ref="H23" r:id="rId17"/>
-    <hyperlink ref="H32" r:id="rId18"/>
-    <hyperlink ref="H52" r:id="rId19"/>
-    <hyperlink ref="H41" r:id="rId20"/>
-    <hyperlink ref="H40" r:id="rId21"/>
-    <hyperlink ref="H21" r:id="rId22"/>
-    <hyperlink ref="H9" r:id="rId23"/>
-    <hyperlink ref="H30" r:id="rId24"/>
-    <hyperlink ref="H59" r:id="rId25"/>
-    <hyperlink ref="H37" r:id="rId26"/>
-    <hyperlink ref="H25" r:id="rId27"/>
-    <hyperlink ref="H5" r:id="rId28"/>
-    <hyperlink ref="H58" r:id="rId29"/>
-    <hyperlink ref="H57" r:id="rId30"/>
-    <hyperlink ref="H3" r:id="rId31"/>
-    <hyperlink ref="H14" r:id="rId32"/>
-    <hyperlink ref="H56" r:id="rId33"/>
-    <hyperlink ref="H55" r:id="rId34"/>
-    <hyperlink ref="H54" r:id="rId35"/>
-    <hyperlink ref="H18" r:id="rId36"/>
-    <hyperlink ref="H46" r:id="rId37"/>
-    <hyperlink ref="H45" r:id="rId38"/>
-    <hyperlink ref="H31" r:id="rId39"/>
-    <hyperlink ref="H13" r:id="rId40"/>
-    <hyperlink ref="H44" r:id="rId41"/>
-    <hyperlink ref="H12" r:id="rId42"/>
-    <hyperlink ref="H2" r:id="rId43"/>
-    <hyperlink ref="H28" r:id="rId44"/>
-    <hyperlink ref="H26" r:id="rId45"/>
-    <hyperlink ref="H19" r:id="rId46"/>
-    <hyperlink ref="H60" r:id="rId47"/>
-    <hyperlink ref="H34" r:id="rId48"/>
-    <hyperlink ref="H35" r:id="rId49"/>
-    <hyperlink ref="H62" r:id="rId50"/>
-    <hyperlink ref="H10" r:id="rId51" location="texto"/>
-    <hyperlink ref="H42" r:id="rId52"/>
-    <hyperlink ref="H43" r:id="rId53"/>
-    <hyperlink ref="H33" r:id="rId54"/>
-    <hyperlink ref="H39" r:id="rId55"/>
-    <hyperlink ref="H4" r:id="rId56"/>
-    <hyperlink ref="H8" r:id="rId57"/>
-    <hyperlink ref="H11" r:id="rId58"/>
-    <hyperlink ref="H6" r:id="rId59"/>
-    <hyperlink ref="H7" r:id="rId60"/>
-    <hyperlink ref="I46" r:id="rId61"/>
-    <hyperlink ref="I41" r:id="rId62"/>
-    <hyperlink ref="I40" r:id="rId63"/>
-    <hyperlink ref="I39" r:id="rId64"/>
-    <hyperlink ref="I37" r:id="rId65"/>
-    <hyperlink ref="I36" r:id="rId66"/>
-    <hyperlink ref="I35" r:id="rId67"/>
-    <hyperlink ref="I34" r:id="rId68"/>
-    <hyperlink ref="I32" r:id="rId69"/>
-    <hyperlink ref="I14" r:id="rId70"/>
-    <hyperlink ref="I5" r:id="rId71"/>
-    <hyperlink ref="I4" r:id="rId72"/>
-    <hyperlink ref="I42" r:id="rId73"/>
-    <hyperlink ref="I33" r:id="rId74"/>
-    <hyperlink ref="I17" r:id="rId75"/>
-    <hyperlink ref="I11" r:id="rId76"/>
-    <hyperlink ref="I10" r:id="rId77"/>
-    <hyperlink ref="I9" r:id="rId78"/>
-    <hyperlink ref="I8" r:id="rId79"/>
-    <hyperlink ref="I7" r:id="rId80"/>
-    <hyperlink ref="I19" r:id="rId81"/>
-    <hyperlink ref="I30" r:id="rId82"/>
-    <hyperlink ref="I28" r:id="rId83"/>
-    <hyperlink ref="I27" r:id="rId84"/>
-    <hyperlink ref="I26" r:id="rId85"/>
-    <hyperlink ref="I25" r:id="rId86"/>
-    <hyperlink ref="I44" r:id="rId87"/>
-    <hyperlink ref="I31" r:id="rId88"/>
-    <hyperlink ref="I18" r:id="rId89"/>
-    <hyperlink ref="I2" r:id="rId90"/>
-    <hyperlink ref="I63" r:id="rId91" display="http://www.loteriamineira.mg.gov.br"/>
-    <hyperlink ref="I62" r:id="rId92" display="http://www.jucemg.mg.gov.br"/>
-    <hyperlink ref="I23" r:id="rId93" display="http://www.gabinetemilitar.mg.gov.br"/>
-    <hyperlink ref="I60" r:id="rId94"/>
-    <hyperlink ref="I59" r:id="rId95"/>
-    <hyperlink ref="I58" r:id="rId96"/>
-    <hyperlink ref="I57" r:id="rId97"/>
-    <hyperlink ref="I56" r:id="rId98"/>
-    <hyperlink ref="I55" r:id="rId99"/>
-    <hyperlink ref="I54" r:id="rId100"/>
-    <hyperlink ref="I53" r:id="rId101"/>
-    <hyperlink ref="I52" r:id="rId102"/>
-    <hyperlink ref="I61" r:id="rId103"/>
-    <hyperlink ref="I24" r:id="rId104"/>
-    <hyperlink ref="I45" r:id="rId105"/>
+    <hyperlink ref="J31" r:id="rId1"/>
+    <hyperlink ref="J39" r:id="rId2"/>
+    <hyperlink ref="J38" r:id="rId3"/>
+    <hyperlink ref="J21" r:id="rId4"/>
+    <hyperlink ref="J9" r:id="rId5"/>
+    <hyperlink ref="J22" r:id="rId6"/>
+    <hyperlink ref="J33" r:id="rId7"/>
+    <hyperlink ref="J7" r:id="rId8"/>
+    <hyperlink ref="J32" r:id="rId9"/>
+    <hyperlink ref="J29" r:id="rId10"/>
+    <hyperlink ref="J10" r:id="rId11"/>
+    <hyperlink ref="J27" r:id="rId12"/>
+    <hyperlink ref="J5" r:id="rId13"/>
+    <hyperlink ref="J14" r:id="rId14"/>
+    <hyperlink ref="J19" r:id="rId15"/>
+    <hyperlink ref="J43" r:id="rId16"/>
+    <hyperlink ref="J12" r:id="rId17"/>
+    <hyperlink ref="J8" r:id="rId18"/>
+    <hyperlink ref="J35" r:id="rId19"/>
+    <hyperlink ref="J18" r:id="rId20"/>
+    <hyperlink ref="J6" r:id="rId21"/>
+    <hyperlink ref="J24" r:id="rId22"/>
+    <hyperlink ref="J57" r:id="rId23"/>
+    <hyperlink ref="J13" r:id="rId24"/>
+    <hyperlink ref="J30" r:id="rId25"/>
+    <hyperlink ref="J16" r:id="rId26"/>
+    <hyperlink ref="J42" r:id="rId27"/>
+    <hyperlink ref="J15" r:id="rId28"/>
+    <hyperlink ref="J41" r:id="rId29"/>
+    <hyperlink ref="J34" r:id="rId30"/>
+    <hyperlink ref="J23" r:id="rId31"/>
+    <hyperlink ref="J37" r:id="rId32"/>
+    <hyperlink ref="J49" r:id="rId33"/>
+    <hyperlink ref="J48" r:id="rId34"/>
+    <hyperlink ref="J40" r:id="rId35"/>
+    <hyperlink ref="J44" r:id="rId36"/>
+    <hyperlink ref="J63" r:id="rId37"/>
+    <hyperlink ref="J3" r:id="rId38"/>
+    <hyperlink ref="J50" r:id="rId39"/>
+    <hyperlink ref="J2" r:id="rId40"/>
+    <hyperlink ref="J28" r:id="rId41"/>
+    <hyperlink ref="J61" r:id="rId42"/>
+    <hyperlink ref="J60" r:id="rId43"/>
+    <hyperlink ref="J47" r:id="rId44"/>
+    <hyperlink ref="J20" r:id="rId45"/>
+    <hyperlink ref="J25" r:id="rId46"/>
+    <hyperlink ref="J36" r:id="rId47"/>
+    <hyperlink ref="J17" r:id="rId48"/>
+    <hyperlink ref="J46" r:id="rId49"/>
+    <hyperlink ref="J45" r:id="rId50"/>
+    <hyperlink ref="J56" r:id="rId51" location="texto"/>
+    <hyperlink ref="J51" r:id="rId52"/>
+    <hyperlink ref="J54" r:id="rId53"/>
+    <hyperlink ref="J53" r:id="rId54"/>
+    <hyperlink ref="J11" r:id="rId55"/>
+    <hyperlink ref="J26" r:id="rId56"/>
+    <hyperlink ref="J55" r:id="rId57"/>
+    <hyperlink ref="J58" r:id="rId58"/>
+    <hyperlink ref="J59" r:id="rId59"/>
+    <hyperlink ref="J52" r:id="rId60"/>
+    <hyperlink ref="K63" r:id="rId61"/>
+    <hyperlink ref="K6" r:id="rId62"/>
+    <hyperlink ref="K11" r:id="rId63"/>
+    <hyperlink ref="K16" r:id="rId64"/>
+    <hyperlink ref="K62" r:id="rId65"/>
+    <hyperlink ref="K46" r:id="rId66"/>
+    <hyperlink ref="K17" r:id="rId67"/>
+    <hyperlink ref="K8" r:id="rId68"/>
+    <hyperlink ref="K37" r:id="rId69"/>
+    <hyperlink ref="K15" r:id="rId70"/>
+    <hyperlink ref="K26" r:id="rId71"/>
+    <hyperlink ref="K51" r:id="rId72"/>
+    <hyperlink ref="K53" r:id="rId73"/>
+    <hyperlink ref="K7" r:id="rId74"/>
+    <hyperlink ref="K58" r:id="rId75"/>
+    <hyperlink ref="K56" r:id="rId76"/>
+    <hyperlink ref="K57" r:id="rId77"/>
+    <hyperlink ref="K55" r:id="rId78"/>
+    <hyperlink ref="K52" r:id="rId79"/>
+    <hyperlink ref="K25" r:id="rId80"/>
+    <hyperlink ref="K13" r:id="rId81"/>
+    <hyperlink ref="K47" r:id="rId82"/>
+    <hyperlink ref="K19" r:id="rId83"/>
+    <hyperlink ref="K20" r:id="rId84"/>
+    <hyperlink ref="K42" r:id="rId85"/>
+    <hyperlink ref="K28" r:id="rId86"/>
+    <hyperlink ref="K50" r:id="rId87"/>
+    <hyperlink ref="K60" r:id="rId88"/>
+    <hyperlink ref="K4" r:id="rId89" display="http://www.loteriamineira.mg.gov.br"/>
+    <hyperlink ref="K45" r:id="rId90" display="http://www.jucemg.mg.gov.br"/>
+    <hyperlink ref="K12" r:id="rId91" display="http://www.gabinetemilitar.mg.gov.br"/>
+    <hyperlink ref="K36" r:id="rId92"/>
+    <hyperlink ref="K30" r:id="rId93"/>
+    <hyperlink ref="K41" r:id="rId94"/>
+    <hyperlink ref="K34" r:id="rId95"/>
+    <hyperlink ref="K49" r:id="rId96"/>
+    <hyperlink ref="K48" r:id="rId97"/>
+    <hyperlink ref="K40" r:id="rId98"/>
+    <hyperlink ref="K43" r:id="rId99"/>
+    <hyperlink ref="K35" r:id="rId100"/>
+    <hyperlink ref="K31" r:id="rId101"/>
+    <hyperlink ref="K14" r:id="rId102"/>
+    <hyperlink ref="K3" r:id="rId103"/>
+    <hyperlink ref="H60" r:id="rId104"/>
+    <hyperlink ref="H26" r:id="rId105"/>
+    <hyperlink ref="H27" r:id="rId106"/>
+    <hyperlink ref="H22" r:id="rId107"/>
+    <hyperlink ref="H19" r:id="rId108"/>
+    <hyperlink ref="H13" r:id="rId109"/>
+    <hyperlink ref="H51" r:id="rId110"/>
+    <hyperlink ref="H64" r:id="rId111"/>
+    <hyperlink ref="H43" r:id="rId112"/>
+    <hyperlink ref="H18" r:id="rId113"/>
+    <hyperlink ref="K18" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId106"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId115"/>
 </worksheet>
 </file>
--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_estrutura_organizacional\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1166,9 +1166,6 @@
     <t>Secretaria Geral do Estado de Minas Gerais</t>
   </si>
   <si>
-    <t>e-mail</t>
-  </si>
-  <si>
     <t>horario_atendimento</t>
   </si>
   <si>
@@ -1644,6 +1641,9 @@
   </si>
   <si>
     <t>www.loteriamineira.com.br/fale-conosco</t>
+  </si>
+  <si>
+    <t>email</t>
   </si>
 </sst>
 </file>
@@ -2075,10 +2075,10 @@
         <v>193</v>
       </c>
       <c r="H1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I1" t="s">
         <v>375</v>
-      </c>
-      <c r="I1" t="s">
-        <v>376</v>
       </c>
       <c r="J1" t="s">
         <v>128</v>
@@ -2107,13 +2107,13 @@
         <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>170</v>
@@ -2142,13 +2142,13 @@
         <v>270</v>
       </c>
       <c r="G3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>168</v>
@@ -2177,13 +2177,13 @@
         <v>197</v>
       </c>
       <c r="G4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J4" t="s">
         <v>143</v>
@@ -2212,13 +2212,13 @@
         <v>242</v>
       </c>
       <c r="G5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>142</v>
@@ -2247,13 +2247,13 @@
         <v>203</v>
       </c>
       <c r="G6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>151</v>
@@ -2282,13 +2282,13 @@
         <v>240</v>
       </c>
       <c r="G7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>137</v>
@@ -2320,10 +2320,10 @@
         <v>337</v>
       </c>
       <c r="H8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>148</v>
@@ -2352,13 +2352,13 @@
         <v>269</v>
       </c>
       <c r="G9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>134</v>
@@ -2387,13 +2387,13 @@
         <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>140</v>
@@ -2422,13 +2422,13 @@
         <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>185</v>
@@ -2457,13 +2457,13 @@
         <v>266</v>
       </c>
       <c r="G12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>147</v>
@@ -2492,13 +2492,13 @@
         <v>255</v>
       </c>
       <c r="G13" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>154</v>
@@ -2527,13 +2527,13 @@
         <v>251</v>
       </c>
       <c r="G14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>144</v>
@@ -2562,13 +2562,13 @@
         <v>231</v>
       </c>
       <c r="G15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>158</v>
@@ -2597,13 +2597,13 @@
         <v>209</v>
       </c>
       <c r="G16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>156</v>
@@ -2632,13 +2632,13 @@
         <v>218</v>
       </c>
       <c r="G17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>178</v>
@@ -2667,13 +2667,13 @@
         <v>210</v>
       </c>
       <c r="G18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>150</v>
@@ -2702,13 +2702,13 @@
         <v>259</v>
       </c>
       <c r="G19" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I19" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>145</v>
@@ -2737,13 +2737,13 @@
         <v>261</v>
       </c>
       <c r="G20" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H20" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>175</v>
@@ -2772,13 +2772,13 @@
         <v>254</v>
       </c>
       <c r="G21" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>133</v>
@@ -2807,13 +2807,13 @@
         <v>267</v>
       </c>
       <c r="G22" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>135</v>
@@ -2842,13 +2842,13 @@
         <v>210</v>
       </c>
       <c r="G23" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H23" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>161</v>
@@ -2877,13 +2877,13 @@
         <v>268</v>
       </c>
       <c r="G24" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H24" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>152</v>
@@ -2912,13 +2912,13 @@
         <v>253</v>
       </c>
       <c r="G25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H25" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I25" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>176</v>
@@ -2950,10 +2950,10 @@
         <v>336</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I26" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>186</v>
@@ -2982,13 +2982,13 @@
         <v>241</v>
       </c>
       <c r="G27" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>141</v>
@@ -3017,13 +3017,13 @@
         <v>277</v>
       </c>
       <c r="G28" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H28" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>171</v>
@@ -3052,13 +3052,13 @@
         <v>306</v>
       </c>
       <c r="G29" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H29" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>139</v>
@@ -3087,13 +3087,13 @@
         <v>344</v>
       </c>
       <c r="G30" t="s">
+        <v>442</v>
+      </c>
+      <c r="H30" t="s">
         <v>443</v>
       </c>
-      <c r="H30" t="s">
-        <v>444</v>
-      </c>
       <c r="I30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>155</v>
@@ -3116,19 +3116,19 @@
         <v>31</v>
       </c>
       <c r="E31" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F31" t="s">
         <v>306</v>
       </c>
       <c r="G31" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H31" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>130</v>
@@ -3157,13 +3157,13 @@
         <v>306</v>
       </c>
       <c r="G32" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H32" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>138</v>
@@ -3192,13 +3192,13 @@
         <v>303</v>
       </c>
       <c r="G33" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H33" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I33" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>136</v>
@@ -3227,13 +3227,13 @@
         <v>289</v>
       </c>
       <c r="G34" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H34" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I34" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>160</v>
@@ -3262,13 +3262,13 @@
         <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H35" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I35" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>149</v>
@@ -3297,13 +3297,13 @@
         <v>282</v>
       </c>
       <c r="G36" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H36" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>177</v>
@@ -3332,13 +3332,13 @@
         <v>228</v>
       </c>
       <c r="G37" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H37" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>162</v>
@@ -3367,13 +3367,13 @@
         <v>221</v>
       </c>
       <c r="G38" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H38" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>132</v>
@@ -3402,13 +3402,13 @@
         <v>309</v>
       </c>
       <c r="G39" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H39" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I39" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>131</v>
@@ -3437,13 +3437,13 @@
         <v>296</v>
       </c>
       <c r="G40" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H40" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I40" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>165</v>
@@ -3472,13 +3472,13 @@
         <v>286</v>
       </c>
       <c r="G41" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H41" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>159</v>
@@ -3507,13 +3507,13 @@
         <v>209</v>
       </c>
       <c r="G42" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H42" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>157</v>
@@ -3542,13 +3542,13 @@
         <v>299</v>
       </c>
       <c r="G43" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>146</v>
@@ -3577,19 +3577,19 @@
         <v>276</v>
       </c>
       <c r="G44" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I44" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>166</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3612,13 +3612,13 @@
         <v>211</v>
       </c>
       <c r="G45" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I45" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>180</v>
@@ -3650,10 +3650,10 @@
         <v>338</v>
       </c>
       <c r="H46" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I46" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>179</v>
@@ -3682,13 +3682,13 @@
         <v>257</v>
       </c>
       <c r="G47" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H47" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>174</v>
@@ -3717,13 +3717,13 @@
         <v>294</v>
       </c>
       <c r="G48" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H48" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I48" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>164</v>
@@ -3752,13 +3752,13 @@
         <v>290</v>
       </c>
       <c r="G49" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H49" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I49" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>163</v>
@@ -3787,13 +3787,13 @@
         <v>274</v>
       </c>
       <c r="G50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>169</v>
@@ -3822,13 +3822,13 @@
         <v>237</v>
       </c>
       <c r="G51" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I51" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>182</v>
@@ -3857,13 +3857,13 @@
         <v>252</v>
       </c>
       <c r="G52" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H52" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I52" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>189</v>
@@ -3892,13 +3892,13 @@
         <v>221</v>
       </c>
       <c r="G53" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H53" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I53" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>183</v>
@@ -3927,13 +3927,13 @@
         <v>343</v>
       </c>
       <c r="G54" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H54" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I54" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>183</v>
@@ -3962,13 +3962,13 @@
         <v>251</v>
       </c>
       <c r="G55" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H55" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>187</v>
@@ -3997,13 +3997,13 @@
         <v>248</v>
       </c>
       <c r="G56" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H56" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I56" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>181</v>
@@ -4032,13 +4032,13 @@
         <v>249</v>
       </c>
       <c r="G57" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H57" t="s">
+        <v>383</v>
+      </c>
+      <c r="I57" t="s">
         <v>384</v>
-      </c>
-      <c r="I57" t="s">
-        <v>385</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>153</v>
@@ -4067,13 +4067,13 @@
         <v>246</v>
       </c>
       <c r="G58" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H58" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I58" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>188</v>
@@ -4102,13 +4102,13 @@
         <v>235</v>
       </c>
       <c r="G59" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H59" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>190</v>
@@ -4137,13 +4137,13 @@
         <v>279</v>
       </c>
       <c r="G60" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I60" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>173</v>
@@ -4172,13 +4172,13 @@
         <v>277</v>
       </c>
       <c r="G61" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H61" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I61" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>172</v>
@@ -4207,13 +4207,13 @@
         <v>215</v>
       </c>
       <c r="G62" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H62" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I62" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J62" t="s">
         <v>184</v>
@@ -4242,13 +4242,13 @@
         <v>215</v>
       </c>
       <c r="G63" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H63" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I63" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>167</v>
@@ -4259,10 +4259,10 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
+        <v>421</v>
+      </c>
+      <c r="B64" t="s">
         <v>422</v>
-      </c>
-      <c r="B64" t="s">
-        <v>423</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -4271,33 +4271,33 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F64" t="s">
         <v>290</v>
       </c>
       <c r="G64" t="s">
+        <v>501</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="I64" t="s">
+        <v>380</v>
+      </c>
+      <c r="J64" t="s">
+        <v>529</v>
+      </c>
+      <c r="K64" t="s">
         <v>503</v>
-      </c>
-      <c r="I64" t="s">
-        <v>381</v>
-      </c>
-      <c r="J64" t="s">
-        <v>530</v>
-      </c>
-      <c r="K64" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B65" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -4306,33 +4306,33 @@
         <v>26</v>
       </c>
       <c r="E65" t="s">
+        <v>436</v>
+      </c>
+      <c r="F65" t="s">
         <v>437</v>
-      </c>
-      <c r="F65" t="s">
-        <v>438</v>
       </c>
       <c r="G65">
         <v>155</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I65" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J65" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K65" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
+        <v>424</v>
+      </c>
+      <c r="B66" t="s">
         <v>425</v>
-      </c>
-      <c r="B66" t="s">
-        <v>426</v>
       </c>
       <c r="C66" t="s">
         <v>44</v>
@@ -4341,33 +4341,33 @@
         <v>34</v>
       </c>
       <c r="E66" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G66">
         <v>117</v>
       </c>
       <c r="H66" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I66" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J66" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K66" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
+        <v>428</v>
+      </c>
+      <c r="B67" t="s">
         <v>429</v>
-      </c>
-      <c r="B67" t="s">
-        <v>430</v>
       </c>
       <c r="C67" t="s">
         <v>44</v>
@@ -4382,13 +4382,13 @@
         <v>290</v>
       </c>
       <c r="G67" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H67" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I67" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J67" t="s">
         <v>163</v>

--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_estrutura_organizacional\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32525654-30D1-4A89-BCC6-DF0F6C065072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -22,17 +23,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -931,9 +921,6 @@
     <t>6º e 7º andar do Edifício Minas - Cidade Administrativa, Belo Horizonte</t>
   </si>
   <si>
-    <t>Luiz Claudio Fernandes Lourenço Gomes</t>
-  </si>
-  <si>
     <t>http://www.educacao.mg.gov.br</t>
   </si>
   <si>
@@ -955,9 +942,6 @@
     <t>https://www.comunicacao.mg.gov.br/</t>
   </si>
   <si>
-    <t>Bernardo Assis Fonseca Santos</t>
-  </si>
-  <si>
     <t>4º andar do Palácio Tiradentes - Cidade Administrativa, Belo Horizonte</t>
   </si>
   <si>
@@ -982,21 +966,12 @@
     <t>Luciana Lopes Nominato Braga</t>
   </si>
   <si>
-    <t>Marcelo Guilherme de Aro Ferreira</t>
-  </si>
-  <si>
     <t>Patrícia Vinte di Iorio</t>
   </si>
   <si>
-    <t>Sérgio Rodrigues Reis</t>
-  </si>
-  <si>
     <t>Silvia Caroline Listgasten Dias</t>
   </si>
   <si>
-    <t>Wirley Rodrigues Reis</t>
-  </si>
-  <si>
     <t>Marcela Oliveira Ferreira Dias</t>
   </si>
   <si>
@@ -1009,25 +984,10 @@
     <t>Luísa Cardoso Barreto</t>
   </si>
   <si>
-    <t>Márcio Almeida Bernardino</t>
-  </si>
-  <si>
-    <t>Otávio Martins Maia</t>
-  </si>
-  <si>
-    <t>Gustavo Mendicino de Oliveira</t>
-  </si>
-  <si>
     <t>Nilda de Fátima Ferreira Soares</t>
   </si>
   <si>
     <t>Carlos Alberto Arruda de Oliveira</t>
-  </si>
-  <si>
-    <t>Rodrigo Tavares</t>
-  </si>
-  <si>
-    <t>Weverton Vilas Boas de Castro</t>
   </si>
   <si>
     <t>Camila Barbosa Neves</t>
@@ -1148,18 +1108,12 @@
     <t>https://www.cultura.mg.gov.br/</t>
   </si>
   <si>
-    <t>Bárbara Barros Botega</t>
-  </si>
-  <si>
     <t>https://www.casacivil.mg.gov.br/</t>
   </si>
   <si>
     <t>https://www.mg.gov.br/agricultura</t>
   </si>
   <si>
-    <t>Rossieli Soares da Silva</t>
-  </si>
-  <si>
     <t>Lyssandro Norton Siqueira</t>
   </si>
   <si>
@@ -1644,13 +1598,49 @@
   </si>
   <si>
     <t>email</t>
+  </si>
+  <si>
+    <t>Cláudio Augusto Bortolini</t>
+  </si>
+  <si>
+    <t>Ike Yagelovic</t>
+  </si>
+  <si>
+    <t>Yuri Mesquita</t>
+  </si>
+  <si>
+    <t>Rodrigo César Câmara Baia</t>
+  </si>
+  <si>
+    <t>Cássia Amorim Ximenes de Souza</t>
+  </si>
+  <si>
+    <t>Leônidas Oliveira</t>
+  </si>
+  <si>
+    <t>Luciana Mundim de Mattos Paixão</t>
+  </si>
+  <si>
+    <t>Gustavo Braga</t>
+  </si>
+  <si>
+    <t>Castellar Modesto Guimarães Neto</t>
+  </si>
+  <si>
+    <t>Milena Pedrosa</t>
+  </si>
+  <si>
+    <t>Gustavo Fonseca Nogueira</t>
+  </si>
+  <si>
+    <t>Zezinho Andrada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2035,24 +2025,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K67"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.625" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.25" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="49.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2075,10 +2065,10 @@
         <v>193</v>
       </c>
       <c r="H1" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="I1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="J1" t="s">
         <v>128</v>
@@ -2087,7 +2077,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -2101,28 +2091,28 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F2" t="s">
         <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="H2" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="I2" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>170</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -2136,28 +2126,28 @@
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="F3" t="s">
         <v>270</v>
       </c>
       <c r="G3" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="H3" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="I3" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>168</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="57">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -2177,13 +2167,13 @@
         <v>197</v>
       </c>
       <c r="G4" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="H4" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="I4" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="J4" t="s">
         <v>143</v>
@@ -2192,7 +2182,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -2206,28 +2196,28 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>324</v>
+        <v>523</v>
       </c>
       <c r="F5" t="s">
         <v>242</v>
       </c>
       <c r="G5" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="H5" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="I5" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>142</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -2241,19 +2231,19 @@
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F6" t="s">
         <v>203</v>
       </c>
       <c r="G6" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="H6" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="I6" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>151</v>
@@ -2262,7 +2252,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -2276,19 +2266,19 @@
         <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>325</v>
+        <v>524</v>
       </c>
       <c r="F7" t="s">
         <v>240</v>
       </c>
       <c r="G7" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="H7" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="I7" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>137</v>
@@ -2297,7 +2287,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2317,13 +2307,13 @@
         <v>221</v>
       </c>
       <c r="G8" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="H8" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="I8" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>148</v>
@@ -2332,7 +2322,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -2346,28 +2336,28 @@
         <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>316</v>
+        <v>525</v>
       </c>
       <c r="F9" t="s">
         <v>269</v>
       </c>
       <c r="G9" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="H9" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="I9" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>134</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2387,22 +2377,22 @@
         <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="H10" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="I10" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>140</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2422,13 +2412,13 @@
         <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="H11" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="I11" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>185</v>
@@ -2437,7 +2427,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -2451,19 +2441,19 @@
         <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F12" t="s">
         <v>266</v>
       </c>
       <c r="G12" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="H12" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="I12" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>147</v>
@@ -2472,7 +2462,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>118</v>
       </c>
@@ -2486,19 +2476,19 @@
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F13" t="s">
         <v>255</v>
       </c>
       <c r="G13" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="I13" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>154</v>
@@ -2507,7 +2497,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>120</v>
       </c>
@@ -2527,27 +2517,27 @@
         <v>251</v>
       </c>
       <c r="G14" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="H14" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="I14" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>144</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="28.5">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2562,13 +2552,13 @@
         <v>231</v>
       </c>
       <c r="G15" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="H15" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="I15" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>158</v>
@@ -2577,7 +2567,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="57">
+    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2591,19 +2581,19 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G16" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="H16" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="I16" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>156</v>
@@ -2612,7 +2602,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="57">
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2632,13 +2622,13 @@
         <v>218</v>
       </c>
       <c r="G17" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="H17" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="I17" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>178</v>
@@ -2647,7 +2637,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -2667,13 +2657,13 @@
         <v>210</v>
       </c>
       <c r="G18" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="I18" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>150</v>
@@ -2682,7 +2672,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>114</v>
       </c>
@@ -2702,13 +2692,13 @@
         <v>259</v>
       </c>
       <c r="G19" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="I19" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>145</v>
@@ -2717,7 +2707,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>122</v>
       </c>
@@ -2737,13 +2727,13 @@
         <v>261</v>
       </c>
       <c r="G20" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="H20" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="I20" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>175</v>
@@ -2752,9 +2742,9 @@
         <v>226</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="28.5">
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B21" t="s">
         <v>74</v>
@@ -2766,28 +2756,28 @@
         <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F21" t="s">
         <v>254</v>
       </c>
       <c r="G21" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="H21" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="I21" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>133</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -2801,28 +2791,28 @@
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>318</v>
+        <v>526</v>
       </c>
       <c r="F22" t="s">
         <v>267</v>
       </c>
       <c r="G22" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="I22" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>135</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2836,28 +2826,28 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="F23" t="s">
         <v>210</v>
       </c>
       <c r="G23" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="H23" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="I23" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>161</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -2871,28 +2861,28 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="F24" t="s">
         <v>268</v>
       </c>
       <c r="G24" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="H24" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="I24" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>152</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -2906,19 +2896,19 @@
         <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F25" t="s">
         <v>253</v>
       </c>
       <c r="G25" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="H25" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="I25" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>176</v>
@@ -2927,7 +2917,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="57">
+    <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
@@ -2947,13 +2937,13 @@
         <v>234</v>
       </c>
       <c r="G26" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="I26" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>186</v>
@@ -2962,7 +2952,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -2976,28 +2966,28 @@
         <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F27" t="s">
         <v>241</v>
       </c>
       <c r="G27" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I27" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>141</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="57">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -3011,19 +3001,19 @@
         <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>277</v>
       </c>
       <c r="G28" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="H28" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="I28" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>171</v>
@@ -3032,7 +3022,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -3046,28 +3036,28 @@
         <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F29" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G29" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="H29" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="I29" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>139</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="57">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -3081,19 +3071,19 @@
         <v>31</v>
       </c>
       <c r="E30" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G30" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="H30" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="I30" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>155</v>
@@ -3102,9 +3092,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B31" t="s">
         <v>110</v>
@@ -3116,28 +3106,28 @@
         <v>31</v>
       </c>
       <c r="E31" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="F31" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G31" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="H31" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="I31" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>130</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -3151,28 +3141,28 @@
         <v>31</v>
       </c>
       <c r="E32" t="s">
-        <v>305</v>
+        <v>527</v>
       </c>
       <c r="F32" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G32" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="H32" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="I32" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>138</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="57">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -3186,28 +3176,28 @@
         <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>369</v>
+        <v>528</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G33" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="H33" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="I33" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>136</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>104</v>
       </c>
@@ -3227,13 +3217,13 @@
         <v>289</v>
       </c>
       <c r="G34" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="H34" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="I34" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>160</v>
@@ -3242,7 +3232,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>97</v>
       </c>
@@ -3256,28 +3246,28 @@
         <v>31</v>
       </c>
       <c r="E35" t="s">
+        <v>300</v>
+      </c>
+      <c r="F35" t="s">
         <v>301</v>
       </c>
-      <c r="F35" t="s">
-        <v>302</v>
-      </c>
       <c r="G35" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="H35" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="I35" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>149</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>108</v>
       </c>
@@ -3297,13 +3287,13 @@
         <v>282</v>
       </c>
       <c r="G36" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="H36" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I36" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>177</v>
@@ -3312,7 +3302,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -3326,19 +3316,19 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F37" t="s">
         <v>228</v>
       </c>
       <c r="G37" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="H37" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="I37" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>162</v>
@@ -3347,7 +3337,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="57">
+    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>96</v>
       </c>
@@ -3361,28 +3351,28 @@
         <v>31</v>
       </c>
       <c r="E38" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>221</v>
       </c>
       <c r="G38" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="H38" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="I38" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>132</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="57">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>93</v>
       </c>
@@ -3396,28 +3386,28 @@
         <v>31</v>
       </c>
       <c r="E39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G39" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="H39" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="I39" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>131</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>99</v>
       </c>
@@ -3431,19 +3421,19 @@
         <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>297</v>
+        <v>529</v>
       </c>
       <c r="F40" t="s">
         <v>296</v>
       </c>
       <c r="G40" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="H40" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="I40" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>165</v>
@@ -3452,7 +3442,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>106</v>
       </c>
@@ -3466,19 +3456,19 @@
         <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="F41" t="s">
         <v>286</v>
       </c>
       <c r="G41" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="H41" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="I41" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>159</v>
@@ -3487,9 +3477,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="57">
+    <row r="42" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s">
         <v>113</v>
@@ -3507,13 +3497,13 @@
         <v>209</v>
       </c>
       <c r="G42" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="H42" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="I42" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>157</v>
@@ -3522,7 +3512,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -3536,28 +3526,28 @@
         <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>372</v>
+        <v>530</v>
       </c>
       <c r="F43" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G43" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="I43" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>146</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -3577,22 +3567,22 @@
         <v>276</v>
       </c>
       <c r="G44" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="H44" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="I44" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>166</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -3612,13 +3602,13 @@
         <v>211</v>
       </c>
       <c r="G45" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="H45" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="I45" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>180</v>
@@ -3627,7 +3617,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="57">
+    <row r="46" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -3644,16 +3634,16 @@
         <v>216</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="G46" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H46" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="I46" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>179</v>
@@ -3662,7 +3652,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>116</v>
       </c>
@@ -3682,13 +3672,13 @@
         <v>257</v>
       </c>
       <c r="G47" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="H47" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="I47" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>174</v>
@@ -3697,7 +3687,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="57">
+    <row r="48" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>101</v>
       </c>
@@ -3711,19 +3701,19 @@
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>314</v>
+        <v>531</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>294</v>
       </c>
       <c r="G48" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="H48" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="I48" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>164</v>
@@ -3732,7 +3722,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>103</v>
       </c>
@@ -3752,13 +3742,13 @@
         <v>290</v>
       </c>
       <c r="G49" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="H49" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="I49" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>163</v>
@@ -3767,7 +3757,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -3787,13 +3777,13 @@
         <v>274</v>
       </c>
       <c r="G50" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="I50" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>169</v>
@@ -3802,7 +3792,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -3816,19 +3806,19 @@
         <v>34</v>
       </c>
       <c r="E51" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F51" t="s">
         <v>237</v>
       </c>
       <c r="G51" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="I51" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>182</v>
@@ -3837,7 +3827,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>49</v>
       </c>
@@ -3851,19 +3841,19 @@
         <v>34</v>
       </c>
       <c r="E52" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F52" t="s">
         <v>252</v>
       </c>
       <c r="G52" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="H52" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="I52" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>189</v>
@@ -3872,7 +3862,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -3886,19 +3876,19 @@
         <v>34</v>
       </c>
       <c r="E53" t="s">
-        <v>328</v>
+        <v>532</v>
       </c>
       <c r="F53" t="s">
         <v>221</v>
       </c>
       <c r="G53" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="H53" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="I53" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>183</v>
@@ -3907,7 +3897,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="57">
+    <row r="54" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -3921,28 +3911,28 @@
         <v>34</v>
       </c>
       <c r="E54" t="s">
-        <v>329</v>
+        <v>533</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="G54" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="H54" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="I54" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>183</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -3956,19 +3946,19 @@
         <v>34</v>
       </c>
       <c r="E55" t="s">
-        <v>323</v>
+        <v>534</v>
       </c>
       <c r="F55" t="s">
         <v>251</v>
       </c>
       <c r="G55" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="H55" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="I55" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>187</v>
@@ -3977,7 +3967,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -3991,19 +3981,19 @@
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="F56" t="s">
         <v>248</v>
       </c>
       <c r="G56" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="H56" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="I56" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>181</v>
@@ -4012,7 +4002,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -4032,13 +4022,13 @@
         <v>249</v>
       </c>
       <c r="G57" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="H57" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="I57" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>153</v>
@@ -4047,7 +4037,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -4061,19 +4051,19 @@
         <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F58" t="s">
         <v>246</v>
       </c>
       <c r="G58" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="H58" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="I58" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>188</v>
@@ -4082,7 +4072,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42.75">
+    <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>45</v>
       </c>
@@ -4096,30 +4086,30 @@
         <v>34</v>
       </c>
       <c r="E59" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>235</v>
       </c>
       <c r="G59" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="H59" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="I59" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>190</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B60" t="s">
         <v>75</v>
@@ -4131,19 +4121,19 @@
         <v>31</v>
       </c>
       <c r="E60" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="F60" t="s">
         <v>279</v>
       </c>
       <c r="G60" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="I60" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>173</v>
@@ -4152,9 +4142,9 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B61" t="s">
         <v>79</v>
@@ -4166,28 +4156,28 @@
         <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F61" t="s">
         <v>277</v>
       </c>
       <c r="G61" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="H61" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="I61" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>172</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>29</v>
       </c>
@@ -4201,19 +4191,19 @@
         <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F62" t="s">
         <v>215</v>
       </c>
       <c r="G62" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="H62" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="I62" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J62" t="s">
         <v>184</v>
@@ -4222,7 +4212,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>88</v>
       </c>
@@ -4236,19 +4226,19 @@
         <v>31</v>
       </c>
       <c r="E63" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F63" t="s">
         <v>215</v>
       </c>
       <c r="G63" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="H63" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="I63" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>167</v>
@@ -4257,12 +4247,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B64" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -4271,33 +4261,33 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="F64" t="s">
         <v>290</v>
       </c>
       <c r="G64" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="I64" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J64" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="K64" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B65" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -4306,33 +4296,33 @@
         <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="F65" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="G65">
         <v>155</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="I65" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J65" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="K65" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B66" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C66" t="s">
         <v>44</v>
@@ -4341,33 +4331,33 @@
         <v>34</v>
       </c>
       <c r="E66" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="F66" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="G66">
         <v>117</v>
       </c>
       <c r="H66" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="I66" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="J66" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="K66" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B67" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C67" t="s">
         <v>44</v>
@@ -4382,13 +4372,13 @@
         <v>290</v>
       </c>
       <c r="G67" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="H67" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="I67" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="J67" t="s">
         <v>163</v>
@@ -4398,126 +4388,126 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1">
-    <sortState ref="A2:K67">
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K67">
       <sortCondition ref="J1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J31" r:id="rId1"/>
-    <hyperlink ref="J39" r:id="rId2"/>
-    <hyperlink ref="J38" r:id="rId3"/>
-    <hyperlink ref="J21" r:id="rId4"/>
-    <hyperlink ref="J9" r:id="rId5"/>
-    <hyperlink ref="J22" r:id="rId6"/>
-    <hyperlink ref="J33" r:id="rId7"/>
-    <hyperlink ref="J7" r:id="rId8"/>
-    <hyperlink ref="J32" r:id="rId9"/>
-    <hyperlink ref="J29" r:id="rId10"/>
-    <hyperlink ref="J10" r:id="rId11"/>
-    <hyperlink ref="J27" r:id="rId12"/>
-    <hyperlink ref="J5" r:id="rId13"/>
-    <hyperlink ref="J14" r:id="rId14"/>
-    <hyperlink ref="J19" r:id="rId15"/>
-    <hyperlink ref="J43" r:id="rId16"/>
-    <hyperlink ref="J12" r:id="rId17"/>
-    <hyperlink ref="J8" r:id="rId18"/>
-    <hyperlink ref="J35" r:id="rId19"/>
-    <hyperlink ref="J18" r:id="rId20"/>
-    <hyperlink ref="J6" r:id="rId21"/>
-    <hyperlink ref="J24" r:id="rId22"/>
-    <hyperlink ref="J57" r:id="rId23"/>
-    <hyperlink ref="J13" r:id="rId24"/>
-    <hyperlink ref="J30" r:id="rId25"/>
-    <hyperlink ref="J16" r:id="rId26"/>
-    <hyperlink ref="J42" r:id="rId27"/>
-    <hyperlink ref="J15" r:id="rId28"/>
-    <hyperlink ref="J41" r:id="rId29"/>
-    <hyperlink ref="J34" r:id="rId30"/>
-    <hyperlink ref="J23" r:id="rId31"/>
-    <hyperlink ref="J37" r:id="rId32"/>
-    <hyperlink ref="J49" r:id="rId33"/>
-    <hyperlink ref="J48" r:id="rId34"/>
-    <hyperlink ref="J40" r:id="rId35"/>
-    <hyperlink ref="J44" r:id="rId36"/>
-    <hyperlink ref="J63" r:id="rId37"/>
-    <hyperlink ref="J3" r:id="rId38"/>
-    <hyperlink ref="J50" r:id="rId39"/>
-    <hyperlink ref="J2" r:id="rId40"/>
-    <hyperlink ref="J28" r:id="rId41"/>
-    <hyperlink ref="J61" r:id="rId42"/>
-    <hyperlink ref="J60" r:id="rId43"/>
-    <hyperlink ref="J47" r:id="rId44"/>
-    <hyperlink ref="J20" r:id="rId45"/>
-    <hyperlink ref="J25" r:id="rId46"/>
-    <hyperlink ref="J36" r:id="rId47"/>
-    <hyperlink ref="J17" r:id="rId48"/>
-    <hyperlink ref="J46" r:id="rId49"/>
-    <hyperlink ref="J45" r:id="rId50"/>
-    <hyperlink ref="J56" r:id="rId51" location="texto"/>
-    <hyperlink ref="J51" r:id="rId52"/>
-    <hyperlink ref="J54" r:id="rId53"/>
-    <hyperlink ref="J53" r:id="rId54"/>
-    <hyperlink ref="J11" r:id="rId55"/>
-    <hyperlink ref="J26" r:id="rId56"/>
-    <hyperlink ref="J55" r:id="rId57"/>
-    <hyperlink ref="J58" r:id="rId58"/>
-    <hyperlink ref="J59" r:id="rId59"/>
-    <hyperlink ref="J52" r:id="rId60"/>
-    <hyperlink ref="K63" r:id="rId61"/>
-    <hyperlink ref="K6" r:id="rId62"/>
-    <hyperlink ref="K11" r:id="rId63"/>
-    <hyperlink ref="K16" r:id="rId64"/>
-    <hyperlink ref="K62" r:id="rId65"/>
-    <hyperlink ref="K46" r:id="rId66"/>
-    <hyperlink ref="K17" r:id="rId67"/>
-    <hyperlink ref="K8" r:id="rId68"/>
-    <hyperlink ref="K37" r:id="rId69"/>
-    <hyperlink ref="K15" r:id="rId70"/>
-    <hyperlink ref="K26" r:id="rId71"/>
-    <hyperlink ref="K51" r:id="rId72"/>
-    <hyperlink ref="K53" r:id="rId73"/>
-    <hyperlink ref="K7" r:id="rId74"/>
-    <hyperlink ref="K58" r:id="rId75"/>
-    <hyperlink ref="K56" r:id="rId76"/>
-    <hyperlink ref="K57" r:id="rId77"/>
-    <hyperlink ref="K55" r:id="rId78"/>
-    <hyperlink ref="K52" r:id="rId79"/>
-    <hyperlink ref="K25" r:id="rId80"/>
-    <hyperlink ref="K13" r:id="rId81"/>
-    <hyperlink ref="K47" r:id="rId82"/>
-    <hyperlink ref="K19" r:id="rId83"/>
-    <hyperlink ref="K20" r:id="rId84"/>
-    <hyperlink ref="K42" r:id="rId85"/>
-    <hyperlink ref="K28" r:id="rId86"/>
-    <hyperlink ref="K50" r:id="rId87"/>
-    <hyperlink ref="K60" r:id="rId88"/>
-    <hyperlink ref="K4" r:id="rId89" display="http://www.loteriamineira.mg.gov.br"/>
-    <hyperlink ref="K45" r:id="rId90" display="http://www.jucemg.mg.gov.br"/>
-    <hyperlink ref="K12" r:id="rId91" display="http://www.gabinetemilitar.mg.gov.br"/>
-    <hyperlink ref="K36" r:id="rId92"/>
-    <hyperlink ref="K30" r:id="rId93"/>
-    <hyperlink ref="K41" r:id="rId94"/>
-    <hyperlink ref="K34" r:id="rId95"/>
-    <hyperlink ref="K49" r:id="rId96"/>
-    <hyperlink ref="K48" r:id="rId97"/>
-    <hyperlink ref="K40" r:id="rId98"/>
-    <hyperlink ref="K43" r:id="rId99"/>
-    <hyperlink ref="K35" r:id="rId100"/>
-    <hyperlink ref="K31" r:id="rId101"/>
-    <hyperlink ref="K14" r:id="rId102"/>
-    <hyperlink ref="K3" r:id="rId103"/>
-    <hyperlink ref="H60" r:id="rId104"/>
-    <hyperlink ref="H26" r:id="rId105"/>
-    <hyperlink ref="H27" r:id="rId106"/>
-    <hyperlink ref="H22" r:id="rId107"/>
-    <hyperlink ref="H19" r:id="rId108"/>
-    <hyperlink ref="H13" r:id="rId109"/>
-    <hyperlink ref="H51" r:id="rId110"/>
-    <hyperlink ref="H64" r:id="rId111"/>
-    <hyperlink ref="H43" r:id="rId112"/>
-    <hyperlink ref="H18" r:id="rId113"/>
-    <hyperlink ref="K18" r:id="rId114"/>
+    <hyperlink ref="J31" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="J38" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J21" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="J9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="J22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="J33" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="J7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J32" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="J29" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="J10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="J27" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="J5" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="J14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="J19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="J43" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="J12" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="J8" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="J18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="J6" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="J24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="J57" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="J13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="J30" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="J16" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="J42" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="J15" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="J41" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="J34" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="J23" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="J37" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="J49" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="J48" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="J40" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="J44" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="J63" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="J3" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="J50" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="J2" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="J28" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="J61" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="J60" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="J47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="J20" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="J25" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="J36" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="J17" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="J46" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="J45" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="J56" r:id="rId51" location="texto" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="J51" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="J54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="J53" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="J11" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="J26" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="J55" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="J58" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="J59" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="J52" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="K6" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="K11" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="K16" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="K62" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="K46" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="K17" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="K8" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="K37" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="K15" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="K26" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="K51" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="K53" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="K7" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="K58" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="K56" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="K57" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="K55" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="K52" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="K25" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="K13" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="K47" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="K19" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="K20" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="K42" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="K28" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="K50" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="K60" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="K4" r:id="rId89" display="http://www.loteriamineira.mg.gov.br" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="K45" r:id="rId90" display="http://www.jucemg.mg.gov.br" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="K12" r:id="rId91" display="http://www.gabinetemilitar.mg.gov.br" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="K36" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="K30" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="K41" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="K34" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="K49" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="K48" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="K40" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="K43" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="K35" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="K31" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="K14" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="K3" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="H60" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="H26" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="H27" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="H22" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="H19" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="H13" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="H51" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="H64" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="H43" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="H18" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="K18" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId115"/>

--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32525654-30D1-4A89-BCC6-DF0F6C065072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="534">
   <si>
     <t>orgao</t>
   </si>
@@ -633,9 +632,6 @@
     <t>http://www.loteriamineira.mg.gov.br</t>
   </si>
   <si>
-    <t>Onésimo Diniz Moreira</t>
-  </si>
-  <si>
     <t>http://www.jucemg.mg.gov.br</t>
   </si>
   <si>
@@ -819,9 +815,6 @@
     <t>https://feam.br/</t>
   </si>
   <si>
-    <t>Edson de Resende Castro</t>
-  </si>
-  <si>
     <t>Frederico Correa Lima de Carvalho</t>
   </si>
   <si>
@@ -930,9 +923,6 @@
     <t>http://www.social.mg.gov.br</t>
   </si>
   <si>
-    <t>Alê Portela</t>
-  </si>
-  <si>
     <t>14º andar do Edifício Minas - Cidade Administrativa, Belo Horizonte</t>
   </si>
   <si>
@@ -945,9 +935,6 @@
     <t>4º andar do Palácio Tiradentes - Cidade Administrativa, Belo Horizonte</t>
   </si>
   <si>
-    <t>Luiz Otávio de Oliveira Gonçalves</t>
-  </si>
-  <si>
     <t>Thales Almeida Ferreira Fernandes</t>
   </si>
   <si>
@@ -957,9 +944,6 @@
     <t>http://www.secretariageral.mg.gov.br/</t>
   </si>
   <si>
-    <t>Coronel Carlos Frederico Otoni Garcia</t>
-  </si>
-  <si>
     <t>Gabriela Câmara Campos Bernardes Siqueira</t>
   </si>
   <si>
@@ -976,9 +960,6 @@
   </si>
   <si>
     <t>Gabriel Viégas Neto</t>
-  </si>
-  <si>
-    <t>Reynaldo Passanezi Filho</t>
   </si>
   <si>
     <t>Luísa Cardoso Barreto</t>
@@ -1045,9 +1026,6 @@
     <t>https://www.agenciarmbh.mg.gov.br/</t>
   </si>
   <si>
-    <t>Ilce Alves Rocha Perdigão</t>
-  </si>
-  <si>
     <t>https://www.bombeiros.mg.gov.br/</t>
   </si>
   <si>
@@ -1513,9 +1491,6 @@
     <t>atendimento@gasmig.com.br</t>
   </si>
   <si>
-    <t>Carlos Ivan Camargo de Colón</t>
-  </si>
-  <si>
     <t>0800-0300005</t>
   </si>
   <si>
@@ -1606,9 +1581,6 @@
     <t>Ike Yagelovic</t>
   </si>
   <si>
-    <t>Yuri Mesquita</t>
-  </si>
-  <si>
     <t>Rodrigo César Câmara Baia</t>
   </si>
   <si>
@@ -1621,9 +1593,6 @@
     <t>Luciana Mundim de Mattos Paixão</t>
   </si>
   <si>
-    <t>Gustavo Braga</t>
-  </si>
-  <si>
     <t>Castellar Modesto Guimarães Neto</t>
   </si>
   <si>
@@ -1633,14 +1602,41 @@
     <t>Gustavo Fonseca Nogueira</t>
   </si>
   <si>
-    <t>Zezinho Andrada</t>
+    <t>Yuri Mesquita Mesquita</t>
+  </si>
+  <si>
+    <t>Luciano França da Silveira Junior</t>
+  </si>
+  <si>
+    <t>Marcel Dornas Beghini</t>
+  </si>
+  <si>
+    <t>Marcelo Couto Dias</t>
+  </si>
+  <si>
+    <t>Renato Teixeira Brandão</t>
+  </si>
+  <si>
+    <t>Gustavo Oliveira Braga de Souza</t>
+  </si>
+  <si>
+    <t>José Bonifácio Couto de Andrada</t>
+  </si>
+  <si>
+    <t>Coronel Cleide Barcelos dos Reis Rodrigues</t>
+  </si>
+  <si>
+    <t>Gustavo de Marchi</t>
+  </si>
+  <si>
+    <t>Alexandre Ramos Peixoto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1661,6 +1657,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1684,13 +1686,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -2025,24 +2028,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="49.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="66.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.25" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2065,10 +2068,10 @@
         <v>193</v>
       </c>
       <c r="H1" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="I1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="J1" t="s">
         <v>128</v>
@@ -2077,12 +2080,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>
@@ -2091,523 +2094,520 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="F2" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="G2" t="s">
-        <v>451</v>
-      </c>
-      <c r="H2" t="s">
-        <v>376</v>
+        <v>479</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="I2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G3" t="s">
+        <v>447</v>
+      </c>
+      <c r="H3" t="s">
+        <v>359</v>
+      </c>
+      <c r="I3" t="s">
         <v>357</v>
       </c>
-      <c r="F3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G3" t="s">
-        <v>452</v>
-      </c>
-      <c r="H3" t="s">
-        <v>520</v>
-      </c>
-      <c r="I3" t="s">
-        <v>368</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>40</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>197</v>
+        <v>232</v>
+      </c>
+      <c r="F4" t="s">
+        <v>233</v>
       </c>
       <c r="G4" t="s">
-        <v>438</v>
-      </c>
-      <c r="H4" t="s">
-        <v>498</v>
+        <v>320</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="I4" t="s">
-        <v>381</v>
-      </c>
-      <c r="J4" t="s">
-        <v>143</v>
+        <v>357</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>42</v>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28.5">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>523</v>
+        <v>229</v>
       </c>
       <c r="F5" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G5" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="H5" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="I5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>402</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>403</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>312</v>
+        <v>481</v>
       </c>
       <c r="F6" t="s">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="G6" t="s">
-        <v>427</v>
-      </c>
-      <c r="H6" t="s">
-        <v>504</v>
+        <v>482</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>483</v>
       </c>
       <c r="I6" t="s">
-        <v>391</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="J6" t="s">
+        <v>509</v>
+      </c>
+      <c r="K6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>524</v>
+        <v>310</v>
       </c>
       <c r="F7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H7" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="I7" t="s">
+        <v>362</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F8" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" t="s">
+        <v>434</v>
+      </c>
+      <c r="H8" t="s">
+        <v>404</v>
+      </c>
+      <c r="I8" t="s">
+        <v>384</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B9" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="F9" t="s">
+        <v>485</v>
+      </c>
+      <c r="G9">
+        <v>117</v>
+      </c>
+      <c r="H9" t="s">
+        <v>486</v>
+      </c>
+      <c r="I9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J9" t="s">
+        <v>511</v>
+      </c>
+      <c r="K9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F10" t="s">
+        <v>250</v>
+      </c>
+      <c r="G10" t="s">
+        <v>446</v>
+      </c>
+      <c r="H10" t="s">
+        <v>508</v>
+      </c>
+      <c r="I10" t="s">
+        <v>357</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F11" t="s">
+        <v>248</v>
+      </c>
+      <c r="G11" t="s">
+        <v>468</v>
+      </c>
+      <c r="H11" t="s">
+        <v>364</v>
+      </c>
+      <c r="I11" t="s">
+        <v>365</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F12" t="s">
+        <v>247</v>
+      </c>
+      <c r="G12" t="s">
+        <v>469</v>
+      </c>
+      <c r="H12" t="s">
+        <v>366</v>
+      </c>
+      <c r="I12" t="s">
+        <v>357</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="F13" t="s">
+        <v>245</v>
+      </c>
+      <c r="G13" t="s">
+        <v>462</v>
+      </c>
+      <c r="H13" t="s">
+        <v>367</v>
+      </c>
+      <c r="I13" t="s">
+        <v>357</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>324</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>309</v>
+      </c>
+      <c r="F14" t="s">
+        <v>275</v>
+      </c>
+      <c r="G14" t="s">
+        <v>454</v>
+      </c>
+      <c r="H14" t="s">
         <v>368</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>220</v>
-      </c>
-      <c r="F8" t="s">
-        <v>221</v>
-      </c>
-      <c r="G8" t="s">
-        <v>327</v>
-      </c>
-      <c r="H8" t="s">
-        <v>401</v>
-      </c>
-      <c r="I8" t="s">
-        <v>364</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>525</v>
-      </c>
-      <c r="F9" t="s">
-        <v>269</v>
-      </c>
-      <c r="G9" t="s">
-        <v>483</v>
-      </c>
-      <c r="H9" t="s">
-        <v>387</v>
-      </c>
-      <c r="I9" t="s">
-        <v>421</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G10" t="s">
-        <v>447</v>
-      </c>
-      <c r="H10" t="s">
-        <v>407</v>
-      </c>
-      <c r="I10" t="s">
-        <v>364</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>208</v>
-      </c>
-      <c r="F11" t="s">
-        <v>209</v>
-      </c>
-      <c r="G11" t="s">
-        <v>463</v>
-      </c>
-      <c r="H11" t="s">
-        <v>509</v>
-      </c>
-      <c r="I11" t="s">
-        <v>364</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>348</v>
-      </c>
-      <c r="F12" t="s">
-        <v>266</v>
-      </c>
-      <c r="G12" t="s">
-        <v>480</v>
-      </c>
-      <c r="H12" t="s">
-        <v>390</v>
-      </c>
-      <c r="I12" t="s">
-        <v>382</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>311</v>
-      </c>
-      <c r="F13" t="s">
-        <v>255</v>
-      </c>
-      <c r="G13" t="s">
-        <v>472</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I13" t="s">
-        <v>419</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>264</v>
-      </c>
-      <c r="F14" t="s">
-        <v>251</v>
-      </c>
-      <c r="G14" t="s">
-        <v>442</v>
-      </c>
-      <c r="H14" t="s">
-        <v>392</v>
-      </c>
       <c r="I14" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>336</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>230</v>
+        <v>339</v>
       </c>
       <c r="F15" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G15" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="H15" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="I15" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>349</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>209</v>
+        <v>335</v>
+      </c>
+      <c r="F16" t="s">
+        <v>227</v>
       </c>
       <c r="G16" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H16" t="s">
-        <v>507</v>
+        <v>370</v>
       </c>
       <c r="I16" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>398</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>397</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -2616,238 +2616,238 @@
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>217</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G17" t="s">
-        <v>473</v>
-      </c>
-      <c r="H17" t="s">
-        <v>506</v>
+        <v>417</v>
+      </c>
+      <c r="F17" t="s">
+        <v>418</v>
+      </c>
+      <c r="G17">
+        <v>155</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>419</v>
       </c>
       <c r="I17" t="s">
-        <v>364</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="J17" t="s">
+        <v>510</v>
+      </c>
+      <c r="K17" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>201</v>
+        <v>515</v>
       </c>
       <c r="F18" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="G18" t="s">
-        <v>439</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>521</v>
+        <v>467</v>
+      </c>
+      <c r="H18" t="s">
+        <v>372</v>
       </c>
       <c r="I18" t="s">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="F19" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="G19" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="I19" t="s">
-        <v>397</v>
+        <v>357</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>516</v>
       </c>
       <c r="F20" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="G20" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="H20" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="I20" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>331</v>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>350</v>
+        <v>273</v>
       </c>
       <c r="F21" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="G21" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="H21" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="I21" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
         <v>70</v>
       </c>
       <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>340</v>
+      </c>
+      <c r="F22" t="s">
+        <v>252</v>
+      </c>
+      <c r="G22" t="s">
+        <v>459</v>
+      </c>
+      <c r="H22" t="s">
+        <v>379</v>
+      </c>
+      <c r="I22" t="s">
+        <v>378</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
         <v>71</v>
       </c>
-      <c r="E22" t="s">
-        <v>526</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E23" t="s">
+        <v>524</v>
+      </c>
+      <c r="F23" t="s">
         <v>267</v>
       </c>
-      <c r="G22" t="s">
-        <v>467</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I22" t="s">
-        <v>368</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
-        <v>338</v>
-      </c>
-      <c r="F23" t="s">
-        <v>210</v>
-      </c>
       <c r="G23" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="H23" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="I23" t="s">
-        <v>364</v>
+        <v>414</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -2861,1653 +2861,1653 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G24" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="H24" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="I24" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>152</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
         <v>70</v>
       </c>
       <c r="D25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" t="s">
+        <v>517</v>
+      </c>
+      <c r="F25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" t="s">
+        <v>460</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I25" t="s">
+        <v>361</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>341</v>
+      </c>
+      <c r="F26" t="s">
+        <v>264</v>
+      </c>
+      <c r="G26" t="s">
+        <v>473</v>
+      </c>
+      <c r="H26" t="s">
+        <v>383</v>
+      </c>
+      <c r="I26" t="s">
+        <v>375</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" t="s">
+        <v>262</v>
+      </c>
+      <c r="F27" t="s">
+        <v>250</v>
+      </c>
+      <c r="G27" t="s">
+        <v>435</v>
+      </c>
+      <c r="H27" t="s">
+        <v>385</v>
+      </c>
+      <c r="I27" t="s">
+        <v>384</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>528</v>
+      </c>
+      <c r="F28" t="s">
+        <v>208</v>
+      </c>
+      <c r="G28" t="s">
+        <v>457</v>
+      </c>
+      <c r="H28" t="s">
+        <v>386</v>
+      </c>
+      <c r="I28" t="s">
+        <v>384</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
         <v>109</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E29" t="s">
+        <v>259</v>
+      </c>
+      <c r="F29" t="s">
+        <v>260</v>
+      </c>
+      <c r="G29" t="s">
+        <v>430</v>
+      </c>
+      <c r="H29" t="s">
+        <v>387</v>
+      </c>
+      <c r="I29" t="s">
+        <v>357</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" t="s">
+        <v>257</v>
+      </c>
+      <c r="F30" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" t="s">
+        <v>461</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I30" t="s">
+        <v>390</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" t="s">
+        <v>255</v>
+      </c>
+      <c r="F31" t="s">
+        <v>256</v>
+      </c>
+      <c r="G31" t="s">
+        <v>474</v>
+      </c>
+      <c r="H31" t="s">
+        <v>391</v>
+      </c>
+      <c r="I31" t="s">
+        <v>357</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="28.5">
+      <c r="A32" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" t="s">
+        <v>253</v>
+      </c>
+      <c r="G32" t="s">
+        <v>477</v>
+      </c>
+      <c r="H32" t="s">
+        <v>411</v>
+      </c>
+      <c r="I32" t="s">
+        <v>361</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F25" t="s">
-        <v>253</v>
-      </c>
-      <c r="G25" t="s">
-        <v>466</v>
-      </c>
-      <c r="H25" t="s">
-        <v>386</v>
-      </c>
-      <c r="I25" t="s">
-        <v>385</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" t="s">
-        <v>233</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="G26" t="s">
-        <v>326</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="I26" t="s">
-        <v>364</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" t="s">
-        <v>318</v>
-      </c>
-      <c r="F27" t="s">
-        <v>241</v>
-      </c>
-      <c r="G27" t="s">
-        <v>471</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="I27" t="s">
-        <v>364</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>306</v>
+      </c>
+      <c r="F33" t="s">
+        <v>254</v>
+      </c>
+      <c r="G33" t="s">
+        <v>465</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I33" t="s">
+        <v>412</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
         <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>310</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G28" t="s">
-        <v>462</v>
-      </c>
-      <c r="H28" t="s">
-        <v>422</v>
-      </c>
-      <c r="I28" t="s">
-        <v>364</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" t="s">
-        <v>305</v>
-      </c>
-      <c r="F29" t="s">
-        <v>304</v>
-      </c>
-      <c r="G29" t="s">
-        <v>429</v>
-      </c>
-      <c r="H29" t="s">
-        <v>428</v>
-      </c>
-      <c r="I29" t="s">
-        <v>368</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" t="s">
-        <v>313</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G30" t="s">
-        <v>430</v>
-      </c>
-      <c r="H30" t="s">
-        <v>431</v>
-      </c>
-      <c r="I30" t="s">
-        <v>368</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>362</v>
-      </c>
-      <c r="B31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" t="s">
-        <v>432</v>
-      </c>
-      <c r="F31" t="s">
-        <v>304</v>
-      </c>
-      <c r="G31" t="s">
-        <v>434</v>
-      </c>
-      <c r="H31" t="s">
-        <v>433</v>
-      </c>
-      <c r="I31" t="s">
-        <v>368</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" t="s">
-        <v>527</v>
-      </c>
-      <c r="F32" t="s">
-        <v>304</v>
-      </c>
-      <c r="G32" t="s">
-        <v>435</v>
-      </c>
-      <c r="H32" t="s">
-        <v>423</v>
-      </c>
-      <c r="I32" t="s">
-        <v>368</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" t="s">
-        <v>528</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G33" t="s">
-        <v>460</v>
-      </c>
-      <c r="H33" t="s">
-        <v>511</v>
-      </c>
-      <c r="I33" t="s">
-        <v>391</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" t="s">
-        <v>92</v>
       </c>
       <c r="D34" t="s">
         <v>31</v>
       </c>
       <c r="E34" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="F34" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="G34" t="s">
-        <v>458</v>
-      </c>
-      <c r="H34" t="s">
-        <v>512</v>
+        <v>452</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="I34" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" t="s">
         <v>16</v>
       </c>
-      <c r="C35" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" t="s">
-        <v>31</v>
-      </c>
       <c r="E35" t="s">
-        <v>300</v>
+        <v>219</v>
       </c>
       <c r="F35" t="s">
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="G35" t="s">
-        <v>440</v>
+        <v>321</v>
       </c>
       <c r="H35" t="s">
-        <v>499</v>
+        <v>394</v>
       </c>
       <c r="I35" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" t="s">
-        <v>281</v>
+        <v>34</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>522</v>
       </c>
       <c r="F36" t="s">
-        <v>282</v>
+        <v>220</v>
       </c>
       <c r="G36" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="H36" t="s">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="I36" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>342</v>
+        <v>216</v>
       </c>
       <c r="F37" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G37" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H37" t="s">
-        <v>377</v>
+        <v>498</v>
       </c>
       <c r="I37" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E38" t="s">
+        <v>215</v>
+      </c>
+      <c r="F38" t="s">
+        <v>327</v>
+      </c>
+      <c r="G38" t="s">
         <v>322</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G38" t="s">
-        <v>456</v>
-      </c>
       <c r="H38" t="s">
-        <v>388</v>
+        <v>502</v>
       </c>
       <c r="I38" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="D39" t="s">
         <v>31</v>
       </c>
       <c r="E39" t="s">
-        <v>306</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>307</v>
+        <v>344</v>
+      </c>
+      <c r="F39" t="s">
+        <v>214</v>
       </c>
       <c r="G39" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="H39" t="s">
-        <v>514</v>
+        <v>389</v>
       </c>
       <c r="I39" t="s">
-        <v>369</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>131</v>
+        <v>384</v>
+      </c>
+      <c r="J39" t="s">
+        <v>184</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>529</v>
+        <v>342</v>
       </c>
       <c r="F40" t="s">
-        <v>296</v>
+        <v>208</v>
       </c>
       <c r="G40" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="H40" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="I40" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>361</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
-        <v>286</v>
+        <v>212</v>
       </c>
       <c r="G41" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="H41" t="s">
-        <v>508</v>
+        <v>400</v>
       </c>
       <c r="I41" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="D42" t="s">
         <v>6</v>
       </c>
       <c r="E42" t="s">
-        <v>263</v>
-      </c>
-      <c r="F42" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" t="s">
+        <v>208</v>
+      </c>
+      <c r="G42" t="s">
+        <v>456</v>
+      </c>
+      <c r="H42" t="s">
+        <v>501</v>
+      </c>
+      <c r="I42" t="s">
+        <v>357</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" t="s">
+        <v>307</v>
+      </c>
+      <c r="F43" t="s">
+        <v>202</v>
+      </c>
+      <c r="G43" t="s">
+        <v>420</v>
+      </c>
+      <c r="H43" t="s">
+        <v>496</v>
+      </c>
+      <c r="I43" t="s">
+        <v>384</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" t="s">
+        <v>525</v>
+      </c>
+      <c r="F44" t="s">
         <v>209</v>
       </c>
-      <c r="G42" t="s">
-        <v>464</v>
-      </c>
-      <c r="H42" t="s">
-        <v>393</v>
-      </c>
-      <c r="I42" t="s">
-        <v>391</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>98</v>
-      </c>
-      <c r="B43" t="s">
-        <v>39</v>
-      </c>
-      <c r="C43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="G44" t="s">
+        <v>432</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I44" t="s">
+        <v>401</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" t="s">
+        <v>314</v>
+      </c>
+      <c r="F45" t="s">
+        <v>236</v>
+      </c>
+      <c r="G45" t="s">
+        <v>475</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I45" t="s">
+        <v>357</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" t="s">
+        <v>523</v>
+      </c>
+      <c r="F46" t="s">
+        <v>327</v>
+      </c>
+      <c r="G46" t="s">
+        <v>450</v>
+      </c>
+      <c r="H46" t="s">
+        <v>505</v>
+      </c>
+      <c r="I46" t="s">
+        <v>361</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" t="s">
         <v>31</v>
       </c>
-      <c r="E43" t="s">
-        <v>530</v>
-      </c>
-      <c r="F43" t="s">
-        <v>298</v>
-      </c>
-      <c r="G43" t="s">
-        <v>436</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="I43" t="s">
-        <v>368</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="E47" t="s">
+        <v>305</v>
+      </c>
+      <c r="F47" t="s">
+        <v>275</v>
+      </c>
+      <c r="G47" t="s">
+        <v>455</v>
+      </c>
+      <c r="H47" t="s">
+        <v>415</v>
+      </c>
+      <c r="I47" t="s">
+        <v>357</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" t="s">
         <v>76</v>
-      </c>
-      <c r="D44" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" t="s">
-        <v>275</v>
-      </c>
-      <c r="F44" t="s">
-        <v>276</v>
-      </c>
-      <c r="G44" t="s">
-        <v>478</v>
-      </c>
-      <c r="H44" t="s">
-        <v>384</v>
-      </c>
-      <c r="I44" t="s">
-        <v>368</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" t="s">
-        <v>39</v>
-      </c>
-      <c r="E45" t="s">
-        <v>199</v>
-      </c>
-      <c r="F45" t="s">
-        <v>211</v>
-      </c>
-      <c r="G45" t="s">
-        <v>445</v>
-      </c>
-      <c r="H45" t="s">
-        <v>501</v>
-      </c>
-      <c r="I45" t="s">
-        <v>369</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" t="s">
-        <v>216</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G46" t="s">
-        <v>328</v>
-      </c>
-      <c r="H46" t="s">
-        <v>510</v>
-      </c>
-      <c r="I46" t="s">
-        <v>391</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>116</v>
-      </c>
-      <c r="B47" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" t="s">
-        <v>256</v>
-      </c>
-      <c r="F47" t="s">
-        <v>257</v>
-      </c>
-      <c r="G47" t="s">
-        <v>481</v>
-      </c>
-      <c r="H47" t="s">
-        <v>398</v>
-      </c>
-      <c r="I47" t="s">
-        <v>364</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>101</v>
-      </c>
-      <c r="B48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" t="s">
-        <v>92</v>
       </c>
       <c r="D48" t="s">
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>531</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>294</v>
+        <v>350</v>
+      </c>
+      <c r="F48" t="s">
+        <v>268</v>
       </c>
       <c r="G48" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H48" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="I48" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D49" t="s">
         <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>291</v>
+        <v>531</v>
       </c>
       <c r="F49" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="G49" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="H49" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="I49" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D50" t="s">
         <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="F50" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="G50" t="s">
-        <v>459</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>400</v>
+        <v>448</v>
+      </c>
+      <c r="H50" t="s">
+        <v>506</v>
       </c>
       <c r="I50" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>526</v>
+      </c>
+      <c r="F51" t="s">
+        <v>301</v>
+      </c>
+      <c r="G51" t="s">
+        <v>422</v>
+      </c>
+      <c r="H51" t="s">
+        <v>421</v>
+      </c>
+      <c r="I51" t="s">
+        <v>361</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" t="s">
+        <v>518</v>
+      </c>
+      <c r="F52" t="s">
+        <v>301</v>
+      </c>
+      <c r="G52" t="s">
+        <v>428</v>
+      </c>
+      <c r="H52" t="s">
+        <v>416</v>
+      </c>
+      <c r="I52" t="s">
+        <v>361</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B53" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="s">
+        <v>519</v>
+      </c>
+      <c r="F53" t="s">
+        <v>299</v>
+      </c>
+      <c r="G53" t="s">
+        <v>453</v>
+      </c>
+      <c r="H53" t="s">
+        <v>503</v>
+      </c>
+      <c r="I53" t="s">
+        <v>384</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" t="s">
         <v>34</v>
       </c>
-      <c r="E51" t="s">
-        <v>320</v>
-      </c>
-      <c r="F51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G51" t="s">
-        <v>482</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="I51" t="s">
-        <v>364</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" t="s">
-        <v>34</v>
-      </c>
-      <c r="E52" t="s">
-        <v>317</v>
-      </c>
-      <c r="F52" t="s">
-        <v>252</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" t="s">
+        <v>316</v>
+      </c>
+      <c r="F54" t="s">
+        <v>220</v>
+      </c>
+      <c r="G54" t="s">
+        <v>449</v>
+      </c>
+      <c r="H54" t="s">
+        <v>381</v>
+      </c>
+      <c r="I54" t="s">
+        <v>361</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>527</v>
+      </c>
+      <c r="F55" t="s">
+        <v>298</v>
+      </c>
+      <c r="G55" t="s">
+        <v>433</v>
+      </c>
+      <c r="H55" t="s">
+        <v>491</v>
+      </c>
+      <c r="I55" t="s">
+        <v>357</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" t="s">
+        <v>529</v>
+      </c>
+      <c r="F56" t="s">
+        <v>296</v>
+      </c>
+      <c r="G56" t="s">
+        <v>429</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I56" t="s">
+        <v>361</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" t="s">
+        <v>92</v>
+      </c>
+      <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" t="s">
+        <v>520</v>
+      </c>
+      <c r="F57" t="s">
+        <v>294</v>
+      </c>
+      <c r="G57" t="s">
+        <v>480</v>
+      </c>
+      <c r="H57" t="s">
+        <v>497</v>
+      </c>
+      <c r="I57" t="s">
+        <v>361</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" t="s">
+        <v>92</v>
+      </c>
+      <c r="D58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" t="s">
+        <v>521</v>
+      </c>
+      <c r="F58" t="s">
+        <v>292</v>
+      </c>
+      <c r="G58" t="s">
+        <v>439</v>
+      </c>
+      <c r="H58" t="s">
+        <v>494</v>
+      </c>
+      <c r="I58" t="s">
+        <v>361</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="s">
+        <v>289</v>
+      </c>
+      <c r="F59" t="s">
+        <v>288</v>
+      </c>
+      <c r="G59" t="s">
         <v>441</v>
       </c>
-      <c r="H52" t="s">
-        <v>411</v>
-      </c>
-      <c r="I52" t="s">
-        <v>391</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" t="s">
-        <v>34</v>
-      </c>
-      <c r="E53" t="s">
-        <v>532</v>
-      </c>
-      <c r="F53" t="s">
-        <v>221</v>
-      </c>
-      <c r="G53" t="s">
-        <v>443</v>
-      </c>
-      <c r="H53" t="s">
-        <v>402</v>
-      </c>
-      <c r="I53" t="s">
-        <v>368</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" t="s">
-        <v>34</v>
-      </c>
-      <c r="E54" t="s">
-        <v>533</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G54" t="s">
-        <v>457</v>
-      </c>
-      <c r="H54" t="s">
-        <v>513</v>
-      </c>
-      <c r="I54" t="s">
-        <v>368</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" t="s">
-        <v>34</v>
-      </c>
-      <c r="E55" t="s">
-        <v>534</v>
-      </c>
-      <c r="F55" t="s">
-        <v>251</v>
-      </c>
-      <c r="G55" t="s">
-        <v>453</v>
-      </c>
-      <c r="H55" t="s">
-        <v>516</v>
-      </c>
-      <c r="I55" t="s">
-        <v>364</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" t="s">
-        <v>321</v>
-      </c>
-      <c r="F56" t="s">
-        <v>248</v>
-      </c>
-      <c r="G56" t="s">
-        <v>476</v>
-      </c>
-      <c r="H56" t="s">
-        <v>373</v>
-      </c>
-      <c r="I56" t="s">
-        <v>364</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>53</v>
-      </c>
-      <c r="B57" t="s">
-        <v>54</v>
-      </c>
-      <c r="C57" t="s">
-        <v>44</v>
-      </c>
-      <c r="D57" t="s">
-        <v>34</v>
-      </c>
-      <c r="E57" t="s">
-        <v>285</v>
-      </c>
-      <c r="F57" t="s">
-        <v>249</v>
-      </c>
-      <c r="G57" t="s">
-        <v>475</v>
-      </c>
-      <c r="H57" t="s">
-        <v>371</v>
-      </c>
-      <c r="I57" t="s">
-        <v>372</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>47</v>
-      </c>
-      <c r="B58" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" t="s">
-        <v>34</v>
-      </c>
-      <c r="E58" t="s">
-        <v>316</v>
-      </c>
-      <c r="F58" t="s">
-        <v>246</v>
-      </c>
-      <c r="G58" t="s">
-        <v>469</v>
-      </c>
-      <c r="H58" t="s">
-        <v>374</v>
-      </c>
-      <c r="I58" t="s">
-        <v>364</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59" t="s">
-        <v>44</v>
-      </c>
-      <c r="D59" t="s">
-        <v>34</v>
-      </c>
-      <c r="E59" t="s">
-        <v>315</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G59" t="s">
-        <v>485</v>
-      </c>
       <c r="H59" t="s">
-        <v>370</v>
+        <v>507</v>
       </c>
       <c r="I59" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D60" t="s">
         <v>31</v>
       </c>
       <c r="E60" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="F60" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G60" t="s">
-        <v>486</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>365</v>
+        <v>451</v>
+      </c>
+      <c r="H60" t="s">
+        <v>504</v>
       </c>
       <c r="I60" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>330</v>
+        <v>106</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D61" t="s">
         <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="F61" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="G61" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="H61" t="s">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="I61" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="D62" t="s">
         <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="F62" t="s">
-        <v>215</v>
+        <v>328</v>
       </c>
       <c r="G62" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="H62" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="I62" t="s">
-        <v>391</v>
-      </c>
-      <c r="J62" t="s">
-        <v>184</v>
+        <v>361</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C63" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
         <v>31</v>
       </c>
       <c r="E63" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="F63" t="s">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="G63" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="H63" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="I63" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
+        <v>355</v>
+      </c>
+      <c r="B64" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" t="s">
+        <v>425</v>
+      </c>
+      <c r="F64" t="s">
+        <v>301</v>
+      </c>
+      <c r="G64" t="s">
+        <v>427</v>
+      </c>
+      <c r="H64" t="s">
+        <v>426</v>
+      </c>
+      <c r="I64" t="s">
+        <v>361</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
         <v>409</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>410</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>289</v>
+      </c>
+      <c r="F65" t="s">
+        <v>288</v>
+      </c>
+      <c r="G65" t="s">
+        <v>487</v>
+      </c>
+      <c r="H65" t="s">
+        <v>489</v>
+      </c>
+      <c r="I65" t="s">
+        <v>357</v>
+      </c>
+      <c r="J65" t="s">
+        <v>163</v>
+      </c>
+      <c r="K65" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" t="s">
         <v>5</v>
       </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" t="s">
-        <v>488</v>
-      </c>
-      <c r="F64" t="s">
-        <v>290</v>
-      </c>
-      <c r="G64" t="s">
-        <v>489</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="I64" t="s">
-        <v>368</v>
-      </c>
-      <c r="J64" t="s">
-        <v>517</v>
-      </c>
-      <c r="K64" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>405</v>
-      </c>
-      <c r="B65" t="s">
-        <v>404</v>
-      </c>
-      <c r="C65" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" t="s">
-        <v>424</v>
-      </c>
-      <c r="F65" t="s">
-        <v>425</v>
-      </c>
-      <c r="G65">
-        <v>155</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="I65" t="s">
-        <v>368</v>
-      </c>
-      <c r="J65" t="s">
-        <v>518</v>
-      </c>
-      <c r="K65" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>412</v>
-      </c>
-      <c r="B66" t="s">
-        <v>413</v>
-      </c>
-      <c r="C66" t="s">
-        <v>44</v>
-      </c>
       <c r="D66" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E66" t="s">
-        <v>494</v>
+        <v>199</v>
       </c>
       <c r="F66" t="s">
-        <v>492</v>
-      </c>
-      <c r="G66">
-        <v>117</v>
+        <v>210</v>
+      </c>
+      <c r="G66" t="s">
+        <v>438</v>
       </c>
       <c r="H66" t="s">
         <v>493</v>
       </c>
       <c r="I66" t="s">
-        <v>368</v>
-      </c>
-      <c r="J66" t="s">
-        <v>519</v>
-      </c>
-      <c r="K66" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>416</v>
+        <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>417</v>
+        <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E67" t="s">
-        <v>291</v>
+        <v>195</v>
       </c>
       <c r="F67" t="s">
-        <v>290</v>
+        <v>197</v>
       </c>
       <c r="G67" t="s">
-        <v>495</v>
+        <v>431</v>
       </c>
       <c r="H67" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="I67" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J67" t="s">
-        <v>163</v>
-      </c>
-      <c r="K67" t="s">
-        <v>292</v>
+        <v>143</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K67">
-      <sortCondition ref="J1"/>
+  <autoFilter ref="A1:K1">
+    <sortState ref="A2:K67">
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J31" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="J39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="J38" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="J21" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="J9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="J22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="J33" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="J7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="J32" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="J29" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="J10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="J27" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="J5" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="J14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="J19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="J43" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="J12" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="J8" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="J18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="J6" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="J57" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="J13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="J30" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="J16" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="J42" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="J15" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="J41" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="J34" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="J23" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="J37" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="J49" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="J48" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="J40" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="J44" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="J63" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="J3" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="J50" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="J2" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="J28" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="J61" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="J60" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="J47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="J20" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="J25" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="J36" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="J17" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="J46" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="J45" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="J56" r:id="rId51" location="texto" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="J51" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="J54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="J53" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="J11" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="J26" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="J55" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="J58" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="J59" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="J52" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="K63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="K6" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="K11" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="K16" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="K62" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="K46" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="K17" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="K8" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="K37" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="K15" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="K26" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="K51" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="K53" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="K7" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="K58" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="K56" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="K57" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="K55" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="K52" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="K25" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="K13" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="K47" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="K19" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="K20" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="K42" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="K28" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="K50" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="K60" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="K4" r:id="rId89" display="http://www.loteriamineira.mg.gov.br" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="K45" r:id="rId90" display="http://www.jucemg.mg.gov.br" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="K12" r:id="rId91" display="http://www.gabinetemilitar.mg.gov.br" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="K36" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="K30" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="K41" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="K34" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="K49" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="K48" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="K40" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="K43" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="K35" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="K31" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="K14" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="K3" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="H60" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="H26" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="H27" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="H22" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="H19" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="H13" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="H51" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="H64" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="H43" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="H18" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="K18" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="J64" r:id="rId1"/>
+    <hyperlink ref="J50" r:id="rId2"/>
+    <hyperlink ref="J54" r:id="rId3"/>
+    <hyperlink ref="J32" r:id="rId4"/>
+    <hyperlink ref="J23" r:id="rId5"/>
+    <hyperlink ref="J25" r:id="rId6"/>
+    <hyperlink ref="J53" r:id="rId7"/>
+    <hyperlink ref="J20" r:id="rId8"/>
+    <hyperlink ref="J52" r:id="rId9"/>
+    <hyperlink ref="J51" r:id="rId10"/>
+    <hyperlink ref="J41" r:id="rId11"/>
+    <hyperlink ref="J19" r:id="rId12"/>
+    <hyperlink ref="J18" r:id="rId13"/>
+    <hyperlink ref="J27" r:id="rId14"/>
+    <hyperlink ref="J30" r:id="rId15"/>
+    <hyperlink ref="J56" r:id="rId16"/>
+    <hyperlink ref="J26" r:id="rId17"/>
+    <hyperlink ref="J35" r:id="rId18"/>
+    <hyperlink ref="J55" r:id="rId19"/>
+    <hyperlink ref="J44" r:id="rId20"/>
+    <hyperlink ref="J43" r:id="rId21"/>
+    <hyperlink ref="J24" r:id="rId22"/>
+    <hyperlink ref="J11" r:id="rId23"/>
+    <hyperlink ref="J33" r:id="rId24"/>
+    <hyperlink ref="J62" r:id="rId25"/>
+    <hyperlink ref="J40" r:id="rId26"/>
+    <hyperlink ref="J28" r:id="rId27"/>
+    <hyperlink ref="J5" r:id="rId28"/>
+    <hyperlink ref="J61" r:id="rId29"/>
+    <hyperlink ref="J60" r:id="rId30"/>
+    <hyperlink ref="J3" r:id="rId31"/>
+    <hyperlink ref="J16" r:id="rId32"/>
+    <hyperlink ref="J59" r:id="rId33"/>
+    <hyperlink ref="J58" r:id="rId34"/>
+    <hyperlink ref="J57" r:id="rId35"/>
+    <hyperlink ref="J21" r:id="rId36"/>
+    <hyperlink ref="J49" r:id="rId37"/>
+    <hyperlink ref="J48" r:id="rId38"/>
+    <hyperlink ref="J34" r:id="rId39"/>
+    <hyperlink ref="J15" r:id="rId40"/>
+    <hyperlink ref="J47" r:id="rId41"/>
+    <hyperlink ref="J14" r:id="rId42"/>
+    <hyperlink ref="J2" r:id="rId43"/>
+    <hyperlink ref="J31" r:id="rId44"/>
+    <hyperlink ref="J29" r:id="rId45"/>
+    <hyperlink ref="J22" r:id="rId46"/>
+    <hyperlink ref="J63" r:id="rId47"/>
+    <hyperlink ref="J37" r:id="rId48"/>
+    <hyperlink ref="J38" r:id="rId49"/>
+    <hyperlink ref="J66" r:id="rId50"/>
+    <hyperlink ref="J12" r:id="rId51" location="texto"/>
+    <hyperlink ref="J45" r:id="rId52"/>
+    <hyperlink ref="J46" r:id="rId53"/>
+    <hyperlink ref="J36" r:id="rId54"/>
+    <hyperlink ref="J42" r:id="rId55"/>
+    <hyperlink ref="J4" r:id="rId56"/>
+    <hyperlink ref="J10" r:id="rId57"/>
+    <hyperlink ref="J13" r:id="rId58"/>
+    <hyperlink ref="J7" r:id="rId59"/>
+    <hyperlink ref="J8" r:id="rId60"/>
+    <hyperlink ref="K49" r:id="rId61"/>
+    <hyperlink ref="K43" r:id="rId62"/>
+    <hyperlink ref="K42" r:id="rId63"/>
+    <hyperlink ref="K40" r:id="rId64"/>
+    <hyperlink ref="K39" r:id="rId65"/>
+    <hyperlink ref="K38" r:id="rId66"/>
+    <hyperlink ref="K37" r:id="rId67"/>
+    <hyperlink ref="K35" r:id="rId68"/>
+    <hyperlink ref="K16" r:id="rId69"/>
+    <hyperlink ref="K5" r:id="rId70"/>
+    <hyperlink ref="K4" r:id="rId71"/>
+    <hyperlink ref="K45" r:id="rId72"/>
+    <hyperlink ref="K36" r:id="rId73"/>
+    <hyperlink ref="K20" r:id="rId74"/>
+    <hyperlink ref="K13" r:id="rId75"/>
+    <hyperlink ref="K12" r:id="rId76"/>
+    <hyperlink ref="K11" r:id="rId77"/>
+    <hyperlink ref="K10" r:id="rId78"/>
+    <hyperlink ref="K8" r:id="rId79"/>
+    <hyperlink ref="K22" r:id="rId80"/>
+    <hyperlink ref="K33" r:id="rId81"/>
+    <hyperlink ref="K31" r:id="rId82"/>
+    <hyperlink ref="K30" r:id="rId83"/>
+    <hyperlink ref="K29" r:id="rId84"/>
+    <hyperlink ref="K28" r:id="rId85"/>
+    <hyperlink ref="K47" r:id="rId86"/>
+    <hyperlink ref="K34" r:id="rId87"/>
+    <hyperlink ref="K2" r:id="rId88"/>
+    <hyperlink ref="K67" r:id="rId89" display="http://www.loteriamineira.mg.gov.br"/>
+    <hyperlink ref="K66" r:id="rId90" display="http://www.jucemg.mg.gov.br"/>
+    <hyperlink ref="K26" r:id="rId91" display="http://www.gabinetemilitar.mg.gov.br"/>
+    <hyperlink ref="K63" r:id="rId92"/>
+    <hyperlink ref="K62" r:id="rId93"/>
+    <hyperlink ref="K61" r:id="rId94"/>
+    <hyperlink ref="K60" r:id="rId95"/>
+    <hyperlink ref="K59" r:id="rId96"/>
+    <hyperlink ref="K58" r:id="rId97"/>
+    <hyperlink ref="K57" r:id="rId98"/>
+    <hyperlink ref="K56" r:id="rId99"/>
+    <hyperlink ref="K55" r:id="rId100"/>
+    <hyperlink ref="K64" r:id="rId101"/>
+    <hyperlink ref="K27" r:id="rId102"/>
+    <hyperlink ref="K48" r:id="rId103"/>
+    <hyperlink ref="H2" r:id="rId104"/>
+    <hyperlink ref="H4" r:id="rId105"/>
+    <hyperlink ref="H19" r:id="rId106"/>
+    <hyperlink ref="H25" r:id="rId107"/>
+    <hyperlink ref="H30" r:id="rId108"/>
+    <hyperlink ref="H33" r:id="rId109"/>
+    <hyperlink ref="H45" r:id="rId110"/>
+    <hyperlink ref="H6" r:id="rId111"/>
+    <hyperlink ref="H56" r:id="rId112"/>
+    <hyperlink ref="H44" r:id="rId113"/>
+    <hyperlink ref="K44" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId115"/>

--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="535">
   <si>
     <t>orgao</t>
   </si>
@@ -1630,6 +1630,9 @@
   </si>
   <si>
     <t>Alexandre Ramos Peixoto</t>
+  </si>
+  <si>
+    <t>Ilce Alves Rocha Perdigão</t>
   </si>
 </sst>
 </file>
@@ -2128,6 +2131,9 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
+      <c r="E3" t="s">
+        <v>534</v>
+      </c>
       <c r="F3" t="s">
         <v>209</v>
       </c>

--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -626,9 +626,6 @@
     <t>http://www.uemg.br</t>
   </si>
   <si>
-    <t>Lavínia Rosa Rodrigues</t>
-  </si>
-  <si>
     <t>http://www.loteriamineira.mg.gov.br</t>
   </si>
   <si>
@@ -1056,9 +1053,6 @@
     <t>Gleison Cunha Soares</t>
   </si>
   <si>
-    <t>Letícia Capistrano Campos</t>
-  </si>
-  <si>
     <t>Paulo Roberto Meireles do Nascimento</t>
   </si>
   <si>
@@ -1626,13 +1620,19 @@
     <t>Coronel Cleide Barcelos dos Reis Rodrigues</t>
   </si>
   <si>
-    <t>Gustavo de Marchi</t>
-  </si>
-  <si>
     <t>Alexandre Ramos Peixoto</t>
   </si>
   <si>
-    <t>Ilce Alves Rocha Perdigão</t>
+    <t>Gustavo de Marchi e Silva</t>
+  </si>
+  <si>
+    <t>Ana Luisa Silva Falcão</t>
+  </si>
+  <si>
+    <t>Vinícius de Abreu D'Ávila</t>
+  </si>
+  <si>
+    <t>Aguardando nomeação</t>
   </si>
 </sst>
 </file>
@@ -1668,12 +1668,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1689,7 +1695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1697,6 +1703,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -2040,11 +2047,11 @@
     <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.25" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="6" max="6" width="4.125" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="63.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="31.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2071,10 +2078,10 @@
         <v>193</v>
       </c>
       <c r="H1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="I1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J1" t="s">
         <v>128</v>
@@ -2085,7 +2092,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
@@ -2097,25 +2104,25 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>276</v>
+      <c r="K2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2131,26 +2138,26 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>534</v>
       </c>
       <c r="F3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>331</v>
+      <c r="K3" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2167,25 +2174,25 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" t="s">
         <v>232</v>
       </c>
-      <c r="F4" t="s">
-        <v>233</v>
-      </c>
       <c r="G4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>231</v>
+      <c r="K4" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="28.5">
@@ -2193,7 +2200,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -2202,33 +2209,33 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F5" t="s">
         <v>229</v>
       </c>
-      <c r="F5" t="s">
-        <v>230</v>
-      </c>
       <c r="G5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>228</v>
+      <c r="K5" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -2237,25 +2244,25 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
+        <v>479</v>
+      </c>
+      <c r="F6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G6" t="s">
+        <v>480</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="F6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
+        <v>359</v>
+      </c>
+      <c r="J6" t="s">
+        <v>507</v>
+      </c>
+      <c r="K6" t="s">
         <v>482</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="I6" t="s">
-        <v>361</v>
-      </c>
-      <c r="J6" t="s">
-        <v>509</v>
-      </c>
-      <c r="K6" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2272,25 +2279,25 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>333</v>
+      <c r="K7" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2307,33 +2314,33 @@
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="I8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>244</v>
+      <c r="K8" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B9" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -2342,25 +2349,25 @@
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F9" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G9">
         <v>117</v>
       </c>
       <c r="H9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2377,25 +2384,25 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H10" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="I10" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>249</v>
+      <c r="K10" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2412,25 +2419,25 @@
         <v>34</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G11" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>242</v>
+      <c r="K11" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2447,25 +2454,25 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G12" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>246</v>
+      <c r="K12" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2482,30 +2489,30 @@
         <v>34</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I13" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>243</v>
+      <c r="K13" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B14" t="s">
         <v>79</v>
@@ -2517,25 +2524,25 @@
         <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G14" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I14" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>334</v>
+      <c r="K14" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2552,25 +2559,25 @@
         <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I15" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>332</v>
+      <c r="K15" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2587,33 +2594,33 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G16" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H16" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I16" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>221</v>
+      <c r="K16" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -2622,25 +2629,25 @@
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G17">
         <v>155</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I17" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J17" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K17" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2657,25 +2664,25 @@
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G18" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I18" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>336</v>
+      <c r="K18" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2692,25 +2699,25 @@
         <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G19" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I19" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>337</v>
+      <c r="K19" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2727,25 +2734,25 @@
         <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G20" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H20" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="I20" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>238</v>
+      <c r="K20" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2762,25 +2769,25 @@
         <v>31</v>
       </c>
       <c r="E21" t="s">
+        <v>272</v>
+      </c>
+      <c r="F21" t="s">
         <v>273</v>
       </c>
-      <c r="F21" t="s">
-        <v>274</v>
-      </c>
       <c r="G21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>376</v>
+      <c r="K21" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2797,25 +2804,25 @@
         <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G22" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H22" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>226</v>
+      <c r="K22" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2832,25 +2839,25 @@
         <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G23" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I23" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>346</v>
+      <c r="K23" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2867,25 +2874,25 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G24" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H24" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I24" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>348</v>
+      <c r="K24" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2902,25 +2909,25 @@
         <v>71</v>
       </c>
       <c r="E25" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G25" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I25" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>338</v>
+      <c r="K25" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2937,25 +2944,25 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G26" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I26" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>263</v>
+      <c r="K26" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2972,30 +2979,30 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G27" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H27" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I27" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>317</v>
+      <c r="K27" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B28" t="s">
         <v>113</v>
@@ -3007,25 +3014,25 @@
         <v>6</v>
       </c>
       <c r="E28" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G28" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I28" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>261</v>
+      <c r="K28" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3042,25 +3049,25 @@
         <v>109</v>
       </c>
       <c r="E29" t="s">
+        <v>258</v>
+      </c>
+      <c r="F29" t="s">
         <v>259</v>
       </c>
-      <c r="F29" t="s">
-        <v>260</v>
-      </c>
       <c r="G29" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>225</v>
+      <c r="K29" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3077,25 +3084,25 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
+        <v>256</v>
+      </c>
+      <c r="F30" t="s">
         <v>257</v>
       </c>
-      <c r="F30" t="s">
-        <v>258</v>
-      </c>
       <c r="G30" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I30" t="s">
         <v>388</v>
-      </c>
-      <c r="I30" t="s">
-        <v>390</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>222</v>
+      <c r="K30" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3112,30 +3119,30 @@
         <v>109</v>
       </c>
       <c r="E31" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" t="s">
         <v>255</v>
       </c>
-      <c r="F31" t="s">
-        <v>256</v>
-      </c>
       <c r="G31" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I31" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>223</v>
+      <c r="K31" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="28.5">
       <c r="A32" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s">
         <v>74</v>
@@ -3147,25 +3154,25 @@
         <v>71</v>
       </c>
       <c r="E32" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G32" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H32" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I32" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>347</v>
+      <c r="K32" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3182,25 +3189,25 @@
         <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G33" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I33" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>224</v>
+      <c r="K33" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3217,25 +3224,25 @@
         <v>31</v>
       </c>
       <c r="E34" t="s">
+        <v>270</v>
+      </c>
+      <c r="F34" t="s">
         <v>271</v>
       </c>
-      <c r="F34" t="s">
-        <v>272</v>
-      </c>
       <c r="G34" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I34" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>270</v>
+      <c r="K34" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3252,25 +3259,25 @@
         <v>16</v>
       </c>
       <c r="E35" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" t="s">
         <v>219</v>
       </c>
-      <c r="F35" t="s">
-        <v>220</v>
-      </c>
       <c r="G35" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H35" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I35" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>218</v>
+      <c r="K35" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3287,25 +3294,25 @@
         <v>34</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G36" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H36" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I36" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>237</v>
+      <c r="K36" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3322,25 +3329,25 @@
         <v>26</v>
       </c>
       <c r="E37" t="s">
+        <v>215</v>
+      </c>
+      <c r="F37" t="s">
         <v>216</v>
       </c>
-      <c r="F37" t="s">
-        <v>217</v>
-      </c>
       <c r="G37" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H37" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I37" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>204</v>
+      <c r="K37" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3357,25 +3364,25 @@
         <v>26</v>
       </c>
       <c r="E38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H38" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I38" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>205</v>
+      <c r="K38" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3392,25 +3399,25 @@
         <v>31</v>
       </c>
       <c r="E39" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G39" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H39" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I39" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J39" t="s">
         <v>184</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>206</v>
+      <c r="K39" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3427,25 +3434,25 @@
         <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>342</v>
+        <v>532</v>
       </c>
       <c r="F40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G40" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H40" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I40" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>213</v>
+      <c r="K40" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3462,25 +3469,25 @@
         <v>23</v>
       </c>
       <c r="E41" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" t="s">
         <v>211</v>
       </c>
-      <c r="F41" t="s">
-        <v>212</v>
-      </c>
       <c r="G41" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H41" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I41" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>345</v>
+      <c r="K41" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3497,25 +3504,25 @@
         <v>6</v>
       </c>
       <c r="E42" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" t="s">
         <v>207</v>
       </c>
-      <c r="F42" t="s">
-        <v>208</v>
-      </c>
       <c r="G42" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H42" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I42" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>203</v>
+      <c r="K42" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3532,25 +3539,25 @@
         <v>34</v>
       </c>
       <c r="E43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G43" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H43" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I43" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>201</v>
+      <c r="K43" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3567,25 +3574,25 @@
         <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G44" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="I44" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>200</v>
+      <c r="K44" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3602,25 +3609,25 @@
         <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F45" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G45" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I45" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>235</v>
+      <c r="K45" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3637,25 +3644,25 @@
         <v>34</v>
       </c>
       <c r="E46" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G46" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H46" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I46" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>349</v>
+      <c r="K46" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3672,25 +3679,25 @@
         <v>31</v>
       </c>
       <c r="E47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F47" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G47" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H47" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I47" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>269</v>
+      <c r="K47" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -3707,25 +3714,25 @@
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G48" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I48" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>319</v>
+      <c r="K48" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3742,24 +3749,24 @@
         <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F49" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H49" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I49" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K49" t="s">
         <v>191</v>
       </c>
     </row>
@@ -3777,25 +3784,25 @@
         <v>31</v>
       </c>
       <c r="E50" t="s">
+        <v>301</v>
+      </c>
+      <c r="F50" t="s">
         <v>302</v>
       </c>
-      <c r="F50" t="s">
-        <v>303</v>
-      </c>
       <c r="G50" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H50" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I50" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>353</v>
+      <c r="K50" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3812,25 +3819,25 @@
         <v>31</v>
       </c>
       <c r="E51" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G51" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H51" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I51" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>352</v>
+      <c r="K51" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3847,25 +3854,25 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F52" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G52" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H52" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I52" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>300</v>
+      <c r="K52" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3882,25 +3889,25 @@
         <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F53" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G53" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H53" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>351</v>
+      <c r="K53" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3917,25 +3924,25 @@
         <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G54" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H54" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I54" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="K54" s="2" t="s">
-        <v>318</v>
+      <c r="K54" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -3952,25 +3959,25 @@
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F55" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G55" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H55" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I55" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>297</v>
+      <c r="K55" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3987,25 +3994,25 @@
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F56" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G56" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I56" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>295</v>
+      <c r="K56" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4022,25 +4029,25 @@
         <v>31</v>
       </c>
       <c r="E57" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G57" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H57" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I57" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="K57" s="2" t="s">
-        <v>293</v>
+      <c r="K57" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4057,25 +4064,25 @@
         <v>31</v>
       </c>
       <c r="E58" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F58" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G58" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H58" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I58" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>291</v>
+      <c r="K58" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4092,25 +4099,25 @@
         <v>31</v>
       </c>
       <c r="E59" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G59" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H59" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="I59" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>290</v>
+      <c r="K59" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4127,25 +4134,25 @@
         <v>31</v>
       </c>
       <c r="E60" t="s">
+        <v>285</v>
+      </c>
+      <c r="F60" t="s">
         <v>286</v>
       </c>
-      <c r="F60" t="s">
-        <v>287</v>
-      </c>
       <c r="G60" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H60" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I60" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="K60" s="2" t="s">
-        <v>285</v>
+      <c r="K60" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4162,25 +4169,25 @@
         <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G61" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H61" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I61" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>282</v>
+      <c r="K61" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4197,25 +4204,25 @@
         <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F62" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G62" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H62" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I62" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="K62" s="2" t="s">
-        <v>281</v>
+      <c r="K62" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -4232,30 +4239,30 @@
         <v>31</v>
       </c>
       <c r="E63" t="s">
+        <v>278</v>
+      </c>
+      <c r="F63" t="s">
         <v>279</v>
       </c>
-      <c r="F63" t="s">
-        <v>280</v>
-      </c>
       <c r="G63" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H63" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I63" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K63" s="2" t="s">
-        <v>278</v>
+      <c r="K63" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B64" t="s">
         <v>110</v>
@@ -4267,33 +4274,33 @@
         <v>31</v>
       </c>
       <c r="E64" t="s">
+        <v>423</v>
+      </c>
+      <c r="F64" t="s">
+        <v>300</v>
+      </c>
+      <c r="G64" t="s">
         <v>425</v>
       </c>
-      <c r="F64" t="s">
-        <v>301</v>
-      </c>
-      <c r="G64" t="s">
-        <v>427</v>
-      </c>
       <c r="H64" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I64" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="K64" s="2" t="s">
-        <v>304</v>
+      <c r="K64" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B65" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C65" t="s">
         <v>44</v>
@@ -4302,25 +4309,25 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G65" t="s">
+        <v>485</v>
+      </c>
+      <c r="H65" t="s">
         <v>487</v>
       </c>
-      <c r="H65" t="s">
-        <v>489</v>
-      </c>
       <c r="I65" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J65" t="s">
         <v>163</v>
       </c>
       <c r="K65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -4337,24 +4344,24 @@
         <v>39</v>
       </c>
       <c r="E66" t="s">
-        <v>199</v>
+        <v>533</v>
       </c>
       <c r="F66" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G66" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H66" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I66" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="K66" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4378,18 +4385,18 @@
         <v>197</v>
       </c>
       <c r="G67" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H67" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I67" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J67" t="s">
         <v>143</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="K67" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4488,32 +4495,32 @@
     <hyperlink ref="K47" r:id="rId86"/>
     <hyperlink ref="K34" r:id="rId87"/>
     <hyperlink ref="K2" r:id="rId88"/>
-    <hyperlink ref="K67" r:id="rId89" display="http://www.loteriamineira.mg.gov.br"/>
-    <hyperlink ref="K66" r:id="rId90" display="http://www.jucemg.mg.gov.br"/>
-    <hyperlink ref="K26" r:id="rId91" display="http://www.gabinetemilitar.mg.gov.br"/>
-    <hyperlink ref="K63" r:id="rId92"/>
-    <hyperlink ref="K62" r:id="rId93"/>
-    <hyperlink ref="K61" r:id="rId94"/>
-    <hyperlink ref="K60" r:id="rId95"/>
-    <hyperlink ref="K59" r:id="rId96"/>
-    <hyperlink ref="K58" r:id="rId97"/>
-    <hyperlink ref="K57" r:id="rId98"/>
-    <hyperlink ref="K56" r:id="rId99"/>
-    <hyperlink ref="K55" r:id="rId100"/>
-    <hyperlink ref="K64" r:id="rId101"/>
-    <hyperlink ref="K27" r:id="rId102"/>
-    <hyperlink ref="K48" r:id="rId103"/>
-    <hyperlink ref="H2" r:id="rId104"/>
-    <hyperlink ref="H4" r:id="rId105"/>
-    <hyperlink ref="H19" r:id="rId106"/>
-    <hyperlink ref="H25" r:id="rId107"/>
-    <hyperlink ref="H30" r:id="rId108"/>
-    <hyperlink ref="H33" r:id="rId109"/>
-    <hyperlink ref="H45" r:id="rId110"/>
-    <hyperlink ref="H6" r:id="rId111"/>
-    <hyperlink ref="H56" r:id="rId112"/>
-    <hyperlink ref="H44" r:id="rId113"/>
-    <hyperlink ref="K44" r:id="rId114"/>
+    <hyperlink ref="K66" r:id="rId89" display="http://www.jucemg.mg.gov.br"/>
+    <hyperlink ref="K26" r:id="rId90" display="http://www.gabinetemilitar.mg.gov.br"/>
+    <hyperlink ref="K63" r:id="rId91"/>
+    <hyperlink ref="K62" r:id="rId92"/>
+    <hyperlink ref="K61" r:id="rId93"/>
+    <hyperlink ref="K60" r:id="rId94"/>
+    <hyperlink ref="K59" r:id="rId95"/>
+    <hyperlink ref="K58" r:id="rId96"/>
+    <hyperlink ref="K57" r:id="rId97"/>
+    <hyperlink ref="K56" r:id="rId98"/>
+    <hyperlink ref="K55" r:id="rId99"/>
+    <hyperlink ref="K64" r:id="rId100"/>
+    <hyperlink ref="K27" r:id="rId101"/>
+    <hyperlink ref="K48" r:id="rId102"/>
+    <hyperlink ref="H2" r:id="rId103"/>
+    <hyperlink ref="H4" r:id="rId104"/>
+    <hyperlink ref="H19" r:id="rId105"/>
+    <hyperlink ref="H25" r:id="rId106"/>
+    <hyperlink ref="H30" r:id="rId107"/>
+    <hyperlink ref="H33" r:id="rId108"/>
+    <hyperlink ref="H45" r:id="rId109"/>
+    <hyperlink ref="H6" r:id="rId110"/>
+    <hyperlink ref="H56" r:id="rId111"/>
+    <hyperlink ref="H44" r:id="rId112"/>
+    <hyperlink ref="K44" r:id="rId113"/>
+    <hyperlink ref="K67" r:id="rId114" display="http://www.loteriamineira.mg.gov.br"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId115"/>

--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -1587,9 +1587,6 @@
     <t>Luciana Mundim de Mattos Paixão</t>
   </si>
   <si>
-    <t>Castellar Modesto Guimarães Neto</t>
-  </si>
-  <si>
     <t>Milena Pedrosa</t>
   </si>
   <si>
@@ -1633,6 +1630,9 @@
   </si>
   <si>
     <t>Aguardando nomeação</t>
+  </si>
+  <si>
+    <t>Juliano Fisicaro Borges</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2139,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F3" t="s">
         <v>208</v>
@@ -2302,45 +2302,45 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="F8" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="G8" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="H8" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="I8" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="K8" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>403</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -2349,68 +2349,68 @@
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F9" t="s">
-        <v>483</v>
-      </c>
-      <c r="G9">
-        <v>117</v>
+        <v>244</v>
+      </c>
+      <c r="G9" t="s">
+        <v>460</v>
       </c>
       <c r="H9" t="s">
-        <v>484</v>
+        <v>365</v>
       </c>
       <c r="I9" t="s">
-        <v>359</v>
-      </c>
-      <c r="J9" t="s">
-        <v>509</v>
+        <v>355</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="K9" t="s">
-        <v>405</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>323</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>528</v>
+        <v>308</v>
       </c>
       <c r="F10" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="G10" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="H10" t="s">
-        <v>506</v>
+        <v>366</v>
       </c>
       <c r="I10" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="K10" t="s">
-        <v>248</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>44</v>
@@ -2418,69 +2418,69 @@
       <c r="D11" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>282</v>
+      <c r="E11" t="s">
+        <v>310</v>
       </c>
       <c r="F11" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G11" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="H11" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="I11" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="K11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>314</v>
+        <v>527</v>
       </c>
       <c r="F12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G12" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="H12" t="s">
-        <v>364</v>
+        <v>506</v>
       </c>
       <c r="I12" t="s">
         <v>355</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
@@ -2489,173 +2489,173 @@
         <v>34</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>530</v>
+        <v>282</v>
       </c>
       <c r="F13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G13" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="H13" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I13" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="K13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>323</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="F14" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G14" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="H14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I14" t="s">
         <v>359</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="K14" t="s">
-        <v>333</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>396</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>395</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>338</v>
+        <v>415</v>
       </c>
       <c r="F15" t="s">
-        <v>226</v>
-      </c>
-      <c r="G15" t="s">
-        <v>442</v>
-      </c>
-      <c r="H15" t="s">
-        <v>367</v>
+        <v>416</v>
+      </c>
+      <c r="G15">
+        <v>155</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>417</v>
       </c>
       <c r="I15" t="s">
-        <v>355</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>170</v>
+        <v>359</v>
+      </c>
+      <c r="J15" t="s">
+        <v>508</v>
       </c>
       <c r="K15" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>334</v>
+        <v>513</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G16" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="K16" t="s">
-        <v>220</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>396</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>395</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>415</v>
+        <v>514</v>
       </c>
       <c r="F17" t="s">
-        <v>416</v>
-      </c>
-      <c r="G17">
-        <v>155</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>417</v>
+        <v>238</v>
+      </c>
+      <c r="G17" t="s">
+        <v>468</v>
+      </c>
+      <c r="H17" t="s">
+        <v>371</v>
       </c>
       <c r="I17" t="s">
         <v>359</v>
       </c>
-      <c r="J17" t="s">
-        <v>508</v>
+      <c r="J17" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="K17" t="s">
-        <v>397</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
         <v>44</v>
@@ -2664,305 +2664,305 @@
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>513</v>
+        <v>311</v>
       </c>
       <c r="F18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G18" t="s">
-        <v>465</v>
-      </c>
-      <c r="H18" t="s">
-        <v>370</v>
+        <v>462</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="I18" t="s">
         <v>355</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K18" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="F19" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="G19" t="s">
-        <v>462</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>369</v>
+        <v>469</v>
+      </c>
+      <c r="H19" t="s">
+        <v>375</v>
       </c>
       <c r="I19" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="K19" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F20" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="G20" t="s">
-        <v>468</v>
-      </c>
-      <c r="H20" t="s">
-        <v>371</v>
+        <v>458</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="I20" t="s">
         <v>359</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K20" t="s">
-        <v>237</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="F21" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="G21" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H21" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I21" t="s">
-        <v>359</v>
+        <v>411</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="K21" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
         <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>339</v>
+        <v>521</v>
       </c>
       <c r="F22" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="G22" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="H22" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I22" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="K22" t="s">
-        <v>225</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>325</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
         <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F23" t="s">
-        <v>266</v>
+        <v>207</v>
       </c>
       <c r="G23" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="H23" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="I23" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="K23" t="s">
-        <v>344</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
         <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="F24" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="G24" t="s">
-        <v>470</v>
-      </c>
-      <c r="H24" t="s">
-        <v>379</v>
+        <v>459</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="I24" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K24" t="s">
-        <v>346</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>515</v>
+        <v>254</v>
       </c>
       <c r="F25" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="G25" t="s">
-        <v>458</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>380</v>
+        <v>472</v>
+      </c>
+      <c r="H25" t="s">
+        <v>389</v>
       </c>
       <c r="I25" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="K25" t="s">
-        <v>337</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
         <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="F26" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="G26" t="s">
-        <v>471</v>
-      </c>
-      <c r="H26" t="s">
-        <v>381</v>
+        <v>463</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="I26" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K26" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3002,115 +3002,115 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>325</v>
+        <v>122</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
         <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>526</v>
+        <v>258</v>
       </c>
       <c r="F28" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="G28" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="H28" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I28" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="K28" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>403</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>404</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" t="s">
-        <v>258</v>
+        <v>34</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>530</v>
       </c>
       <c r="F29" t="s">
-        <v>259</v>
-      </c>
-      <c r="G29" t="s">
-        <v>428</v>
+        <v>483</v>
+      </c>
+      <c r="G29">
+        <v>117</v>
       </c>
       <c r="H29" t="s">
-        <v>385</v>
+        <v>484</v>
       </c>
       <c r="I29" t="s">
-        <v>355</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>175</v>
+        <v>359</v>
+      </c>
+      <c r="J29" t="s">
+        <v>509</v>
       </c>
       <c r="K29" t="s">
-        <v>224</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E30" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="F30" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="G30" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I30" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="K30" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
         <v>70</v>
@@ -3119,243 +3119,243 @@
         <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>254</v>
+        <v>339</v>
       </c>
       <c r="F31" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G31" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="H31" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="I31" t="s">
+        <v>376</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K31" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>218</v>
+      </c>
+      <c r="F32" t="s">
+        <v>219</v>
+      </c>
+      <c r="G32" t="s">
+        <v>320</v>
+      </c>
+      <c r="H32" t="s">
+        <v>392</v>
+      </c>
+      <c r="I32" t="s">
         <v>355</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K31" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="28.5">
-      <c r="A32" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" t="s">
-        <v>341</v>
-      </c>
-      <c r="F32" t="s">
-        <v>252</v>
-      </c>
-      <c r="G32" t="s">
-        <v>475</v>
-      </c>
-      <c r="H32" t="s">
-        <v>409</v>
-      </c>
-      <c r="I32" t="s">
-        <v>359</v>
-      </c>
       <c r="J32" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="K32" t="s">
-        <v>345</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" t="s">
+        <v>531</v>
+      </c>
+      <c r="F33" t="s">
+        <v>207</v>
+      </c>
+      <c r="G33" t="s">
+        <v>456</v>
+      </c>
+      <c r="H33" t="s">
+        <v>497</v>
+      </c>
+      <c r="I33" t="s">
+        <v>359</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K33" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="28.5">
+      <c r="A34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
         <v>70</v>
       </c>
-      <c r="D33" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" t="s">
-        <v>305</v>
-      </c>
-      <c r="F33" t="s">
-        <v>253</v>
-      </c>
-      <c r="G33" t="s">
-        <v>463</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="I33" t="s">
-        <v>410</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" t="s">
-        <v>76</v>
-      </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
       <c r="F34" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="G34" t="s">
-        <v>450</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>391</v>
+        <v>475</v>
+      </c>
+      <c r="H34" t="s">
+        <v>409</v>
       </c>
       <c r="I34" t="s">
         <v>359</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="K34" t="s">
-        <v>269</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E35" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F35" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="G35" t="s">
-        <v>320</v>
+        <v>454</v>
       </c>
       <c r="H35" t="s">
-        <v>392</v>
+        <v>499</v>
       </c>
       <c r="I35" t="s">
         <v>355</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="K35" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>520</v>
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>210</v>
       </c>
       <c r="F36" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G36" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="H36" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="I36" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="K36" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" t="s">
-        <v>215</v>
+        <v>34</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>519</v>
       </c>
       <c r="F37" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G37" t="s">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="H37" t="s">
-        <v>496</v>
+        <v>393</v>
       </c>
       <c r="I37" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K37" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -3364,235 +3364,235 @@
         <v>26</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F38" t="s">
-        <v>326</v>
+        <v>216</v>
       </c>
       <c r="G38" t="s">
-        <v>321</v>
+        <v>464</v>
       </c>
       <c r="H38" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I38" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>342</v>
+        <v>214</v>
       </c>
       <c r="F39" t="s">
-        <v>213</v>
+        <v>326</v>
       </c>
       <c r="G39" t="s">
-        <v>441</v>
+        <v>321</v>
       </c>
       <c r="H39" t="s">
-        <v>387</v>
+        <v>500</v>
       </c>
       <c r="I39" t="s">
         <v>382</v>
       </c>
-      <c r="J39" t="s">
-        <v>184</v>
+      <c r="J39" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="K39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>532</v>
+        <v>342</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G40" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="H40" t="s">
-        <v>497</v>
+        <v>387</v>
       </c>
       <c r="I40" t="s">
-        <v>359</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>156</v>
+        <v>382</v>
+      </c>
+      <c r="J40" t="s">
+        <v>184</v>
       </c>
       <c r="K40" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>210</v>
+        <v>306</v>
       </c>
       <c r="F41" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G41" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="H41" t="s">
-        <v>398</v>
+        <v>494</v>
       </c>
       <c r="I41" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K41" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>522</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G42" t="s">
-        <v>454</v>
-      </c>
-      <c r="H42" t="s">
-        <v>499</v>
+        <v>430</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>511</v>
       </c>
       <c r="I42" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="K42" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>407</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>408</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="F43" t="s">
-        <v>201</v>
+        <v>287</v>
       </c>
       <c r="G43" t="s">
-        <v>418</v>
+        <v>485</v>
       </c>
       <c r="H43" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="I43" t="s">
-        <v>382</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>151</v>
+        <v>355</v>
+      </c>
+      <c r="J43" t="s">
+        <v>163</v>
       </c>
       <c r="K43" t="s">
-        <v>200</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
         <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F44" t="s">
-        <v>208</v>
+        <v>326</v>
       </c>
       <c r="G44" t="s">
-        <v>430</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>511</v>
+        <v>448</v>
+      </c>
+      <c r="H44" t="s">
+        <v>503</v>
       </c>
       <c r="I44" t="s">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="K44" t="s">
-        <v>199</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3632,45 +3632,45 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D46" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>521</v>
+        <v>304</v>
       </c>
       <c r="F46" t="s">
-        <v>326</v>
+        <v>274</v>
       </c>
       <c r="G46" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="H46" t="s">
-        <v>503</v>
+        <v>413</v>
       </c>
       <c r="I46" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="K46" t="s">
-        <v>347</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
         <v>76</v>
@@ -3679,33 +3679,33 @@
         <v>31</v>
       </c>
       <c r="E47" t="s">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="F47" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="G47" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="H47" t="s">
-        <v>413</v>
+        <v>510</v>
       </c>
       <c r="I47" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K47" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
         <v>76</v>
@@ -3714,68 +3714,68 @@
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>348</v>
+        <v>528</v>
       </c>
       <c r="F48" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="G48" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H48" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="I48" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K48" t="s">
-        <v>318</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="F49" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="G49" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="H49" t="s">
-        <v>493</v>
+        <v>364</v>
       </c>
       <c r="I49" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="K49" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
         <v>92</v>
@@ -3784,33 +3784,33 @@
         <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>301</v>
+        <v>523</v>
       </c>
       <c r="F50" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G50" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="H50" t="s">
-        <v>504</v>
+        <v>419</v>
       </c>
       <c r="I50" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="K50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
         <v>92</v>
@@ -3819,25 +3819,25 @@
         <v>31</v>
       </c>
       <c r="E51" t="s">
-        <v>524</v>
+        <v>301</v>
       </c>
       <c r="F51" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G51" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="H51" t="s">
-        <v>419</v>
+        <v>504</v>
       </c>
       <c r="I51" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3959,7 +3959,7 @@
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F55" t="s">
         <v>297</v>
@@ -3994,7 +3994,7 @@
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F56" t="s">
         <v>295</v>
@@ -4064,7 +4064,7 @@
         <v>31</v>
       </c>
       <c r="E58" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="F58" t="s">
         <v>291</v>
@@ -4297,45 +4297,45 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>407</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>288</v>
+        <v>532</v>
       </c>
       <c r="F65" t="s">
-        <v>287</v>
+        <v>209</v>
       </c>
       <c r="G65" t="s">
-        <v>485</v>
+        <v>436</v>
       </c>
       <c r="H65" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="I65" t="s">
-        <v>355</v>
-      </c>
-      <c r="J65" t="s">
-        <v>163</v>
+        <v>360</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="K65" t="s">
-        <v>289</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -4344,159 +4344,159 @@
         <v>39</v>
       </c>
       <c r="E66" t="s">
-        <v>533</v>
+        <v>195</v>
       </c>
       <c r="F66" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="G66" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="H66" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="I66" t="s">
-        <v>360</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>180</v>
+        <v>372</v>
+      </c>
+      <c r="J66" t="s">
+        <v>143</v>
       </c>
       <c r="K66" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="B67" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="F67" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="G67" t="s">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="H67" t="s">
-        <v>488</v>
+        <v>381</v>
       </c>
       <c r="I67" t="s">
-        <v>372</v>
-      </c>
-      <c r="J67" t="s">
-        <v>143</v>
+        <v>373</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="K67" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K67">
-      <sortCondition ref="A1"/>
+      <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="J64" r:id="rId1"/>
-    <hyperlink ref="J50" r:id="rId2"/>
+    <hyperlink ref="J51" r:id="rId2"/>
     <hyperlink ref="J54" r:id="rId3"/>
-    <hyperlink ref="J32" r:id="rId4"/>
-    <hyperlink ref="J23" r:id="rId5"/>
-    <hyperlink ref="J25" r:id="rId6"/>
+    <hyperlink ref="J34" r:id="rId4"/>
+    <hyperlink ref="J22" r:id="rId5"/>
+    <hyperlink ref="J20" r:id="rId6"/>
     <hyperlink ref="J53" r:id="rId7"/>
-    <hyperlink ref="J20" r:id="rId8"/>
+    <hyperlink ref="J17" r:id="rId8"/>
     <hyperlink ref="J52" r:id="rId9"/>
-    <hyperlink ref="J51" r:id="rId10"/>
-    <hyperlink ref="J41" r:id="rId11"/>
-    <hyperlink ref="J19" r:id="rId12"/>
-    <hyperlink ref="J18" r:id="rId13"/>
+    <hyperlink ref="J50" r:id="rId10"/>
+    <hyperlink ref="J36" r:id="rId11"/>
+    <hyperlink ref="J18" r:id="rId12"/>
+    <hyperlink ref="J16" r:id="rId13"/>
     <hyperlink ref="J27" r:id="rId14"/>
-    <hyperlink ref="J30" r:id="rId15"/>
+    <hyperlink ref="J24" r:id="rId15"/>
     <hyperlink ref="J56" r:id="rId16"/>
-    <hyperlink ref="J26" r:id="rId17"/>
-    <hyperlink ref="J35" r:id="rId18"/>
+    <hyperlink ref="J67" r:id="rId17"/>
+    <hyperlink ref="J32" r:id="rId18"/>
     <hyperlink ref="J55" r:id="rId19"/>
-    <hyperlink ref="J44" r:id="rId20"/>
-    <hyperlink ref="J43" r:id="rId21"/>
-    <hyperlink ref="J24" r:id="rId22"/>
-    <hyperlink ref="J11" r:id="rId23"/>
-    <hyperlink ref="J33" r:id="rId24"/>
+    <hyperlink ref="J42" r:id="rId20"/>
+    <hyperlink ref="J41" r:id="rId21"/>
+    <hyperlink ref="J21" r:id="rId22"/>
+    <hyperlink ref="J13" r:id="rId23"/>
+    <hyperlink ref="J26" r:id="rId24"/>
     <hyperlink ref="J62" r:id="rId25"/>
-    <hyperlink ref="J40" r:id="rId26"/>
-    <hyperlink ref="J28" r:id="rId27"/>
+    <hyperlink ref="J33" r:id="rId26"/>
+    <hyperlink ref="J23" r:id="rId27"/>
     <hyperlink ref="J5" r:id="rId28"/>
     <hyperlink ref="J61" r:id="rId29"/>
     <hyperlink ref="J60" r:id="rId30"/>
     <hyperlink ref="J3" r:id="rId31"/>
-    <hyperlink ref="J16" r:id="rId32"/>
+    <hyperlink ref="J14" r:id="rId32"/>
     <hyperlink ref="J59" r:id="rId33"/>
     <hyperlink ref="J58" r:id="rId34"/>
     <hyperlink ref="J57" r:id="rId35"/>
-    <hyperlink ref="J21" r:id="rId36"/>
-    <hyperlink ref="J49" r:id="rId37"/>
-    <hyperlink ref="J48" r:id="rId38"/>
-    <hyperlink ref="J34" r:id="rId39"/>
-    <hyperlink ref="J15" r:id="rId40"/>
-    <hyperlink ref="J47" r:id="rId41"/>
-    <hyperlink ref="J14" r:id="rId42"/>
+    <hyperlink ref="J19" r:id="rId36"/>
+    <hyperlink ref="J48" r:id="rId37"/>
+    <hyperlink ref="J47" r:id="rId38"/>
+    <hyperlink ref="J30" r:id="rId39"/>
+    <hyperlink ref="J8" r:id="rId40"/>
+    <hyperlink ref="J46" r:id="rId41"/>
+    <hyperlink ref="J10" r:id="rId42"/>
     <hyperlink ref="J2" r:id="rId43"/>
-    <hyperlink ref="J31" r:id="rId44"/>
-    <hyperlink ref="J29" r:id="rId45"/>
-    <hyperlink ref="J22" r:id="rId46"/>
+    <hyperlink ref="J25" r:id="rId44"/>
+    <hyperlink ref="J28" r:id="rId45"/>
+    <hyperlink ref="J31" r:id="rId46"/>
     <hyperlink ref="J63" r:id="rId47"/>
-    <hyperlink ref="J37" r:id="rId48"/>
-    <hyperlink ref="J38" r:id="rId49"/>
-    <hyperlink ref="J66" r:id="rId50"/>
-    <hyperlink ref="J12" r:id="rId51" location="texto"/>
+    <hyperlink ref="J38" r:id="rId48"/>
+    <hyperlink ref="J39" r:id="rId49"/>
+    <hyperlink ref="J65" r:id="rId50"/>
+    <hyperlink ref="J49" r:id="rId51" location="texto"/>
     <hyperlink ref="J45" r:id="rId52"/>
-    <hyperlink ref="J46" r:id="rId53"/>
-    <hyperlink ref="J36" r:id="rId54"/>
-    <hyperlink ref="J42" r:id="rId55"/>
+    <hyperlink ref="J44" r:id="rId53"/>
+    <hyperlink ref="J37" r:id="rId54"/>
+    <hyperlink ref="J35" r:id="rId55"/>
     <hyperlink ref="J4" r:id="rId56"/>
-    <hyperlink ref="J10" r:id="rId57"/>
-    <hyperlink ref="J13" r:id="rId58"/>
+    <hyperlink ref="J12" r:id="rId57"/>
+    <hyperlink ref="J9" r:id="rId58"/>
     <hyperlink ref="J7" r:id="rId59"/>
-    <hyperlink ref="J8" r:id="rId60"/>
-    <hyperlink ref="K49" r:id="rId61"/>
-    <hyperlink ref="K43" r:id="rId62"/>
-    <hyperlink ref="K42" r:id="rId63"/>
-    <hyperlink ref="K40" r:id="rId64"/>
-    <hyperlink ref="K39" r:id="rId65"/>
-    <hyperlink ref="K38" r:id="rId66"/>
-    <hyperlink ref="K37" r:id="rId67"/>
-    <hyperlink ref="K35" r:id="rId68"/>
-    <hyperlink ref="K16" r:id="rId69"/>
+    <hyperlink ref="J11" r:id="rId60"/>
+    <hyperlink ref="K48" r:id="rId61"/>
+    <hyperlink ref="K41" r:id="rId62"/>
+    <hyperlink ref="K35" r:id="rId63"/>
+    <hyperlink ref="K33" r:id="rId64"/>
+    <hyperlink ref="K40" r:id="rId65"/>
+    <hyperlink ref="K39" r:id="rId66"/>
+    <hyperlink ref="K38" r:id="rId67"/>
+    <hyperlink ref="K32" r:id="rId68"/>
+    <hyperlink ref="K14" r:id="rId69"/>
     <hyperlink ref="K5" r:id="rId70"/>
     <hyperlink ref="K4" r:id="rId71"/>
     <hyperlink ref="K45" r:id="rId72"/>
-    <hyperlink ref="K36" r:id="rId73"/>
-    <hyperlink ref="K20" r:id="rId74"/>
-    <hyperlink ref="K13" r:id="rId75"/>
-    <hyperlink ref="K12" r:id="rId76"/>
-    <hyperlink ref="K11" r:id="rId77"/>
-    <hyperlink ref="K10" r:id="rId78"/>
-    <hyperlink ref="K8" r:id="rId79"/>
-    <hyperlink ref="K22" r:id="rId80"/>
-    <hyperlink ref="K33" r:id="rId81"/>
-    <hyperlink ref="K31" r:id="rId82"/>
-    <hyperlink ref="K30" r:id="rId83"/>
-    <hyperlink ref="K29" r:id="rId84"/>
-    <hyperlink ref="K28" r:id="rId85"/>
-    <hyperlink ref="K47" r:id="rId86"/>
-    <hyperlink ref="K34" r:id="rId87"/>
+    <hyperlink ref="K37" r:id="rId73"/>
+    <hyperlink ref="K17" r:id="rId74"/>
+    <hyperlink ref="K9" r:id="rId75"/>
+    <hyperlink ref="K49" r:id="rId76"/>
+    <hyperlink ref="K13" r:id="rId77"/>
+    <hyperlink ref="K12" r:id="rId78"/>
+    <hyperlink ref="K11" r:id="rId79"/>
+    <hyperlink ref="K31" r:id="rId80"/>
+    <hyperlink ref="K26" r:id="rId81"/>
+    <hyperlink ref="K25" r:id="rId82"/>
+    <hyperlink ref="K24" r:id="rId83"/>
+    <hyperlink ref="K28" r:id="rId84"/>
+    <hyperlink ref="K23" r:id="rId85"/>
+    <hyperlink ref="K46" r:id="rId86"/>
+    <hyperlink ref="K30" r:id="rId87"/>
     <hyperlink ref="K2" r:id="rId88"/>
-    <hyperlink ref="K66" r:id="rId89" display="http://www.jucemg.mg.gov.br"/>
-    <hyperlink ref="K26" r:id="rId90" display="http://www.gabinetemilitar.mg.gov.br"/>
+    <hyperlink ref="K65" r:id="rId89" display="http://www.jucemg.mg.gov.br"/>
+    <hyperlink ref="K67" r:id="rId90" display="http://www.gabinetemilitar.mg.gov.br"/>
     <hyperlink ref="K63" r:id="rId91"/>
     <hyperlink ref="K62" r:id="rId92"/>
     <hyperlink ref="K61" r:id="rId93"/>
@@ -4508,19 +4508,19 @@
     <hyperlink ref="K55" r:id="rId99"/>
     <hyperlink ref="K64" r:id="rId100"/>
     <hyperlink ref="K27" r:id="rId101"/>
-    <hyperlink ref="K48" r:id="rId102"/>
+    <hyperlink ref="K47" r:id="rId102"/>
     <hyperlink ref="H2" r:id="rId103"/>
     <hyperlink ref="H4" r:id="rId104"/>
-    <hyperlink ref="H19" r:id="rId105"/>
-    <hyperlink ref="H25" r:id="rId106"/>
-    <hyperlink ref="H30" r:id="rId107"/>
-    <hyperlink ref="H33" r:id="rId108"/>
+    <hyperlink ref="H18" r:id="rId105"/>
+    <hyperlink ref="H20" r:id="rId106"/>
+    <hyperlink ref="H24" r:id="rId107"/>
+    <hyperlink ref="H26" r:id="rId108"/>
     <hyperlink ref="H45" r:id="rId109"/>
     <hyperlink ref="H6" r:id="rId110"/>
     <hyperlink ref="H56" r:id="rId111"/>
-    <hyperlink ref="H44" r:id="rId112"/>
-    <hyperlink ref="K44" r:id="rId113"/>
-    <hyperlink ref="K67" r:id="rId114" display="http://www.loteriamineira.mg.gov.br"/>
+    <hyperlink ref="H42" r:id="rId112"/>
+    <hyperlink ref="K42" r:id="rId113"/>
+    <hyperlink ref="K66" r:id="rId114" display="http://www.loteriamineira.mg.gov.br"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId115"/>

--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -1608,9 +1608,6 @@
     <t>Renato Teixeira Brandão</t>
   </si>
   <si>
-    <t>Gustavo Oliveira Braga de Souza</t>
-  </si>
-  <si>
     <t>José Bonifácio Couto de Andrada</t>
   </si>
   <si>
@@ -1633,6 +1630,9 @@
   </si>
   <si>
     <t>Juliano Fisicaro Borges</t>
+  </si>
+  <si>
+    <t>Daniel Guimarães Medrado de Castro</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2139,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F3" t="s">
         <v>208</v>
@@ -2349,7 +2349,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F9" t="s">
         <v>244</v>
@@ -2454,7 +2454,7 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F12" t="s">
         <v>249</v>
@@ -3049,7 +3049,7 @@
         <v>34</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F29" t="s">
         <v>483</v>
@@ -3189,7 +3189,7 @@
         <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F33" t="s">
         <v>207</v>
@@ -3714,7 +3714,7 @@
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F48" t="s">
         <v>213</v>
@@ -3994,7 +3994,7 @@
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="F56" t="s">
         <v>295</v>
@@ -4064,7 +4064,7 @@
         <v>31</v>
       </c>
       <c r="E58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F58" t="s">
         <v>291</v>
@@ -4309,7 +4309,7 @@
         <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F65" t="s">
         <v>209</v>

--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="535">
   <si>
     <t>orgao</t>
   </si>
@@ -672,9 +672,6 @@
   </si>
   <si>
     <t>André Luiz Moreira dos Anjos</t>
-  </si>
-  <si>
-    <t>Francisco José da Fonseca</t>
   </si>
   <si>
     <t>Rua Cristiano França Teixeira Guimarães, 80, Cinco, Contagem, 32010-130</t>
@@ -1275,9 +1272,6 @@
     <t>gabsecom@governo.mg.gov.br</t>
   </si>
   <si>
-    <t>Rone Evaldo Barbosa</t>
-  </si>
-  <si>
     <t>3º andar do Edifício Gerais - Cidade Administrativa, Belo Horizonte</t>
   </si>
   <si>
@@ -1572,9 +1566,6 @@
     <t>Cláudio Augusto Bortolini</t>
   </si>
   <si>
-    <t>Ike Yagelovic</t>
-  </si>
-  <si>
     <t>Rodrigo César Câmara Baia</t>
   </si>
   <si>
@@ -1629,17 +1620,26 @@
     <t>Aguardando nomeação</t>
   </si>
   <si>
-    <t>Juliano Fisicaro Borges</t>
-  </si>
-  <si>
     <t>Daniel Guimarães Medrado de Castro</t>
+  </si>
+  <si>
+    <t>Renato Rezende</t>
+  </si>
+  <si>
+    <t>José dos Passos Teixeira de Andrade</t>
+  </si>
+  <si>
+    <t>Luiz Henrique Yagelovic</t>
+  </si>
+  <si>
+    <t>https://www.secult.mg.gov.br/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1662,6 +1662,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1695,7 +1702,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1704,6 +1711,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -2039,23 +2047,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="66.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.25" customWidth="1"/>
-    <col min="6" max="6" width="4.125" customWidth="1"/>
-    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="63.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.125" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="63.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2072,27 +2081,30 @@
         <v>194</v>
       </c>
       <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
         <v>192</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>193</v>
       </c>
-      <c r="H1" t="s">
-        <v>512</v>
-      </c>
       <c r="I1" t="s">
-        <v>354</v>
+        <v>510</v>
       </c>
       <c r="J1" t="s">
+        <v>353</v>
+      </c>
+      <c r="K1" t="s">
         <v>128</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
@@ -2104,28 +2116,31 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G2" t="s">
-        <v>477</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H2" t="s">
+        <v>475</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>354</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="K2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2139,28 +2154,31 @@
         <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" t="s">
         <v>208</v>
       </c>
-      <c r="G3" t="s">
-        <v>445</v>
-      </c>
       <c r="H3" t="s">
-        <v>357</v>
+        <v>443</v>
       </c>
       <c r="I3" t="s">
-        <v>355</v>
-      </c>
-      <c r="J3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J3" t="s">
+        <v>354</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -2174,33 +2192,36 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G4" t="s">
         <v>231</v>
       </c>
-      <c r="F4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G4" t="s">
-        <v>319</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="I4" t="s">
-        <v>355</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="H4" t="s">
+        <v>318</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="J4" t="s">
+        <v>354</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="28.5">
+      <c r="L4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="57">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -2209,33 +2230,36 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" t="s">
+        <v>226</v>
+      </c>
+      <c r="G5" t="s">
         <v>228</v>
       </c>
-      <c r="F5" t="s">
-        <v>229</v>
-      </c>
-      <c r="G5" t="s">
-        <v>440</v>
-      </c>
       <c r="H5" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="I5" t="s">
-        <v>359</v>
-      </c>
-      <c r="J5" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B6" t="s">
         <v>400</v>
-      </c>
-      <c r="B6" t="s">
-        <v>401</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -2244,28 +2268,31 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F6" t="s">
+        <v>480</v>
+      </c>
+      <c r="G6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" t="s">
+        <v>478</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>505</v>
+      </c>
+      <c r="L6" t="s">
         <v>480</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="I6" t="s">
-        <v>359</v>
-      </c>
-      <c r="J6" t="s">
-        <v>507</v>
-      </c>
-      <c r="K6" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -2279,28 +2306,31 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F7" t="s">
-        <v>233</v>
+        <v>331</v>
       </c>
       <c r="G7" t="s">
-        <v>476</v>
+        <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>361</v>
+        <v>474</v>
       </c>
       <c r="I7" t="s">
         <v>360</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" t="s">
+        <v>359</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="K7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>77</v>
       </c>
@@ -2314,28 +2344,31 @@
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>330</v>
       </c>
       <c r="G8" t="s">
-        <v>442</v>
+        <v>225</v>
       </c>
       <c r="H8" t="s">
-        <v>367</v>
+        <v>440</v>
       </c>
       <c r="I8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J8" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J8" t="s">
+        <v>354</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="K8" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -2349,30 +2382,33 @@
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G9" t="s">
-        <v>460</v>
+        <v>243</v>
       </c>
       <c r="H9" t="s">
-        <v>365</v>
+        <v>458</v>
       </c>
       <c r="I9" t="s">
-        <v>355</v>
-      </c>
-      <c r="J9" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="J9" t="s">
+        <v>354</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
         <v>79</v>
@@ -2384,28 +2420,31 @@
         <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F10" t="s">
-        <v>274</v>
+        <v>332</v>
       </c>
       <c r="G10" t="s">
-        <v>452</v>
+        <v>273</v>
       </c>
       <c r="H10" t="s">
-        <v>366</v>
+        <v>450</v>
       </c>
       <c r="I10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J10" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J10" t="s">
+        <v>358</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K10" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -2419,28 +2458,31 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F11" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G11" t="s">
-        <v>432</v>
+        <v>249</v>
       </c>
       <c r="H11" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="I11" t="s">
-        <v>382</v>
-      </c>
-      <c r="J11" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J11" t="s">
+        <v>381</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="K11" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -2454,28 +2496,31 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G12" t="s">
-        <v>444</v>
+        <v>248</v>
       </c>
       <c r="H12" t="s">
-        <v>506</v>
+        <v>442</v>
       </c>
       <c r="I12" t="s">
-        <v>355</v>
-      </c>
-      <c r="J12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="J12" t="s">
+        <v>354</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="K12" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -2489,28 +2534,31 @@
         <v>34</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F13" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G13" t="s">
-        <v>466</v>
+        <v>246</v>
       </c>
       <c r="H13" t="s">
+        <v>464</v>
+      </c>
+      <c r="I13" t="s">
+        <v>361</v>
+      </c>
+      <c r="J13" t="s">
         <v>362</v>
       </c>
-      <c r="I13" t="s">
-        <v>363</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="K13" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2524,33 +2572,36 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F14" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G14" t="s">
-        <v>461</v>
+        <v>225</v>
       </c>
       <c r="H14" t="s">
-        <v>368</v>
+        <v>459</v>
       </c>
       <c r="I14" t="s">
-        <v>359</v>
-      </c>
-      <c r="J14" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="J14" t="s">
+        <v>358</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2558,29 +2609,32 @@
       <c r="D15" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="F15" t="s">
+        <v>396</v>
+      </c>
+      <c r="G15" t="s">
+        <v>414</v>
+      </c>
+      <c r="H15">
+        <v>155</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="F15" t="s">
-        <v>416</v>
-      </c>
-      <c r="G15">
-        <v>155</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="I15" t="s">
-        <v>359</v>
-      </c>
       <c r="J15" t="s">
-        <v>508</v>
+        <v>358</v>
       </c>
       <c r="K15" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>506</v>
+      </c>
+      <c r="L15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2594,28 +2648,31 @@
         <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F16" t="s">
-        <v>240</v>
+        <v>334</v>
       </c>
       <c r="G16" t="s">
-        <v>465</v>
+        <v>239</v>
       </c>
       <c r="H16" t="s">
-        <v>370</v>
+        <v>463</v>
       </c>
       <c r="I16" t="s">
-        <v>355</v>
-      </c>
-      <c r="J16" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="J16" t="s">
+        <v>354</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K16" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2628,29 +2685,32 @@
       <c r="D17" t="s">
         <v>57</v>
       </c>
-      <c r="E17" t="s">
-        <v>514</v>
+      <c r="E17" s="6" t="s">
+        <v>533</v>
       </c>
       <c r="F17" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G17" t="s">
-        <v>468</v>
+        <v>237</v>
       </c>
       <c r="H17" t="s">
-        <v>371</v>
+        <v>466</v>
       </c>
       <c r="I17" t="s">
-        <v>359</v>
-      </c>
-      <c r="J17" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="J17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K17" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -2664,28 +2724,31 @@
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F18" t="s">
-        <v>239</v>
+        <v>335</v>
       </c>
       <c r="G18" t="s">
-        <v>462</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="I18" t="s">
-        <v>355</v>
-      </c>
-      <c r="J18" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H18" t="s">
+        <v>460</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J18" t="s">
+        <v>354</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="K18" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>80</v>
       </c>
@@ -2699,28 +2762,31 @@
         <v>31</v>
       </c>
       <c r="E19" t="s">
+        <v>271</v>
+      </c>
+      <c r="F19" t="s">
+        <v>373</v>
+      </c>
+      <c r="G19" t="s">
         <v>272</v>
       </c>
-      <c r="F19" t="s">
-        <v>273</v>
-      </c>
-      <c r="G19" t="s">
-        <v>469</v>
-      </c>
       <c r="H19" t="s">
-        <v>375</v>
+        <v>467</v>
       </c>
       <c r="I19" t="s">
-        <v>359</v>
-      </c>
-      <c r="J19" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J19" t="s">
+        <v>358</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K19" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -2734,28 +2800,31 @@
         <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F20" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="G20" t="s">
-        <v>458</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="I20" t="s">
-        <v>359</v>
-      </c>
-      <c r="J20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H20" t="s">
+        <v>456</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="J20" t="s">
+        <v>358</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="K20" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>111</v>
       </c>
@@ -2769,28 +2838,31 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F21" t="s">
-        <v>265</v>
+        <v>345</v>
       </c>
       <c r="G21" t="s">
-        <v>470</v>
+        <v>264</v>
       </c>
       <c r="H21" t="s">
-        <v>379</v>
+        <v>468</v>
       </c>
       <c r="I21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J21" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J21" t="s">
+        <v>410</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="K21" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -2804,30 +2876,33 @@
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F22" t="s">
-        <v>266</v>
+        <v>343</v>
       </c>
       <c r="G22" t="s">
-        <v>474</v>
+        <v>265</v>
       </c>
       <c r="H22" t="s">
-        <v>378</v>
+        <v>472</v>
       </c>
       <c r="I22" t="s">
-        <v>412</v>
-      </c>
-      <c r="J22" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J22" t="s">
+        <v>411</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="K22" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B23" t="s">
         <v>113</v>
@@ -2839,28 +2914,31 @@
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>525</v>
-      </c>
-      <c r="F23" t="s">
+        <v>522</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G23" t="s">
         <v>207</v>
       </c>
-      <c r="G23" t="s">
-        <v>455</v>
-      </c>
       <c r="H23" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="I23" t="s">
-        <v>382</v>
-      </c>
-      <c r="J23" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J23" t="s">
+        <v>381</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K23" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>114</v>
       </c>
@@ -2874,28 +2952,31 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
+        <v>255</v>
+      </c>
+      <c r="F24" t="s">
+        <v>220</v>
+      </c>
+      <c r="G24" t="s">
         <v>256</v>
       </c>
-      <c r="F24" t="s">
-        <v>257</v>
-      </c>
-      <c r="G24" t="s">
-        <v>459</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="I24" t="s">
-        <v>388</v>
-      </c>
-      <c r="J24" s="2" t="s">
+      <c r="H24" t="s">
+        <v>457</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J24" t="s">
+        <v>387</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>116</v>
       </c>
@@ -2909,28 +2990,31 @@
         <v>109</v>
       </c>
       <c r="E25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F25" t="s">
+        <v>221</v>
+      </c>
+      <c r="G25" t="s">
         <v>254</v>
       </c>
-      <c r="F25" t="s">
-        <v>255</v>
-      </c>
-      <c r="G25" t="s">
-        <v>472</v>
-      </c>
       <c r="H25" t="s">
-        <v>389</v>
+        <v>470</v>
       </c>
       <c r="I25" t="s">
-        <v>355</v>
-      </c>
-      <c r="J25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J25" t="s">
+        <v>354</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K25" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -2944,28 +3028,31 @@
         <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F26" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="G26" t="s">
-        <v>463</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="I26" t="s">
-        <v>410</v>
-      </c>
-      <c r="J26" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H26" t="s">
+        <v>461</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J26" t="s">
+        <v>409</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="K26" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>120</v>
       </c>
@@ -2979,28 +3066,31 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F27" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="G27" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="H27" t="s">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c r="I27" t="s">
         <v>382</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" t="s">
+        <v>381</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="K27" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -3014,33 +3104,36 @@
         <v>109</v>
       </c>
       <c r="E28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" t="s">
+        <v>223</v>
+      </c>
+      <c r="G28" t="s">
         <v>258</v>
       </c>
-      <c r="F28" t="s">
-        <v>259</v>
-      </c>
-      <c r="G28" t="s">
-        <v>428</v>
-      </c>
       <c r="H28" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="I28" t="s">
-        <v>355</v>
-      </c>
-      <c r="J28" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J28" t="s">
+        <v>354</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K28" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
+        <v>402</v>
+      </c>
+      <c r="B29" t="s">
         <v>403</v>
-      </c>
-      <c r="B29" t="s">
-        <v>404</v>
       </c>
       <c r="C29" t="s">
         <v>44</v>
@@ -3049,28 +3142,31 @@
         <v>34</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F29" t="s">
-        <v>483</v>
-      </c>
-      <c r="G29">
+        <v>404</v>
+      </c>
+      <c r="G29" t="s">
+        <v>481</v>
+      </c>
+      <c r="H29">
         <v>117</v>
       </c>
-      <c r="H29" t="s">
-        <v>484</v>
-      </c>
       <c r="I29" t="s">
-        <v>359</v>
+        <v>482</v>
       </c>
       <c r="J29" t="s">
-        <v>509</v>
+        <v>358</v>
       </c>
       <c r="K29" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>507</v>
+      </c>
+      <c r="L29" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -3084,28 +3180,31 @@
         <v>31</v>
       </c>
       <c r="E30" t="s">
+        <v>269</v>
+      </c>
+      <c r="F30" t="s">
+        <v>268</v>
+      </c>
+      <c r="G30" t="s">
         <v>270</v>
       </c>
-      <c r="F30" t="s">
-        <v>271</v>
-      </c>
-      <c r="G30" t="s">
-        <v>450</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="I30" t="s">
-        <v>359</v>
-      </c>
-      <c r="J30" s="2" t="s">
+      <c r="H30" t="s">
+        <v>448</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J30" t="s">
+        <v>358</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="K30" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -3119,28 +3218,31 @@
         <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>339</v>
-      </c>
-      <c r="F31" t="s">
-        <v>251</v>
+        <v>338</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="G31" t="s">
-        <v>457</v>
+        <v>250</v>
       </c>
       <c r="H31" t="s">
-        <v>377</v>
+        <v>455</v>
       </c>
       <c r="I31" t="s">
         <v>376</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" t="s">
+        <v>375</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="K31" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -3154,28 +3256,31 @@
         <v>16</v>
       </c>
       <c r="E32" t="s">
+        <v>217</v>
+      </c>
+      <c r="F32" t="s">
+        <v>216</v>
+      </c>
+      <c r="G32" t="s">
         <v>218</v>
       </c>
-      <c r="F32" t="s">
-        <v>219</v>
-      </c>
-      <c r="G32" t="s">
-        <v>320</v>
-      </c>
       <c r="H32" t="s">
-        <v>392</v>
+        <v>319</v>
       </c>
       <c r="I32" t="s">
-        <v>355</v>
-      </c>
-      <c r="J32" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J32" t="s">
+        <v>354</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K32" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -3189,30 +3294,33 @@
         <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F33" t="s">
+        <v>212</v>
+      </c>
+      <c r="G33" t="s">
         <v>207</v>
       </c>
-      <c r="G33" t="s">
-        <v>456</v>
-      </c>
       <c r="H33" t="s">
-        <v>497</v>
+        <v>454</v>
       </c>
       <c r="I33" t="s">
-        <v>359</v>
-      </c>
-      <c r="J33" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="J33" t="s">
+        <v>358</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="28.5">
+    <row r="34" spans="1:12" ht="42.75">
       <c r="A34" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s">
         <v>74</v>
@@ -3224,28 +3332,31 @@
         <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F34" t="s">
-        <v>252</v>
+        <v>344</v>
       </c>
       <c r="G34" t="s">
-        <v>475</v>
+        <v>251</v>
       </c>
       <c r="H34" t="s">
-        <v>409</v>
+        <v>473</v>
       </c>
       <c r="I34" t="s">
-        <v>359</v>
-      </c>
-      <c r="J34" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="J34" t="s">
+        <v>358</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K34" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -3261,26 +3372,29 @@
       <c r="E35" t="s">
         <v>206</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G35" t="s">
         <v>207</v>
       </c>
-      <c r="G35" t="s">
-        <v>454</v>
-      </c>
       <c r="H35" t="s">
-        <v>499</v>
+        <v>452</v>
       </c>
       <c r="I35" t="s">
-        <v>355</v>
-      </c>
-      <c r="J35" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J35" t="s">
+        <v>354</v>
+      </c>
+      <c r="K35" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -3296,26 +3410,29 @@
       <c r="E36" t="s">
         <v>210</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G36" t="s">
         <v>211</v>
       </c>
-      <c r="G36" t="s">
-        <v>438</v>
-      </c>
       <c r="H36" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="I36" t="s">
-        <v>355</v>
-      </c>
-      <c r="J36" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="J36" t="s">
+        <v>354</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="K36" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -3329,28 +3446,31 @@
         <v>34</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F37" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G37" t="s">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="H37" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
       <c r="I37" t="s">
-        <v>359</v>
-      </c>
-      <c r="J37" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="J37" t="s">
+        <v>358</v>
+      </c>
+      <c r="K37" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K37" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3363,29 +3483,32 @@
       <c r="D38" t="s">
         <v>26</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="F38" t="s">
+        <v>203</v>
+      </c>
+      <c r="G38" t="s">
         <v>215</v>
       </c>
-      <c r="F38" t="s">
-        <v>216</v>
-      </c>
-      <c r="G38" t="s">
-        <v>464</v>
-      </c>
       <c r="H38" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="I38" t="s">
-        <v>355</v>
-      </c>
-      <c r="J38" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="J38" t="s">
+        <v>354</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -3401,26 +3524,29 @@
       <c r="E39" t="s">
         <v>214</v>
       </c>
-      <c r="F39" t="s">
-        <v>326</v>
+      <c r="F39" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="G39" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H39" t="s">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="I39" t="s">
-        <v>382</v>
-      </c>
-      <c r="J39" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="J39" t="s">
+        <v>381</v>
+      </c>
+      <c r="K39" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -3434,28 +3560,31 @@
         <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F40" t="s">
+        <v>205</v>
+      </c>
+      <c r="G40" t="s">
         <v>213</v>
       </c>
-      <c r="G40" t="s">
-        <v>441</v>
-      </c>
       <c r="H40" t="s">
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="I40" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J40" t="s">
+        <v>381</v>
+      </c>
+      <c r="K40" t="s">
         <v>184</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -3469,28 +3598,31 @@
         <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>306</v>
-      </c>
-      <c r="F41" t="s">
+        <v>305</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G41" t="s">
         <v>201</v>
       </c>
-      <c r="G41" t="s">
-        <v>418</v>
-      </c>
       <c r="H41" t="s">
-        <v>494</v>
+        <v>416</v>
       </c>
       <c r="I41" t="s">
-        <v>382</v>
-      </c>
-      <c r="J41" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J41" t="s">
+        <v>381</v>
+      </c>
+      <c r="K41" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -3504,33 +3636,36 @@
         <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>522</v>
-      </c>
-      <c r="F42" t="s">
+        <v>519</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G42" t="s">
         <v>208</v>
       </c>
-      <c r="G42" t="s">
-        <v>430</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="I42" t="s">
-        <v>399</v>
-      </c>
-      <c r="J42" s="2" t="s">
+      <c r="H42" t="s">
+        <v>428</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J42" t="s">
+        <v>398</v>
+      </c>
+      <c r="K42" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
+        <v>406</v>
+      </c>
+      <c r="B43" t="s">
         <v>407</v>
-      </c>
-      <c r="B43" t="s">
-        <v>408</v>
       </c>
       <c r="C43" t="s">
         <v>44</v>
@@ -3539,28 +3674,31 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
+        <v>287</v>
+      </c>
+      <c r="F43" t="s">
         <v>288</v>
       </c>
-      <c r="F43" t="s">
-        <v>287</v>
-      </c>
       <c r="G43" t="s">
+        <v>286</v>
+      </c>
+      <c r="H43" t="s">
+        <v>483</v>
+      </c>
+      <c r="I43" t="s">
         <v>485</v>
       </c>
-      <c r="H43" t="s">
-        <v>487</v>
-      </c>
-      <c r="I43" t="s">
-        <v>355</v>
-      </c>
       <c r="J43" t="s">
+        <v>354</v>
+      </c>
+      <c r="K43" t="s">
         <v>163</v>
       </c>
-      <c r="K43" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>62</v>
       </c>
@@ -3574,28 +3712,31 @@
         <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F44" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="G44" t="s">
-        <v>448</v>
+        <v>325</v>
       </c>
       <c r="H44" t="s">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="I44" t="s">
-        <v>359</v>
-      </c>
-      <c r="J44" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="J44" t="s">
+        <v>358</v>
+      </c>
+      <c r="K44" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K44" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>64</v>
       </c>
@@ -3609,28 +3750,31 @@
         <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F45" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G45" t="s">
-        <v>473</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="I45" t="s">
-        <v>355</v>
-      </c>
-      <c r="J45" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H45" t="s">
+        <v>471</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J45" t="s">
+        <v>354</v>
+      </c>
+      <c r="K45" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="K45" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="L45" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -3644,28 +3788,31 @@
         <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>304</v>
-      </c>
-      <c r="F46" t="s">
-        <v>274</v>
+        <v>303</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="G46" t="s">
-        <v>453</v>
+        <v>273</v>
       </c>
       <c r="H46" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="I46" t="s">
-        <v>355</v>
-      </c>
-      <c r="J46" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="J46" t="s">
+        <v>354</v>
+      </c>
+      <c r="K46" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K46" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3679,28 +3826,31 @@
         <v>31</v>
       </c>
       <c r="E47" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F47" t="s">
-        <v>267</v>
+        <v>317</v>
       </c>
       <c r="G47" t="s">
-        <v>443</v>
+        <v>266</v>
       </c>
       <c r="H47" t="s">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="I47" t="s">
-        <v>359</v>
-      </c>
-      <c r="J47" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="J47" t="s">
+        <v>358</v>
+      </c>
+      <c r="K47" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="K47" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -3714,28 +3864,31 @@
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>527</v>
-      </c>
-      <c r="F48" t="s">
+        <v>524</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G48" t="s">
         <v>213</v>
       </c>
-      <c r="G48" t="s">
-        <v>441</v>
-      </c>
       <c r="H48" t="s">
-        <v>493</v>
+        <v>439</v>
       </c>
       <c r="I48" t="s">
-        <v>382</v>
-      </c>
-      <c r="J48" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J48" t="s">
+        <v>381</v>
+      </c>
+      <c r="K48" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -3749,28 +3902,31 @@
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F49" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G49" t="s">
-        <v>467</v>
+        <v>245</v>
       </c>
       <c r="H49" t="s">
-        <v>364</v>
+        <v>465</v>
       </c>
       <c r="I49" t="s">
-        <v>355</v>
-      </c>
-      <c r="J49" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="J49" t="s">
+        <v>354</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="K49" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="L49" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>90</v>
       </c>
@@ -3784,28 +3940,31 @@
         <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>523</v>
-      </c>
-      <c r="F50" t="s">
-        <v>300</v>
+        <v>520</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="G50" t="s">
-        <v>420</v>
+        <v>299</v>
       </c>
       <c r="H50" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I50" t="s">
-        <v>359</v>
-      </c>
-      <c r="J50" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="J50" t="s">
+        <v>358</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="K50" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="L50" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
         <v>93</v>
       </c>
@@ -3819,28 +3978,31 @@
         <v>31</v>
       </c>
       <c r="E51" t="s">
+        <v>300</v>
+      </c>
+      <c r="F51" t="s">
+        <v>350</v>
+      </c>
+      <c r="G51" t="s">
         <v>301</v>
       </c>
-      <c r="F51" t="s">
-        <v>302</v>
-      </c>
-      <c r="G51" t="s">
-        <v>446</v>
-      </c>
       <c r="H51" t="s">
-        <v>504</v>
+        <v>444</v>
       </c>
       <c r="I51" t="s">
-        <v>360</v>
-      </c>
-      <c r="J51" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="J51" t="s">
+        <v>359</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="K51" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="L51" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -3854,28 +4016,31 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>516</v>
-      </c>
-      <c r="F52" t="s">
-        <v>300</v>
+        <v>513</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="G52" t="s">
-        <v>426</v>
+        <v>299</v>
       </c>
       <c r="H52" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="I52" t="s">
-        <v>359</v>
-      </c>
-      <c r="J52" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J52" t="s">
+        <v>358</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K52" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="L52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
         <v>95</v>
       </c>
@@ -3889,28 +4054,31 @@
         <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>517</v>
-      </c>
-      <c r="F53" t="s">
-        <v>298</v>
+        <v>514</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>534</v>
       </c>
       <c r="G53" t="s">
-        <v>451</v>
+        <v>297</v>
       </c>
       <c r="H53" t="s">
-        <v>501</v>
+        <v>449</v>
       </c>
       <c r="I53" t="s">
-        <v>382</v>
-      </c>
-      <c r="J53" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="J53" t="s">
+        <v>381</v>
+      </c>
+      <c r="K53" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K53" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="L53" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
         <v>96</v>
       </c>
@@ -3924,28 +4092,31 @@
         <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F54" t="s">
-        <v>219</v>
+        <v>316</v>
       </c>
       <c r="G54" t="s">
-        <v>447</v>
+        <v>218</v>
       </c>
       <c r="H54" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
       <c r="I54" t="s">
-        <v>359</v>
-      </c>
-      <c r="J54" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J54" t="s">
+        <v>358</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="K54" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
         <v>97</v>
       </c>
@@ -3959,28 +4130,31 @@
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F55" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G55" t="s">
-        <v>431</v>
+        <v>296</v>
       </c>
       <c r="H55" t="s">
-        <v>489</v>
+        <v>429</v>
       </c>
       <c r="I55" t="s">
-        <v>355</v>
-      </c>
-      <c r="J55" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J55" t="s">
+        <v>354</v>
+      </c>
+      <c r="K55" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K55" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -3994,28 +4168,31 @@
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F56" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G56" t="s">
-        <v>427</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="I56" t="s">
-        <v>359</v>
-      </c>
-      <c r="J56" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H56" t="s">
+        <v>425</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="J56" t="s">
+        <v>358</v>
+      </c>
+      <c r="K56" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K56" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
         <v>99</v>
       </c>
@@ -4029,28 +4206,31 @@
         <v>31</v>
       </c>
       <c r="E57" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F57" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G57" t="s">
-        <v>478</v>
+        <v>292</v>
       </c>
       <c r="H57" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="I57" t="s">
-        <v>359</v>
-      </c>
-      <c r="J57" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="J57" t="s">
+        <v>358</v>
+      </c>
+      <c r="K57" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="K57" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="L57" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>101</v>
       </c>
@@ -4064,28 +4244,31 @@
         <v>31</v>
       </c>
       <c r="E58" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G58" t="s">
-        <v>437</v>
+        <v>290</v>
       </c>
       <c r="H58" t="s">
-        <v>492</v>
+        <v>435</v>
       </c>
       <c r="I58" t="s">
-        <v>359</v>
-      </c>
-      <c r="J58" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J58" t="s">
+        <v>358</v>
+      </c>
+      <c r="K58" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="K58" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="L58" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
         <v>103</v>
       </c>
@@ -4099,28 +4282,31 @@
         <v>31</v>
       </c>
       <c r="E59" t="s">
+        <v>287</v>
+      </c>
+      <c r="F59" t="s">
         <v>288</v>
       </c>
-      <c r="F59" t="s">
-        <v>287</v>
-      </c>
       <c r="G59" t="s">
-        <v>439</v>
+        <v>286</v>
       </c>
       <c r="H59" t="s">
-        <v>505</v>
+        <v>437</v>
       </c>
       <c r="I59" t="s">
-        <v>359</v>
-      </c>
-      <c r="J59" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="J59" t="s">
+        <v>358</v>
+      </c>
+      <c r="K59" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="K59" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="L59" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
         <v>104</v>
       </c>
@@ -4134,28 +4320,31 @@
         <v>31</v>
       </c>
       <c r="E60" t="s">
+        <v>284</v>
+      </c>
+      <c r="F60" t="s">
+        <v>283</v>
+      </c>
+      <c r="G60" t="s">
         <v>285</v>
       </c>
-      <c r="F60" t="s">
-        <v>286</v>
-      </c>
-      <c r="G60" t="s">
-        <v>449</v>
-      </c>
       <c r="H60" t="s">
-        <v>502</v>
+        <v>447</v>
       </c>
       <c r="I60" t="s">
-        <v>372</v>
-      </c>
-      <c r="J60" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="J60" t="s">
+        <v>371</v>
+      </c>
+      <c r="K60" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="K60" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="L60" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
         <v>106</v>
       </c>
@@ -4169,28 +4358,31 @@
         <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F61" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G61" t="s">
-        <v>454</v>
+        <v>282</v>
       </c>
       <c r="H61" t="s">
-        <v>498</v>
+        <v>452</v>
       </c>
       <c r="I61" t="s">
-        <v>359</v>
-      </c>
-      <c r="J61" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J61" t="s">
+        <v>358</v>
+      </c>
+      <c r="K61" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="K61" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="L61" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
         <v>107</v>
       </c>
@@ -4204,28 +4396,31 @@
         <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F62" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="G62" t="s">
-        <v>421</v>
+        <v>326</v>
       </c>
       <c r="H62" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I62" t="s">
-        <v>359</v>
-      </c>
-      <c r="J62" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="J62" t="s">
+        <v>358</v>
+      </c>
+      <c r="K62" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="K62" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="L62" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
         <v>108</v>
       </c>
@@ -4239,30 +4434,33 @@
         <v>31</v>
       </c>
       <c r="E63" t="s">
+        <v>277</v>
+      </c>
+      <c r="F63" t="s">
+        <v>276</v>
+      </c>
+      <c r="G63" t="s">
         <v>278</v>
       </c>
-      <c r="F63" t="s">
-        <v>279</v>
-      </c>
-      <c r="G63" t="s">
-        <v>435</v>
-      </c>
       <c r="H63" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="I63" t="s">
-        <v>359</v>
-      </c>
-      <c r="J63" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="J63" t="s">
+        <v>358</v>
+      </c>
+      <c r="K63" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K63" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="L63" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B64" t="s">
         <v>110</v>
@@ -4274,28 +4472,31 @@
         <v>31</v>
       </c>
       <c r="E64" t="s">
+        <v>421</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G64" t="s">
+        <v>299</v>
+      </c>
+      <c r="H64" t="s">
         <v>423</v>
       </c>
-      <c r="F64" t="s">
-        <v>300</v>
-      </c>
-      <c r="G64" t="s">
-        <v>425</v>
-      </c>
-      <c r="H64" t="s">
-        <v>424</v>
-      </c>
       <c r="I64" t="s">
-        <v>359</v>
-      </c>
-      <c r="J64" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J64" t="s">
+        <v>358</v>
+      </c>
+      <c r="K64" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="K64" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="L64" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -4309,28 +4510,31 @@
         <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>531</v>
-      </c>
-      <c r="F65" t="s">
+        <v>528</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G65" t="s">
         <v>209</v>
       </c>
-      <c r="G65" t="s">
-        <v>436</v>
-      </c>
       <c r="H65" t="s">
-        <v>491</v>
+        <v>434</v>
       </c>
       <c r="I65" t="s">
-        <v>360</v>
-      </c>
-      <c r="J65" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="J65" t="s">
+        <v>359</v>
+      </c>
+      <c r="K65" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -4346,26 +4550,29 @@
       <c r="E66" t="s">
         <v>195</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G66" t="s">
         <v>197</v>
       </c>
-      <c r="G66" t="s">
-        <v>429</v>
-      </c>
       <c r="H66" t="s">
-        <v>488</v>
+        <v>427</v>
       </c>
       <c r="I66" t="s">
-        <v>372</v>
+        <v>486</v>
       </c>
       <c r="J66" t="s">
+        <v>371</v>
+      </c>
+      <c r="K66" t="s">
         <v>143</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
         <v>126</v>
       </c>
@@ -4379,150 +4586,200 @@
         <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F67" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G67" t="s">
-        <v>471</v>
+        <v>262</v>
       </c>
       <c r="H67" t="s">
-        <v>381</v>
+        <v>469</v>
       </c>
       <c r="I67" t="s">
-        <v>373</v>
-      </c>
-      <c r="J67" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J67" t="s">
+        <v>372</v>
+      </c>
+      <c r="K67" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="K67" t="s">
-        <v>262</v>
+      <c r="L67" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1">
+  <autoFilter ref="A1:L1">
     <sortState ref="A2:K67">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J64" r:id="rId1"/>
-    <hyperlink ref="J51" r:id="rId2"/>
-    <hyperlink ref="J54" r:id="rId3"/>
-    <hyperlink ref="J34" r:id="rId4"/>
-    <hyperlink ref="J22" r:id="rId5"/>
-    <hyperlink ref="J20" r:id="rId6"/>
-    <hyperlink ref="J53" r:id="rId7"/>
-    <hyperlink ref="J17" r:id="rId8"/>
-    <hyperlink ref="J52" r:id="rId9"/>
-    <hyperlink ref="J50" r:id="rId10"/>
-    <hyperlink ref="J36" r:id="rId11"/>
-    <hyperlink ref="J18" r:id="rId12"/>
-    <hyperlink ref="J16" r:id="rId13"/>
-    <hyperlink ref="J27" r:id="rId14"/>
-    <hyperlink ref="J24" r:id="rId15"/>
-    <hyperlink ref="J56" r:id="rId16"/>
-    <hyperlink ref="J67" r:id="rId17"/>
-    <hyperlink ref="J32" r:id="rId18"/>
-    <hyperlink ref="J55" r:id="rId19"/>
-    <hyperlink ref="J42" r:id="rId20"/>
-    <hyperlink ref="J41" r:id="rId21"/>
-    <hyperlink ref="J21" r:id="rId22"/>
-    <hyperlink ref="J13" r:id="rId23"/>
-    <hyperlink ref="J26" r:id="rId24"/>
-    <hyperlink ref="J62" r:id="rId25"/>
-    <hyperlink ref="J33" r:id="rId26"/>
-    <hyperlink ref="J23" r:id="rId27"/>
-    <hyperlink ref="J5" r:id="rId28"/>
-    <hyperlink ref="J61" r:id="rId29"/>
-    <hyperlink ref="J60" r:id="rId30"/>
-    <hyperlink ref="J3" r:id="rId31"/>
-    <hyperlink ref="J14" r:id="rId32"/>
-    <hyperlink ref="J59" r:id="rId33"/>
-    <hyperlink ref="J58" r:id="rId34"/>
-    <hyperlink ref="J57" r:id="rId35"/>
-    <hyperlink ref="J19" r:id="rId36"/>
-    <hyperlink ref="J48" r:id="rId37"/>
-    <hyperlink ref="J47" r:id="rId38"/>
-    <hyperlink ref="J30" r:id="rId39"/>
-    <hyperlink ref="J8" r:id="rId40"/>
-    <hyperlink ref="J46" r:id="rId41"/>
-    <hyperlink ref="J10" r:id="rId42"/>
-    <hyperlink ref="J2" r:id="rId43"/>
-    <hyperlink ref="J25" r:id="rId44"/>
-    <hyperlink ref="J28" r:id="rId45"/>
-    <hyperlink ref="J31" r:id="rId46"/>
-    <hyperlink ref="J63" r:id="rId47"/>
-    <hyperlink ref="J38" r:id="rId48"/>
-    <hyperlink ref="J39" r:id="rId49"/>
-    <hyperlink ref="J65" r:id="rId50"/>
-    <hyperlink ref="J49" r:id="rId51" location="texto"/>
-    <hyperlink ref="J45" r:id="rId52"/>
-    <hyperlink ref="J44" r:id="rId53"/>
-    <hyperlink ref="J37" r:id="rId54"/>
-    <hyperlink ref="J35" r:id="rId55"/>
-    <hyperlink ref="J4" r:id="rId56"/>
-    <hyperlink ref="J12" r:id="rId57"/>
-    <hyperlink ref="J9" r:id="rId58"/>
-    <hyperlink ref="J7" r:id="rId59"/>
-    <hyperlink ref="J11" r:id="rId60"/>
-    <hyperlink ref="K48" r:id="rId61"/>
-    <hyperlink ref="K41" r:id="rId62"/>
-    <hyperlink ref="K35" r:id="rId63"/>
-    <hyperlink ref="K33" r:id="rId64"/>
-    <hyperlink ref="K40" r:id="rId65"/>
-    <hyperlink ref="K39" r:id="rId66"/>
-    <hyperlink ref="K38" r:id="rId67"/>
-    <hyperlink ref="K32" r:id="rId68"/>
-    <hyperlink ref="K14" r:id="rId69"/>
-    <hyperlink ref="K5" r:id="rId70"/>
-    <hyperlink ref="K4" r:id="rId71"/>
-    <hyperlink ref="K45" r:id="rId72"/>
-    <hyperlink ref="K37" r:id="rId73"/>
-    <hyperlink ref="K17" r:id="rId74"/>
-    <hyperlink ref="K9" r:id="rId75"/>
-    <hyperlink ref="K49" r:id="rId76"/>
-    <hyperlink ref="K13" r:id="rId77"/>
-    <hyperlink ref="K12" r:id="rId78"/>
-    <hyperlink ref="K11" r:id="rId79"/>
-    <hyperlink ref="K31" r:id="rId80"/>
-    <hyperlink ref="K26" r:id="rId81"/>
-    <hyperlink ref="K25" r:id="rId82"/>
-    <hyperlink ref="K24" r:id="rId83"/>
-    <hyperlink ref="K28" r:id="rId84"/>
-    <hyperlink ref="K23" r:id="rId85"/>
-    <hyperlink ref="K46" r:id="rId86"/>
-    <hyperlink ref="K30" r:id="rId87"/>
-    <hyperlink ref="K2" r:id="rId88"/>
-    <hyperlink ref="K65" r:id="rId89" display="http://www.jucemg.mg.gov.br"/>
-    <hyperlink ref="K67" r:id="rId90" display="http://www.gabinetemilitar.mg.gov.br"/>
-    <hyperlink ref="K63" r:id="rId91"/>
-    <hyperlink ref="K62" r:id="rId92"/>
-    <hyperlink ref="K61" r:id="rId93"/>
-    <hyperlink ref="K60" r:id="rId94"/>
-    <hyperlink ref="K59" r:id="rId95"/>
-    <hyperlink ref="K58" r:id="rId96"/>
-    <hyperlink ref="K57" r:id="rId97"/>
-    <hyperlink ref="K56" r:id="rId98"/>
-    <hyperlink ref="K55" r:id="rId99"/>
-    <hyperlink ref="K64" r:id="rId100"/>
-    <hyperlink ref="K27" r:id="rId101"/>
-    <hyperlink ref="K47" r:id="rId102"/>
-    <hyperlink ref="H2" r:id="rId103"/>
-    <hyperlink ref="H4" r:id="rId104"/>
-    <hyperlink ref="H18" r:id="rId105"/>
-    <hyperlink ref="H20" r:id="rId106"/>
-    <hyperlink ref="H24" r:id="rId107"/>
-    <hyperlink ref="H26" r:id="rId108"/>
-    <hyperlink ref="H45" r:id="rId109"/>
-    <hyperlink ref="H6" r:id="rId110"/>
-    <hyperlink ref="H56" r:id="rId111"/>
-    <hyperlink ref="H42" r:id="rId112"/>
-    <hyperlink ref="K42" r:id="rId113"/>
-    <hyperlink ref="K66" r:id="rId114" display="http://www.loteriamineira.mg.gov.br"/>
+    <hyperlink ref="K64" r:id="rId1"/>
+    <hyperlink ref="K51" r:id="rId2"/>
+    <hyperlink ref="K54" r:id="rId3"/>
+    <hyperlink ref="K34" r:id="rId4"/>
+    <hyperlink ref="K22" r:id="rId5"/>
+    <hyperlink ref="K20" r:id="rId6"/>
+    <hyperlink ref="K53" r:id="rId7"/>
+    <hyperlink ref="K17" r:id="rId8"/>
+    <hyperlink ref="K52" r:id="rId9"/>
+    <hyperlink ref="K50" r:id="rId10"/>
+    <hyperlink ref="K36" r:id="rId11"/>
+    <hyperlink ref="K18" r:id="rId12"/>
+    <hyperlink ref="K16" r:id="rId13"/>
+    <hyperlink ref="K27" r:id="rId14"/>
+    <hyperlink ref="K24" r:id="rId15"/>
+    <hyperlink ref="K56" r:id="rId16"/>
+    <hyperlink ref="K67" r:id="rId17"/>
+    <hyperlink ref="K32" r:id="rId18"/>
+    <hyperlink ref="K55" r:id="rId19"/>
+    <hyperlink ref="K42" r:id="rId20"/>
+    <hyperlink ref="K41" r:id="rId21"/>
+    <hyperlink ref="K21" r:id="rId22"/>
+    <hyperlink ref="K13" r:id="rId23"/>
+    <hyperlink ref="K26" r:id="rId24"/>
+    <hyperlink ref="K62" r:id="rId25"/>
+    <hyperlink ref="K33" r:id="rId26"/>
+    <hyperlink ref="K23" r:id="rId27"/>
+    <hyperlink ref="K5" r:id="rId28"/>
+    <hyperlink ref="K61" r:id="rId29"/>
+    <hyperlink ref="K60" r:id="rId30"/>
+    <hyperlink ref="K3" r:id="rId31"/>
+    <hyperlink ref="K14" r:id="rId32"/>
+    <hyperlink ref="K59" r:id="rId33"/>
+    <hyperlink ref="K58" r:id="rId34"/>
+    <hyperlink ref="K57" r:id="rId35"/>
+    <hyperlink ref="K19" r:id="rId36"/>
+    <hyperlink ref="K48" r:id="rId37"/>
+    <hyperlink ref="K47" r:id="rId38"/>
+    <hyperlink ref="K30" r:id="rId39"/>
+    <hyperlink ref="K8" r:id="rId40"/>
+    <hyperlink ref="K46" r:id="rId41"/>
+    <hyperlink ref="K10" r:id="rId42"/>
+    <hyperlink ref="K2" r:id="rId43"/>
+    <hyperlink ref="K25" r:id="rId44"/>
+    <hyperlink ref="K28" r:id="rId45"/>
+    <hyperlink ref="K31" r:id="rId46"/>
+    <hyperlink ref="K63" r:id="rId47"/>
+    <hyperlink ref="K38" r:id="rId48"/>
+    <hyperlink ref="K39" r:id="rId49"/>
+    <hyperlink ref="K65" r:id="rId50"/>
+    <hyperlink ref="K49" r:id="rId51" location="texto"/>
+    <hyperlink ref="K45" r:id="rId52"/>
+    <hyperlink ref="K44" r:id="rId53"/>
+    <hyperlink ref="K37" r:id="rId54"/>
+    <hyperlink ref="K35" r:id="rId55"/>
+    <hyperlink ref="K4" r:id="rId56"/>
+    <hyperlink ref="K12" r:id="rId57"/>
+    <hyperlink ref="K9" r:id="rId58"/>
+    <hyperlink ref="K7" r:id="rId59"/>
+    <hyperlink ref="K11" r:id="rId60"/>
+    <hyperlink ref="L48" r:id="rId61"/>
+    <hyperlink ref="L41" r:id="rId62"/>
+    <hyperlink ref="L35" r:id="rId63"/>
+    <hyperlink ref="L33" r:id="rId64"/>
+    <hyperlink ref="L40" r:id="rId65"/>
+    <hyperlink ref="L39" r:id="rId66"/>
+    <hyperlink ref="L38" r:id="rId67"/>
+    <hyperlink ref="L32" r:id="rId68"/>
+    <hyperlink ref="L14" r:id="rId69"/>
+    <hyperlink ref="L5" r:id="rId70"/>
+    <hyperlink ref="L4" r:id="rId71"/>
+    <hyperlink ref="L45" r:id="rId72"/>
+    <hyperlink ref="L37" r:id="rId73"/>
+    <hyperlink ref="L17" r:id="rId74"/>
+    <hyperlink ref="L9" r:id="rId75"/>
+    <hyperlink ref="L49" r:id="rId76"/>
+    <hyperlink ref="L13" r:id="rId77"/>
+    <hyperlink ref="L12" r:id="rId78"/>
+    <hyperlink ref="L11" r:id="rId79"/>
+    <hyperlink ref="L31" r:id="rId80"/>
+    <hyperlink ref="L26" r:id="rId81"/>
+    <hyperlink ref="L25" r:id="rId82"/>
+    <hyperlink ref="L24" r:id="rId83"/>
+    <hyperlink ref="L28" r:id="rId84"/>
+    <hyperlink ref="L23" r:id="rId85"/>
+    <hyperlink ref="L46" r:id="rId86"/>
+    <hyperlink ref="L30" r:id="rId87"/>
+    <hyperlink ref="L2" r:id="rId88"/>
+    <hyperlink ref="L65" r:id="rId89" display="http://www.jucemg.mg.gov.br"/>
+    <hyperlink ref="L67" r:id="rId90" display="http://www.gabinetemilitar.mg.gov.br"/>
+    <hyperlink ref="L63" r:id="rId91"/>
+    <hyperlink ref="L62" r:id="rId92"/>
+    <hyperlink ref="L61" r:id="rId93"/>
+    <hyperlink ref="L60" r:id="rId94"/>
+    <hyperlink ref="L59" r:id="rId95"/>
+    <hyperlink ref="L58" r:id="rId96"/>
+    <hyperlink ref="L57" r:id="rId97"/>
+    <hyperlink ref="L56" r:id="rId98"/>
+    <hyperlink ref="L55" r:id="rId99"/>
+    <hyperlink ref="L64" r:id="rId100"/>
+    <hyperlink ref="L27" r:id="rId101"/>
+    <hyperlink ref="L47" r:id="rId102"/>
+    <hyperlink ref="I2" r:id="rId103"/>
+    <hyperlink ref="I4" r:id="rId104"/>
+    <hyperlink ref="I18" r:id="rId105"/>
+    <hyperlink ref="I20" r:id="rId106"/>
+    <hyperlink ref="I24" r:id="rId107"/>
+    <hyperlink ref="I26" r:id="rId108"/>
+    <hyperlink ref="I45" r:id="rId109"/>
+    <hyperlink ref="I6" r:id="rId110"/>
+    <hyperlink ref="I56" r:id="rId111"/>
+    <hyperlink ref="I42" r:id="rId112"/>
+    <hyperlink ref="L42" r:id="rId113"/>
+    <hyperlink ref="L66" r:id="rId114" display="http://www.loteriamineira.mg.gov.br"/>
+    <hyperlink ref="F48" r:id="rId115"/>
+    <hyperlink ref="F41" r:id="rId116"/>
+    <hyperlink ref="F35" r:id="rId117"/>
+    <hyperlink ref="F33" r:id="rId118"/>
+    <hyperlink ref="F40" r:id="rId119"/>
+    <hyperlink ref="F39" r:id="rId120"/>
+    <hyperlink ref="F38" r:id="rId121"/>
+    <hyperlink ref="F32" r:id="rId122"/>
+    <hyperlink ref="F14" r:id="rId123"/>
+    <hyperlink ref="F5" r:id="rId124"/>
+    <hyperlink ref="F4" r:id="rId125"/>
+    <hyperlink ref="F45" r:id="rId126"/>
+    <hyperlink ref="F37" r:id="rId127"/>
+    <hyperlink ref="F17" r:id="rId128"/>
+    <hyperlink ref="F9" r:id="rId129"/>
+    <hyperlink ref="F49" r:id="rId130"/>
+    <hyperlink ref="F13" r:id="rId131"/>
+    <hyperlink ref="F12" r:id="rId132"/>
+    <hyperlink ref="F11" r:id="rId133"/>
+    <hyperlink ref="F31" r:id="rId134"/>
+    <hyperlink ref="F26" r:id="rId135"/>
+    <hyperlink ref="F25" r:id="rId136"/>
+    <hyperlink ref="F24" r:id="rId137"/>
+    <hyperlink ref="F28" r:id="rId138"/>
+    <hyperlink ref="F23" r:id="rId139"/>
+    <hyperlink ref="F46" r:id="rId140"/>
+    <hyperlink ref="F30" r:id="rId141"/>
+    <hyperlink ref="F2" r:id="rId142"/>
+    <hyperlink ref="F65" r:id="rId143"/>
+    <hyperlink ref="F67" r:id="rId144" display="http://www.gabinetemilitar.mg.gov.br"/>
+    <hyperlink ref="F63" r:id="rId145"/>
+    <hyperlink ref="F62" r:id="rId146"/>
+    <hyperlink ref="F61" r:id="rId147"/>
+    <hyperlink ref="F60" r:id="rId148"/>
+    <hyperlink ref="F59" r:id="rId149"/>
+    <hyperlink ref="F58" r:id="rId150"/>
+    <hyperlink ref="F57" r:id="rId151"/>
+    <hyperlink ref="F56" r:id="rId152"/>
+    <hyperlink ref="F55" r:id="rId153"/>
+    <hyperlink ref="F64" r:id="rId154"/>
+    <hyperlink ref="F27" r:id="rId155"/>
+    <hyperlink ref="F47" r:id="rId156"/>
+    <hyperlink ref="F42" r:id="rId157"/>
+    <hyperlink ref="F66" r:id="rId158"/>
+    <hyperlink ref="F36" r:id="rId159"/>
+    <hyperlink ref="F50" r:id="rId160"/>
+    <hyperlink ref="F52" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId115"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId162"/>
 </worksheet>
 </file>